--- a/formularios/devolucao_credito.xlsx
+++ b/formularios/devolucao_credito.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CONTROLE DE QUALIDADE\formularios\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B4F54BA-6DE8-43A6-84D5-0982ADA6AEBC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E43D89CC-0488-4EFF-A9AC-C726D6C754C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -828,7 +828,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="115">
+  <cellXfs count="116">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
@@ -927,7 +927,6 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -949,9 +948,6 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -989,136 +985,145 @@
     <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1651,66 +1656,66 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:23" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="73" t="s">
+      <c r="A1" s="95" t="s">
         <v>29</v>
       </c>
-      <c r="B1" s="73"/>
-      <c r="C1" s="73"/>
-      <c r="D1" s="73"/>
-      <c r="E1" s="73"/>
+      <c r="B1" s="95"/>
+      <c r="C1" s="95"/>
+      <c r="D1" s="95"/>
+      <c r="E1" s="95"/>
       <c r="F1" s="25"/>
-      <c r="G1" s="74" t="s">
+      <c r="G1" s="96" t="s">
         <v>0</v>
       </c>
-      <c r="H1" s="74"/>
-      <c r="I1" s="74"/>
-      <c r="J1" s="74"/>
-      <c r="K1" s="74"/>
-      <c r="L1" s="74"/>
-      <c r="M1" s="74"/>
-      <c r="N1" s="74"/>
-      <c r="O1" s="74"/>
-      <c r="P1" s="74"/>
-      <c r="Q1" s="74"/>
-      <c r="R1" s="74"/>
+      <c r="H1" s="96"/>
+      <c r="I1" s="96"/>
+      <c r="J1" s="96"/>
+      <c r="K1" s="96"/>
+      <c r="L1" s="96"/>
+      <c r="M1" s="96"/>
+      <c r="N1" s="96"/>
+      <c r="O1" s="96"/>
+      <c r="P1" s="96"/>
+      <c r="Q1" s="96"/>
+      <c r="R1" s="96"/>
     </row>
     <row r="2" spans="1:23" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="73" t="s">
+      <c r="A2" s="95" t="s">
         <v>39</v>
       </c>
-      <c r="B2" s="73"/>
-      <c r="C2" s="73"/>
-      <c r="D2" s="73"/>
-      <c r="E2" s="73"/>
+      <c r="B2" s="95"/>
+      <c r="C2" s="95"/>
+      <c r="D2" s="95"/>
+      <c r="E2" s="95"/>
       <c r="F2" s="25"/>
-      <c r="G2" s="74"/>
-      <c r="H2" s="74"/>
-      <c r="I2" s="74"/>
-      <c r="J2" s="74"/>
-      <c r="K2" s="74"/>
-      <c r="L2" s="74"/>
-      <c r="M2" s="74"/>
-      <c r="N2" s="74"/>
-      <c r="O2" s="74"/>
-      <c r="P2" s="74"/>
-      <c r="Q2" s="74"/>
-      <c r="R2" s="74"/>
+      <c r="G2" s="96"/>
+      <c r="H2" s="96"/>
+      <c r="I2" s="96"/>
+      <c r="J2" s="96"/>
+      <c r="K2" s="96"/>
+      <c r="L2" s="96"/>
+      <c r="M2" s="96"/>
+      <c r="N2" s="96"/>
+      <c r="O2" s="96"/>
+      <c r="P2" s="96"/>
+      <c r="Q2" s="96"/>
+      <c r="R2" s="96"/>
     </row>
     <row r="3" spans="1:23" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="E3" s="6"/>
       <c r="F3" s="6"/>
-      <c r="G3" s="74"/>
-      <c r="H3" s="74"/>
-      <c r="I3" s="74"/>
-      <c r="J3" s="74"/>
-      <c r="K3" s="74"/>
-      <c r="L3" s="74"/>
-      <c r="M3" s="74"/>
-      <c r="N3" s="74"/>
-      <c r="O3" s="74"/>
-      <c r="P3" s="74"/>
-      <c r="Q3" s="74"/>
-      <c r="R3" s="74"/>
+      <c r="G3" s="96"/>
+      <c r="H3" s="96"/>
+      <c r="I3" s="96"/>
+      <c r="J3" s="96"/>
+      <c r="K3" s="96"/>
+      <c r="L3" s="96"/>
+      <c r="M3" s="96"/>
+      <c r="N3" s="96"/>
+      <c r="O3" s="96"/>
+      <c r="P3" s="96"/>
+      <c r="Q3" s="96"/>
+      <c r="R3" s="96"/>
     </row>
     <row r="4" spans="1:23" ht="5.0999999999999996" customHeight="1" x14ac:dyDescent="0.3">
       <c r="E4" s="2"/>
@@ -1730,38 +1735,38 @@
     </row>
     <row r="5" spans="1:23" ht="5.0999999999999996" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="10"/>
-      <c r="B5" s="75"/>
-      <c r="C5" s="75"/>
-      <c r="D5" s="75"/>
-      <c r="E5" s="75"/>
-      <c r="F5" s="75"/>
-      <c r="G5" s="75"/>
-      <c r="H5" s="75"/>
-      <c r="I5" s="75"/>
-      <c r="J5" s="75"/>
-      <c r="K5" s="75"/>
-      <c r="L5" s="75"/>
-      <c r="M5" s="75"/>
-      <c r="N5" s="75"/>
-      <c r="O5" s="75"/>
-      <c r="P5" s="75"/>
-      <c r="Q5" s="75"/>
-      <c r="R5" s="75"/>
-      <c r="S5" s="75"/>
-      <c r="T5" s="75"/>
-      <c r="U5" s="75"/>
-      <c r="V5" s="75"/>
-      <c r="W5" s="75"/>
+      <c r="B5" s="91"/>
+      <c r="C5" s="91"/>
+      <c r="D5" s="91"/>
+      <c r="E5" s="91"/>
+      <c r="F5" s="91"/>
+      <c r="G5" s="91"/>
+      <c r="H5" s="91"/>
+      <c r="I5" s="91"/>
+      <c r="J5" s="91"/>
+      <c r="K5" s="91"/>
+      <c r="L5" s="91"/>
+      <c r="M5" s="91"/>
+      <c r="N5" s="91"/>
+      <c r="O5" s="91"/>
+      <c r="P5" s="91"/>
+      <c r="Q5" s="91"/>
+      <c r="R5" s="91"/>
+      <c r="S5" s="91"/>
+      <c r="T5" s="91"/>
+      <c r="U5" s="91"/>
+      <c r="V5" s="91"/>
+      <c r="W5" s="91"/>
     </row>
     <row r="6" spans="1:23" ht="5.0999999999999996" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="7" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="76" t="s">
+      <c r="A7" s="69" t="s">
         <v>46</v>
       </c>
-      <c r="B7" s="76"/>
-      <c r="C7" s="76"/>
-      <c r="D7" s="76"/>
-      <c r="E7" s="76"/>
+      <c r="B7" s="69"/>
+      <c r="C7" s="69"/>
+      <c r="D7" s="69"/>
+      <c r="E7" s="69"/>
       <c r="F7" s="18"/>
       <c r="G7" s="2"/>
       <c r="H7" s="2"/>
@@ -1796,29 +1801,29 @@
       <c r="R8" s="2"/>
     </row>
     <row r="9" spans="1:23" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="71" t="s">
+      <c r="A9" s="79" t="s">
         <v>40</v>
       </c>
-      <c r="B9" s="71"/>
-      <c r="C9" s="71"/>
-      <c r="D9" s="72"/>
-      <c r="E9" s="72"/>
+      <c r="B9" s="79"/>
+      <c r="C9" s="79"/>
+      <c r="D9" s="90"/>
+      <c r="E9" s="90"/>
       <c r="F9" s="26"/>
-      <c r="J9" s="77" t="s">
+      <c r="J9" s="87" t="s">
         <v>41</v>
       </c>
-      <c r="K9" s="77"/>
+      <c r="K9" s="87"/>
       <c r="L9" s="19"/>
       <c r="M9" s="19"/>
       <c r="N9" s="19"/>
       <c r="O9"/>
       <c r="R9"/>
       <c r="S9"/>
-      <c r="T9" s="71" t="s">
+      <c r="T9" s="79" t="s">
         <v>42</v>
       </c>
-      <c r="U9" s="71"/>
-      <c r="V9" s="71"/>
+      <c r="U9" s="79"/>
+      <c r="V9" s="79"/>
       <c r="W9" s="5"/>
     </row>
     <row r="10" spans="1:23" ht="5.0999999999999996" customHeight="1" x14ac:dyDescent="0.3">
@@ -1838,31 +1843,31 @@
       <c r="R10" s="2"/>
     </row>
     <row r="11" spans="1:23" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="71" t="s">
+      <c r="A11" s="79" t="s">
         <v>48</v>
       </c>
-      <c r="B11" s="71"/>
-      <c r="C11" s="71"/>
-      <c r="D11" s="72"/>
-      <c r="E11" s="72"/>
-      <c r="F11" s="72"/>
-      <c r="G11" s="72"/>
-      <c r="H11" s="72"/>
-      <c r="I11" s="72"/>
-      <c r="J11" s="72"/>
-      <c r="K11" s="72"/>
-      <c r="L11" s="72"/>
-      <c r="M11" s="72"/>
-      <c r="N11" s="72"/>
-      <c r="O11" s="72"/>
-      <c r="P11" s="72"/>
-      <c r="Q11" s="72"/>
-      <c r="R11" s="72"/>
-      <c r="S11" s="72"/>
-      <c r="T11" s="72"/>
-      <c r="U11" s="72"/>
-      <c r="V11" s="72"/>
-      <c r="W11" s="72"/>
+      <c r="B11" s="79"/>
+      <c r="C11" s="79"/>
+      <c r="D11" s="90"/>
+      <c r="E11" s="90"/>
+      <c r="F11" s="90"/>
+      <c r="G11" s="90"/>
+      <c r="H11" s="90"/>
+      <c r="I11" s="90"/>
+      <c r="J11" s="90"/>
+      <c r="K11" s="90"/>
+      <c r="L11" s="90"/>
+      <c r="M11" s="90"/>
+      <c r="N11" s="90"/>
+      <c r="O11" s="90"/>
+      <c r="P11" s="90"/>
+      <c r="Q11" s="90"/>
+      <c r="R11" s="90"/>
+      <c r="S11" s="90"/>
+      <c r="T11" s="90"/>
+      <c r="U11" s="90"/>
+      <c r="V11" s="90"/>
+      <c r="W11" s="90"/>
     </row>
     <row r="12" spans="1:23" ht="5.0999999999999996" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="11"/>
@@ -1870,31 +1875,31 @@
       <c r="C12" s="12"/>
     </row>
     <row r="13" spans="1:23" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="71" t="s">
+      <c r="A13" s="79" t="s">
         <v>25</v>
       </c>
-      <c r="B13" s="71"/>
-      <c r="C13" s="71"/>
-      <c r="D13" s="72"/>
-      <c r="E13" s="72"/>
-      <c r="F13" s="72"/>
-      <c r="G13" s="72"/>
-      <c r="H13" s="72"/>
-      <c r="I13" s="72"/>
-      <c r="J13" s="72"/>
-      <c r="K13" s="72"/>
-      <c r="L13" s="72"/>
-      <c r="M13" s="72"/>
-      <c r="N13" s="72"/>
-      <c r="O13" s="72"/>
-      <c r="P13" s="72"/>
-      <c r="Q13" s="72"/>
-      <c r="R13" s="72"/>
-      <c r="S13" s="72"/>
-      <c r="T13" s="72"/>
-      <c r="U13" s="72"/>
-      <c r="V13" s="72"/>
-      <c r="W13" s="72"/>
+      <c r="B13" s="79"/>
+      <c r="C13" s="79"/>
+      <c r="D13" s="90"/>
+      <c r="E13" s="90"/>
+      <c r="F13" s="90"/>
+      <c r="G13" s="90"/>
+      <c r="H13" s="90"/>
+      <c r="I13" s="90"/>
+      <c r="J13" s="90"/>
+      <c r="K13" s="90"/>
+      <c r="L13" s="90"/>
+      <c r="M13" s="90"/>
+      <c r="N13" s="90"/>
+      <c r="O13" s="90"/>
+      <c r="P13" s="90"/>
+      <c r="Q13" s="90"/>
+      <c r="R13" s="90"/>
+      <c r="S13" s="90"/>
+      <c r="T13" s="90"/>
+      <c r="U13" s="90"/>
+      <c r="V13" s="90"/>
+      <c r="W13" s="90"/>
     </row>
     <row r="14" spans="1:23" ht="5.0999999999999996" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="12"/>
@@ -1902,75 +1907,75 @@
       <c r="C14" s="12"/>
     </row>
     <row r="15" spans="1:23" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="71" t="s">
+      <c r="A15" s="79" t="s">
         <v>26</v>
       </c>
-      <c r="B15" s="71"/>
-      <c r="C15" s="71"/>
-      <c r="D15" s="72"/>
-      <c r="E15" s="72"/>
+      <c r="B15" s="79"/>
+      <c r="C15" s="79"/>
+      <c r="D15" s="90"/>
+      <c r="E15" s="90"/>
       <c r="F15" s="26"/>
       <c r="G15" s="24" t="s">
         <v>43</v>
       </c>
-      <c r="H15" s="72"/>
-      <c r="I15" s="72"/>
-      <c r="J15" s="72"/>
-      <c r="K15" s="71" t="s">
+      <c r="H15" s="90"/>
+      <c r="I15" s="90"/>
+      <c r="J15" s="90"/>
+      <c r="K15" s="79" t="s">
         <v>27</v>
       </c>
-      <c r="L15" s="71"/>
+      <c r="L15" s="79"/>
       <c r="M15" s="20"/>
-      <c r="N15" s="72"/>
-      <c r="O15" s="72"/>
-      <c r="P15" s="72"/>
-      <c r="Q15" s="77" t="s">
+      <c r="N15" s="90"/>
+      <c r="O15" s="90"/>
+      <c r="P15" s="90"/>
+      <c r="Q15" s="87" t="s">
         <v>28</v>
       </c>
-      <c r="R15" s="77"/>
-      <c r="S15" s="77"/>
-      <c r="T15" s="72"/>
-      <c r="U15" s="72"/>
-      <c r="V15" s="72"/>
-      <c r="W15" s="72"/>
+      <c r="R15" s="87"/>
+      <c r="S15" s="87"/>
+      <c r="T15" s="90"/>
+      <c r="U15" s="90"/>
+      <c r="V15" s="90"/>
+      <c r="W15" s="90"/>
     </row>
     <row r="16" spans="1:23" ht="5.0999999999999996" customHeight="1" x14ac:dyDescent="0.3">
       <c r="J16" s="2"/>
     </row>
     <row r="17" spans="1:92" ht="5.0999999999999996" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="10"/>
-      <c r="B17" s="75"/>
-      <c r="C17" s="75"/>
-      <c r="D17" s="75"/>
-      <c r="E17" s="75"/>
-      <c r="F17" s="75"/>
-      <c r="G17" s="75"/>
-      <c r="H17" s="75"/>
-      <c r="I17" s="75"/>
-      <c r="J17" s="75"/>
-      <c r="K17" s="75"/>
-      <c r="L17" s="75"/>
-      <c r="M17" s="75"/>
-      <c r="N17" s="75"/>
-      <c r="O17" s="75"/>
-      <c r="P17" s="75"/>
-      <c r="Q17" s="75"/>
-      <c r="R17" s="75"/>
-      <c r="S17" s="75"/>
-      <c r="T17" s="75"/>
-      <c r="U17" s="75"/>
-      <c r="V17" s="75"/>
-      <c r="W17" s="75"/>
+      <c r="B17" s="91"/>
+      <c r="C17" s="91"/>
+      <c r="D17" s="91"/>
+      <c r="E17" s="91"/>
+      <c r="F17" s="91"/>
+      <c r="G17" s="91"/>
+      <c r="H17" s="91"/>
+      <c r="I17" s="91"/>
+      <c r="J17" s="91"/>
+      <c r="K17" s="91"/>
+      <c r="L17" s="91"/>
+      <c r="M17" s="91"/>
+      <c r="N17" s="91"/>
+      <c r="O17" s="91"/>
+      <c r="P17" s="91"/>
+      <c r="Q17" s="91"/>
+      <c r="R17" s="91"/>
+      <c r="S17" s="91"/>
+      <c r="T17" s="91"/>
+      <c r="U17" s="91"/>
+      <c r="V17" s="91"/>
+      <c r="W17" s="91"/>
     </row>
     <row r="18" spans="1:92" ht="5.0999999999999996" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="19" spans="1:92" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="76" t="s">
+      <c r="A19" s="69" t="s">
         <v>18</v>
       </c>
-      <c r="B19" s="76"/>
-      <c r="C19" s="76"/>
-      <c r="D19" s="76"/>
-      <c r="E19" s="76"/>
+      <c r="B19" s="69"/>
+      <c r="C19" s="69"/>
+      <c r="D19" s="69"/>
+      <c r="E19" s="69"/>
       <c r="F19" s="18"/>
       <c r="G19" s="13"/>
       <c r="H19" s="13"/>
@@ -2060,31 +2065,31 @@
       <c r="CN19"/>
     </row>
     <row r="20" spans="1:92" s="1" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="78" t="s">
+      <c r="A20" s="92" t="s">
         <v>47</v>
       </c>
-      <c r="B20" s="78"/>
-      <c r="C20" s="78"/>
-      <c r="D20" s="78"/>
-      <c r="E20" s="78"/>
-      <c r="F20" s="78"/>
-      <c r="G20" s="78"/>
-      <c r="H20" s="78"/>
-      <c r="I20" s="78"/>
-      <c r="J20" s="78"/>
-      <c r="K20" s="78"/>
-      <c r="L20" s="78"/>
-      <c r="M20" s="78"/>
-      <c r="N20" s="78"/>
-      <c r="O20" s="78"/>
-      <c r="P20" s="78"/>
-      <c r="Q20" s="78"/>
-      <c r="R20" s="78"/>
-      <c r="S20" s="78"/>
-      <c r="T20" s="78"/>
-      <c r="U20" s="78"/>
-      <c r="V20" s="78"/>
-      <c r="W20" s="78"/>
+      <c r="B20" s="92"/>
+      <c r="C20" s="92"/>
+      <c r="D20" s="92"/>
+      <c r="E20" s="92"/>
+      <c r="F20" s="92"/>
+      <c r="G20" s="92"/>
+      <c r="H20" s="92"/>
+      <c r="I20" s="92"/>
+      <c r="J20" s="92"/>
+      <c r="K20" s="92"/>
+      <c r="L20" s="92"/>
+      <c r="M20" s="92"/>
+      <c r="N20" s="92"/>
+      <c r="O20" s="92"/>
+      <c r="P20" s="92"/>
+      <c r="Q20" s="92"/>
+      <c r="R20" s="92"/>
+      <c r="S20" s="92"/>
+      <c r="T20" s="92"/>
+      <c r="U20" s="92"/>
+      <c r="V20" s="92"/>
+      <c r="W20" s="92"/>
       <c r="X20"/>
       <c r="Y20"/>
       <c r="Z20"/>
@@ -2156,29 +2161,29 @@
       <c r="CN20"/>
     </row>
     <row r="21" spans="1:92" s="1" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="78"/>
-      <c r="B21" s="78"/>
-      <c r="C21" s="78"/>
-      <c r="D21" s="78"/>
-      <c r="E21" s="78"/>
-      <c r="F21" s="78"/>
-      <c r="G21" s="78"/>
-      <c r="H21" s="78"/>
-      <c r="I21" s="78"/>
-      <c r="J21" s="78"/>
-      <c r="K21" s="78"/>
-      <c r="L21" s="78"/>
-      <c r="M21" s="78"/>
-      <c r="N21" s="78"/>
-      <c r="O21" s="78"/>
-      <c r="P21" s="78"/>
-      <c r="Q21" s="78"/>
-      <c r="R21" s="78"/>
-      <c r="S21" s="78"/>
-      <c r="T21" s="78"/>
-      <c r="U21" s="78"/>
-      <c r="V21" s="78"/>
-      <c r="W21" s="78"/>
+      <c r="A21" s="92"/>
+      <c r="B21" s="92"/>
+      <c r="C21" s="92"/>
+      <c r="D21" s="92"/>
+      <c r="E21" s="92"/>
+      <c r="F21" s="92"/>
+      <c r="G21" s="92"/>
+      <c r="H21" s="92"/>
+      <c r="I21" s="92"/>
+      <c r="J21" s="92"/>
+      <c r="K21" s="92"/>
+      <c r="L21" s="92"/>
+      <c r="M21" s="92"/>
+      <c r="N21" s="92"/>
+      <c r="O21" s="92"/>
+      <c r="P21" s="92"/>
+      <c r="Q21" s="92"/>
+      <c r="R21" s="92"/>
+      <c r="S21" s="92"/>
+      <c r="T21" s="92"/>
+      <c r="U21" s="92"/>
+      <c r="V21" s="92"/>
+      <c r="W21" s="92"/>
       <c r="X21"/>
       <c r="Y21"/>
       <c r="Z21"/>
@@ -2250,29 +2255,29 @@
       <c r="CN21"/>
     </row>
     <row r="22" spans="1:92" s="1" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="78"/>
-      <c r="B22" s="78"/>
-      <c r="C22" s="78"/>
-      <c r="D22" s="78"/>
-      <c r="E22" s="78"/>
-      <c r="F22" s="78"/>
-      <c r="G22" s="78"/>
-      <c r="H22" s="78"/>
-      <c r="I22" s="78"/>
-      <c r="J22" s="78"/>
-      <c r="K22" s="78"/>
-      <c r="L22" s="78"/>
-      <c r="M22" s="78"/>
-      <c r="N22" s="78"/>
-      <c r="O22" s="78"/>
-      <c r="P22" s="78"/>
-      <c r="Q22" s="78"/>
-      <c r="R22" s="78"/>
-      <c r="S22" s="78"/>
-      <c r="T22" s="78"/>
-      <c r="U22" s="78"/>
-      <c r="V22" s="78"/>
-      <c r="W22" s="78"/>
+      <c r="A22" s="92"/>
+      <c r="B22" s="92"/>
+      <c r="C22" s="92"/>
+      <c r="D22" s="92"/>
+      <c r="E22" s="92"/>
+      <c r="F22" s="92"/>
+      <c r="G22" s="92"/>
+      <c r="H22" s="92"/>
+      <c r="I22" s="92"/>
+      <c r="J22" s="92"/>
+      <c r="K22" s="92"/>
+      <c r="L22" s="92"/>
+      <c r="M22" s="92"/>
+      <c r="N22" s="92"/>
+      <c r="O22" s="92"/>
+      <c r="P22" s="92"/>
+      <c r="Q22" s="92"/>
+      <c r="R22" s="92"/>
+      <c r="S22" s="92"/>
+      <c r="T22" s="92"/>
+      <c r="U22" s="92"/>
+      <c r="V22" s="92"/>
+      <c r="W22" s="92"/>
       <c r="X22"/>
       <c r="Y22"/>
       <c r="Z22"/>
@@ -2344,29 +2349,29 @@
       <c r="CN22"/>
     </row>
     <row r="23" spans="1:92" s="1" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="78"/>
-      <c r="B23" s="78"/>
-      <c r="C23" s="78"/>
-      <c r="D23" s="78"/>
-      <c r="E23" s="78"/>
-      <c r="F23" s="78"/>
-      <c r="G23" s="78"/>
-      <c r="H23" s="78"/>
-      <c r="I23" s="78"/>
-      <c r="J23" s="78"/>
-      <c r="K23" s="78"/>
-      <c r="L23" s="78"/>
-      <c r="M23" s="78"/>
-      <c r="N23" s="78"/>
-      <c r="O23" s="78"/>
-      <c r="P23" s="78"/>
-      <c r="Q23" s="78"/>
-      <c r="R23" s="78"/>
-      <c r="S23" s="78"/>
-      <c r="T23" s="78"/>
-      <c r="U23" s="78"/>
-      <c r="V23" s="78"/>
-      <c r="W23" s="78"/>
+      <c r="A23" s="92"/>
+      <c r="B23" s="92"/>
+      <c r="C23" s="92"/>
+      <c r="D23" s="92"/>
+      <c r="E23" s="92"/>
+      <c r="F23" s="92"/>
+      <c r="G23" s="92"/>
+      <c r="H23" s="92"/>
+      <c r="I23" s="92"/>
+      <c r="J23" s="92"/>
+      <c r="K23" s="92"/>
+      <c r="L23" s="92"/>
+      <c r="M23" s="92"/>
+      <c r="N23" s="92"/>
+      <c r="O23" s="92"/>
+      <c r="P23" s="92"/>
+      <c r="Q23" s="92"/>
+      <c r="R23" s="92"/>
+      <c r="S23" s="92"/>
+      <c r="T23" s="92"/>
+      <c r="U23" s="92"/>
+      <c r="V23" s="92"/>
+      <c r="W23" s="92"/>
       <c r="X23"/>
       <c r="Y23"/>
       <c r="Z23"/>
@@ -2438,29 +2443,29 @@
       <c r="CN23"/>
     </row>
     <row r="24" spans="1:92" s="1" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="78"/>
-      <c r="B24" s="78"/>
-      <c r="C24" s="78"/>
-      <c r="D24" s="78"/>
-      <c r="E24" s="78"/>
-      <c r="F24" s="78"/>
-      <c r="G24" s="78"/>
-      <c r="H24" s="78"/>
-      <c r="I24" s="78"/>
-      <c r="J24" s="78"/>
-      <c r="K24" s="78"/>
-      <c r="L24" s="78"/>
-      <c r="M24" s="78"/>
-      <c r="N24" s="78"/>
-      <c r="O24" s="78"/>
-      <c r="P24" s="78"/>
-      <c r="Q24" s="78"/>
-      <c r="R24" s="78"/>
-      <c r="S24" s="78"/>
-      <c r="T24" s="78"/>
-      <c r="U24" s="78"/>
-      <c r="V24" s="78"/>
-      <c r="W24" s="78"/>
+      <c r="A24" s="92"/>
+      <c r="B24" s="92"/>
+      <c r="C24" s="92"/>
+      <c r="D24" s="92"/>
+      <c r="E24" s="92"/>
+      <c r="F24" s="92"/>
+      <c r="G24" s="92"/>
+      <c r="H24" s="92"/>
+      <c r="I24" s="92"/>
+      <c r="J24" s="92"/>
+      <c r="K24" s="92"/>
+      <c r="L24" s="92"/>
+      <c r="M24" s="92"/>
+      <c r="N24" s="92"/>
+      <c r="O24" s="92"/>
+      <c r="P24" s="92"/>
+      <c r="Q24" s="92"/>
+      <c r="R24" s="92"/>
+      <c r="S24" s="92"/>
+      <c r="T24" s="92"/>
+      <c r="U24" s="92"/>
+      <c r="V24" s="92"/>
+      <c r="W24" s="92"/>
       <c r="X24"/>
       <c r="Y24"/>
       <c r="Z24"/>
@@ -2532,29 +2537,29 @@
       <c r="CN24"/>
     </row>
     <row r="25" spans="1:92" s="1" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="78"/>
-      <c r="B25" s="78"/>
-      <c r="C25" s="78"/>
-      <c r="D25" s="78"/>
-      <c r="E25" s="78"/>
-      <c r="F25" s="78"/>
-      <c r="G25" s="78"/>
-      <c r="H25" s="78"/>
-      <c r="I25" s="78"/>
-      <c r="J25" s="78"/>
-      <c r="K25" s="78"/>
-      <c r="L25" s="78"/>
-      <c r="M25" s="78"/>
-      <c r="N25" s="78"/>
-      <c r="O25" s="78"/>
-      <c r="P25" s="78"/>
-      <c r="Q25" s="78"/>
-      <c r="R25" s="78"/>
-      <c r="S25" s="78"/>
-      <c r="T25" s="78"/>
-      <c r="U25" s="78"/>
-      <c r="V25" s="78"/>
-      <c r="W25" s="78"/>
+      <c r="A25" s="92"/>
+      <c r="B25" s="92"/>
+      <c r="C25" s="92"/>
+      <c r="D25" s="92"/>
+      <c r="E25" s="92"/>
+      <c r="F25" s="92"/>
+      <c r="G25" s="92"/>
+      <c r="H25" s="92"/>
+      <c r="I25" s="92"/>
+      <c r="J25" s="92"/>
+      <c r="K25" s="92"/>
+      <c r="L25" s="92"/>
+      <c r="M25" s="92"/>
+      <c r="N25" s="92"/>
+      <c r="O25" s="92"/>
+      <c r="P25" s="92"/>
+      <c r="Q25" s="92"/>
+      <c r="R25" s="92"/>
+      <c r="S25" s="92"/>
+      <c r="T25" s="92"/>
+      <c r="U25" s="92"/>
+      <c r="V25" s="92"/>
+      <c r="W25" s="92"/>
       <c r="X25"/>
       <c r="Y25"/>
       <c r="Z25"/>
@@ -2626,29 +2631,29 @@
       <c r="CN25"/>
     </row>
     <row r="26" spans="1:92" s="1" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="78"/>
-      <c r="B26" s="78"/>
-      <c r="C26" s="78"/>
-      <c r="D26" s="78"/>
-      <c r="E26" s="78"/>
-      <c r="F26" s="78"/>
-      <c r="G26" s="78"/>
-      <c r="H26" s="78"/>
-      <c r="I26" s="78"/>
-      <c r="J26" s="78"/>
-      <c r="K26" s="78"/>
-      <c r="L26" s="78"/>
-      <c r="M26" s="78"/>
-      <c r="N26" s="78"/>
-      <c r="O26" s="78"/>
-      <c r="P26" s="78"/>
-      <c r="Q26" s="78"/>
-      <c r="R26" s="78"/>
-      <c r="S26" s="78"/>
-      <c r="T26" s="78"/>
-      <c r="U26" s="78"/>
-      <c r="V26" s="78"/>
-      <c r="W26" s="78"/>
+      <c r="A26" s="92"/>
+      <c r="B26" s="92"/>
+      <c r="C26" s="92"/>
+      <c r="D26" s="92"/>
+      <c r="E26" s="92"/>
+      <c r="F26" s="92"/>
+      <c r="G26" s="92"/>
+      <c r="H26" s="92"/>
+      <c r="I26" s="92"/>
+      <c r="J26" s="92"/>
+      <c r="K26" s="92"/>
+      <c r="L26" s="92"/>
+      <c r="M26" s="92"/>
+      <c r="N26" s="92"/>
+      <c r="O26" s="92"/>
+      <c r="P26" s="92"/>
+      <c r="Q26" s="92"/>
+      <c r="R26" s="92"/>
+      <c r="S26" s="92"/>
+      <c r="T26" s="92"/>
+      <c r="U26" s="92"/>
+      <c r="V26" s="92"/>
+      <c r="W26" s="92"/>
       <c r="X26"/>
       <c r="Y26"/>
       <c r="Z26"/>
@@ -2720,29 +2725,29 @@
       <c r="CN26"/>
     </row>
     <row r="27" spans="1:92" s="1" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="78"/>
-      <c r="B27" s="78"/>
-      <c r="C27" s="78"/>
-      <c r="D27" s="78"/>
-      <c r="E27" s="78"/>
-      <c r="F27" s="78"/>
-      <c r="G27" s="78"/>
-      <c r="H27" s="78"/>
-      <c r="I27" s="78"/>
-      <c r="J27" s="78"/>
-      <c r="K27" s="78"/>
-      <c r="L27" s="78"/>
-      <c r="M27" s="78"/>
-      <c r="N27" s="78"/>
-      <c r="O27" s="78"/>
-      <c r="P27" s="78"/>
-      <c r="Q27" s="78"/>
-      <c r="R27" s="78"/>
-      <c r="S27" s="78"/>
-      <c r="T27" s="78"/>
-      <c r="U27" s="78"/>
-      <c r="V27" s="78"/>
-      <c r="W27" s="78"/>
+      <c r="A27" s="92"/>
+      <c r="B27" s="92"/>
+      <c r="C27" s="92"/>
+      <c r="D27" s="92"/>
+      <c r="E27" s="92"/>
+      <c r="F27" s="92"/>
+      <c r="G27" s="92"/>
+      <c r="H27" s="92"/>
+      <c r="I27" s="92"/>
+      <c r="J27" s="92"/>
+      <c r="K27" s="92"/>
+      <c r="L27" s="92"/>
+      <c r="M27" s="92"/>
+      <c r="N27" s="92"/>
+      <c r="O27" s="92"/>
+      <c r="P27" s="92"/>
+      <c r="Q27" s="92"/>
+      <c r="R27" s="92"/>
+      <c r="S27" s="92"/>
+      <c r="T27" s="92"/>
+      <c r="U27" s="92"/>
+      <c r="V27" s="92"/>
+      <c r="W27" s="92"/>
       <c r="X27"/>
       <c r="Y27"/>
       <c r="Z27"/>
@@ -2814,29 +2819,29 @@
       <c r="CN27"/>
     </row>
     <row r="28" spans="1:92" s="1" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="78"/>
-      <c r="B28" s="78"/>
-      <c r="C28" s="78"/>
-      <c r="D28" s="78"/>
-      <c r="E28" s="78"/>
-      <c r="F28" s="78"/>
-      <c r="G28" s="78"/>
-      <c r="H28" s="78"/>
-      <c r="I28" s="78"/>
-      <c r="J28" s="78"/>
-      <c r="K28" s="78"/>
-      <c r="L28" s="78"/>
-      <c r="M28" s="78"/>
-      <c r="N28" s="78"/>
-      <c r="O28" s="78"/>
-      <c r="P28" s="78"/>
-      <c r="Q28" s="78"/>
-      <c r="R28" s="78"/>
-      <c r="S28" s="78"/>
-      <c r="T28" s="78"/>
-      <c r="U28" s="78"/>
-      <c r="V28" s="78"/>
-      <c r="W28" s="78"/>
+      <c r="A28" s="92"/>
+      <c r="B28" s="92"/>
+      <c r="C28" s="92"/>
+      <c r="D28" s="92"/>
+      <c r="E28" s="92"/>
+      <c r="F28" s="92"/>
+      <c r="G28" s="92"/>
+      <c r="H28" s="92"/>
+      <c r="I28" s="92"/>
+      <c r="J28" s="92"/>
+      <c r="K28" s="92"/>
+      <c r="L28" s="92"/>
+      <c r="M28" s="92"/>
+      <c r="N28" s="92"/>
+      <c r="O28" s="92"/>
+      <c r="P28" s="92"/>
+      <c r="Q28" s="92"/>
+      <c r="R28" s="92"/>
+      <c r="S28" s="92"/>
+      <c r="T28" s="92"/>
+      <c r="U28" s="92"/>
+      <c r="V28" s="92"/>
+      <c r="W28" s="92"/>
       <c r="X28"/>
       <c r="Y28"/>
       <c r="Z28"/>
@@ -2908,29 +2913,29 @@
       <c r="CN28"/>
     </row>
     <row r="29" spans="1:92" s="1" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="78"/>
-      <c r="B29" s="78"/>
-      <c r="C29" s="78"/>
-      <c r="D29" s="78"/>
-      <c r="E29" s="78"/>
-      <c r="F29" s="78"/>
-      <c r="G29" s="78"/>
-      <c r="H29" s="78"/>
-      <c r="I29" s="78"/>
-      <c r="J29" s="78"/>
-      <c r="K29" s="78"/>
-      <c r="L29" s="78"/>
-      <c r="M29" s="78"/>
-      <c r="N29" s="78"/>
-      <c r="O29" s="78"/>
-      <c r="P29" s="78"/>
-      <c r="Q29" s="78"/>
-      <c r="R29" s="78"/>
-      <c r="S29" s="78"/>
-      <c r="T29" s="78"/>
-      <c r="U29" s="78"/>
-      <c r="V29" s="78"/>
-      <c r="W29" s="78"/>
+      <c r="A29" s="92"/>
+      <c r="B29" s="92"/>
+      <c r="C29" s="92"/>
+      <c r="D29" s="92"/>
+      <c r="E29" s="92"/>
+      <c r="F29" s="92"/>
+      <c r="G29" s="92"/>
+      <c r="H29" s="92"/>
+      <c r="I29" s="92"/>
+      <c r="J29" s="92"/>
+      <c r="K29" s="92"/>
+      <c r="L29" s="92"/>
+      <c r="M29" s="92"/>
+      <c r="N29" s="92"/>
+      <c r="O29" s="92"/>
+      <c r="P29" s="92"/>
+      <c r="Q29" s="92"/>
+      <c r="R29" s="92"/>
+      <c r="S29" s="92"/>
+      <c r="T29" s="92"/>
+      <c r="U29" s="92"/>
+      <c r="V29" s="92"/>
+      <c r="W29" s="92"/>
       <c r="X29"/>
       <c r="Y29"/>
       <c r="Z29"/>
@@ -3002,29 +3007,29 @@
       <c r="CN29"/>
     </row>
     <row r="30" spans="1:92" s="1" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="78"/>
-      <c r="B30" s="78"/>
-      <c r="C30" s="78"/>
-      <c r="D30" s="78"/>
-      <c r="E30" s="78"/>
-      <c r="F30" s="78"/>
-      <c r="G30" s="78"/>
-      <c r="H30" s="78"/>
-      <c r="I30" s="78"/>
-      <c r="J30" s="78"/>
-      <c r="K30" s="78"/>
-      <c r="L30" s="78"/>
-      <c r="M30" s="78"/>
-      <c r="N30" s="78"/>
-      <c r="O30" s="78"/>
-      <c r="P30" s="78"/>
-      <c r="Q30" s="78"/>
-      <c r="R30" s="78"/>
-      <c r="S30" s="78"/>
-      <c r="T30" s="78"/>
-      <c r="U30" s="78"/>
-      <c r="V30" s="78"/>
-      <c r="W30" s="78"/>
+      <c r="A30" s="92"/>
+      <c r="B30" s="92"/>
+      <c r="C30" s="92"/>
+      <c r="D30" s="92"/>
+      <c r="E30" s="92"/>
+      <c r="F30" s="92"/>
+      <c r="G30" s="92"/>
+      <c r="H30" s="92"/>
+      <c r="I30" s="92"/>
+      <c r="J30" s="92"/>
+      <c r="K30" s="92"/>
+      <c r="L30" s="92"/>
+      <c r="M30" s="92"/>
+      <c r="N30" s="92"/>
+      <c r="O30" s="92"/>
+      <c r="P30" s="92"/>
+      <c r="Q30" s="92"/>
+      <c r="R30" s="92"/>
+      <c r="S30" s="92"/>
+      <c r="T30" s="92"/>
+      <c r="U30" s="92"/>
+      <c r="V30" s="92"/>
+      <c r="W30" s="92"/>
       <c r="X30"/>
       <c r="Y30"/>
       <c r="Z30"/>
@@ -3096,29 +3101,29 @@
       <c r="CN30"/>
     </row>
     <row r="31" spans="1:92" s="1" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="78"/>
-      <c r="B31" s="78"/>
-      <c r="C31" s="78"/>
-      <c r="D31" s="78"/>
-      <c r="E31" s="78"/>
-      <c r="F31" s="78"/>
-      <c r="G31" s="78"/>
-      <c r="H31" s="78"/>
-      <c r="I31" s="78"/>
-      <c r="J31" s="78"/>
-      <c r="K31" s="78"/>
-      <c r="L31" s="78"/>
-      <c r="M31" s="78"/>
-      <c r="N31" s="78"/>
-      <c r="O31" s="78"/>
-      <c r="P31" s="78"/>
-      <c r="Q31" s="78"/>
-      <c r="R31" s="78"/>
-      <c r="S31" s="78"/>
-      <c r="T31" s="78"/>
-      <c r="U31" s="78"/>
-      <c r="V31" s="78"/>
-      <c r="W31" s="78"/>
+      <c r="A31" s="92"/>
+      <c r="B31" s="92"/>
+      <c r="C31" s="92"/>
+      <c r="D31" s="92"/>
+      <c r="E31" s="92"/>
+      <c r="F31" s="92"/>
+      <c r="G31" s="92"/>
+      <c r="H31" s="92"/>
+      <c r="I31" s="92"/>
+      <c r="J31" s="92"/>
+      <c r="K31" s="92"/>
+      <c r="L31" s="92"/>
+      <c r="M31" s="92"/>
+      <c r="N31" s="92"/>
+      <c r="O31" s="92"/>
+      <c r="P31" s="92"/>
+      <c r="Q31" s="92"/>
+      <c r="R31" s="92"/>
+      <c r="S31" s="92"/>
+      <c r="T31" s="92"/>
+      <c r="U31" s="92"/>
+      <c r="V31" s="92"/>
+      <c r="W31" s="92"/>
       <c r="X31"/>
       <c r="Y31"/>
       <c r="Z31"/>
@@ -3190,29 +3195,29 @@
       <c r="CN31"/>
     </row>
     <row r="32" spans="1:92" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="78"/>
-      <c r="B32" s="78"/>
-      <c r="C32" s="78"/>
-      <c r="D32" s="78"/>
-      <c r="E32" s="78"/>
-      <c r="F32" s="78"/>
-      <c r="G32" s="78"/>
-      <c r="H32" s="78"/>
-      <c r="I32" s="78"/>
-      <c r="J32" s="78"/>
-      <c r="K32" s="78"/>
-      <c r="L32" s="78"/>
-      <c r="M32" s="78"/>
-      <c r="N32" s="78"/>
-      <c r="O32" s="78"/>
-      <c r="P32" s="78"/>
-      <c r="Q32" s="78"/>
-      <c r="R32" s="78"/>
-      <c r="S32" s="78"/>
-      <c r="T32" s="78"/>
-      <c r="U32" s="78"/>
-      <c r="V32" s="78"/>
-      <c r="W32" s="78"/>
+      <c r="A32" s="92"/>
+      <c r="B32" s="92"/>
+      <c r="C32" s="92"/>
+      <c r="D32" s="92"/>
+      <c r="E32" s="92"/>
+      <c r="F32" s="92"/>
+      <c r="G32" s="92"/>
+      <c r="H32" s="92"/>
+      <c r="I32" s="92"/>
+      <c r="J32" s="92"/>
+      <c r="K32" s="92"/>
+      <c r="L32" s="92"/>
+      <c r="M32" s="92"/>
+      <c r="N32" s="92"/>
+      <c r="O32" s="92"/>
+      <c r="P32" s="92"/>
+      <c r="Q32" s="92"/>
+      <c r="R32" s="92"/>
+      <c r="S32" s="92"/>
+      <c r="T32" s="92"/>
+      <c r="U32" s="92"/>
+      <c r="V32" s="92"/>
+      <c r="W32" s="92"/>
     </row>
     <row r="33" spans="1:23" ht="5.0999999999999996" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="10"/>
@@ -3247,64 +3252,64 @@
     </row>
     <row r="36" spans="1:23" ht="5.0999999999999996" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="37" spans="1:23" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="71" t="s">
+      <c r="A37" s="79" t="s">
         <v>30</v>
       </c>
-      <c r="B37" s="71"/>
-      <c r="C37" s="71"/>
-      <c r="D37" s="72"/>
-      <c r="E37" s="72"/>
-      <c r="F37" s="72"/>
-      <c r="G37" s="72"/>
-      <c r="I37" s="71" t="s">
+      <c r="B37" s="79"/>
+      <c r="C37" s="79"/>
+      <c r="D37" s="90"/>
+      <c r="E37" s="90"/>
+      <c r="F37" s="90"/>
+      <c r="G37" s="90"/>
+      <c r="I37" s="79" t="s">
         <v>19</v>
       </c>
-      <c r="J37" s="71"/>
-      <c r="K37" s="71"/>
-      <c r="L37" s="79"/>
-      <c r="M37" s="79"/>
-      <c r="N37" s="79"/>
-      <c r="Q37" s="71" t="s">
+      <c r="J37" s="79"/>
+      <c r="K37" s="79"/>
+      <c r="L37" s="93"/>
+      <c r="M37" s="93"/>
+      <c r="N37" s="93"/>
+      <c r="Q37" s="79" t="s">
         <v>24</v>
       </c>
-      <c r="R37" s="71"/>
-      <c r="S37" s="71"/>
-      <c r="T37" s="71"/>
-      <c r="U37" s="80"/>
-      <c r="V37" s="80"/>
-      <c r="W37" s="80"/>
+      <c r="R37" s="79"/>
+      <c r="S37" s="79"/>
+      <c r="T37" s="79"/>
+      <c r="U37" s="94"/>
+      <c r="V37" s="94"/>
+      <c r="W37" s="94"/>
     </row>
     <row r="38" spans="1:23" ht="5.0999999999999996" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="39" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="77" t="s">
+      <c r="A39" s="87" t="s">
         <v>3</v>
       </c>
-      <c r="B39" s="77"/>
-      <c r="C39" s="77"/>
-      <c r="D39" s="77"/>
-      <c r="E39" s="77"/>
-      <c r="F39" s="77"/>
-      <c r="G39" s="77"/>
-      <c r="H39" s="77"/>
-      <c r="I39" s="77" t="s">
+      <c r="B39" s="87"/>
+      <c r="C39" s="87"/>
+      <c r="D39" s="87"/>
+      <c r="E39" s="87"/>
+      <c r="F39" s="87"/>
+      <c r="G39" s="87"/>
+      <c r="H39" s="87"/>
+      <c r="I39" s="87" t="s">
         <v>52</v>
       </c>
-      <c r="J39" s="77"/>
-      <c r="K39" s="77"/>
-      <c r="L39" s="77"/>
-      <c r="M39" s="77"/>
-      <c r="N39" s="77"/>
-      <c r="O39" s="77"/>
-      <c r="P39" s="77"/>
-      <c r="Q39" s="77" t="s">
+      <c r="J39" s="87"/>
+      <c r="K39" s="87"/>
+      <c r="L39" s="87"/>
+      <c r="M39" s="87"/>
+      <c r="N39" s="87"/>
+      <c r="O39" s="87"/>
+      <c r="P39" s="87"/>
+      <c r="Q39" s="87" t="s">
         <v>4</v>
       </c>
-      <c r="R39" s="77"/>
-      <c r="S39" s="77"/>
-      <c r="T39" s="77"/>
-      <c r="U39" s="77"/>
-      <c r="V39" s="77"/>
-      <c r="W39" s="77"/>
+      <c r="R39" s="87"/>
+      <c r="S39" s="87"/>
+      <c r="T39" s="87"/>
+      <c r="U39" s="87"/>
+      <c r="V39" s="87"/>
+      <c r="W39" s="87"/>
     </row>
     <row r="40" spans="1:23" ht="5.0999999999999996" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="41" spans="1:23" ht="5.0999999999999996" customHeight="1" x14ac:dyDescent="0.3">
@@ -3333,30 +3338,30 @@
     </row>
     <row r="42" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B42" s="15"/>
-      <c r="C42" s="81" t="s">
+      <c r="C42" s="88" t="s">
         <v>15</v>
       </c>
-      <c r="D42" s="82"/>
-      <c r="E42" s="82"/>
-      <c r="F42" s="82"/>
-      <c r="G42" s="82"/>
+      <c r="D42" s="89"/>
+      <c r="E42" s="89"/>
+      <c r="F42" s="89"/>
+      <c r="G42" s="89"/>
       <c r="I42" s="16"/>
       <c r="J42" s="15"/>
-      <c r="K42" s="83" t="s">
+      <c r="K42" s="71" t="s">
         <v>6</v>
       </c>
-      <c r="L42" s="84"/>
-      <c r="M42" s="84"/>
-      <c r="N42" s="84"/>
-      <c r="O42" s="84"/>
+      <c r="L42" s="72"/>
+      <c r="M42" s="72"/>
+      <c r="N42" s="72"/>
+      <c r="O42" s="72"/>
       <c r="Q42" s="16"/>
       <c r="R42" s="15"/>
-      <c r="S42" s="85" t="s">
+      <c r="S42" s="73" t="s">
         <v>9</v>
       </c>
-      <c r="T42" s="86"/>
-      <c r="U42" s="86"/>
-      <c r="V42" s="86"/>
+      <c r="T42" s="74"/>
+      <c r="U42" s="74"/>
+      <c r="V42" s="74"/>
     </row>
     <row r="43" spans="1:23" ht="5.0999999999999996" customHeight="1" x14ac:dyDescent="0.3">
       <c r="I43" s="16"/>
@@ -3373,21 +3378,21 @@
       <c r="G44" s="8"/>
       <c r="I44" s="16"/>
       <c r="J44" s="15"/>
-      <c r="K44" s="83" t="s">
+      <c r="K44" s="71" t="s">
         <v>8</v>
       </c>
-      <c r="L44" s="84"/>
-      <c r="M44" s="84"/>
-      <c r="N44" s="84"/>
-      <c r="O44" s="84"/>
+      <c r="L44" s="72"/>
+      <c r="M44" s="72"/>
+      <c r="N44" s="72"/>
+      <c r="O44" s="72"/>
       <c r="Q44" s="16"/>
       <c r="R44" s="15"/>
-      <c r="S44" s="85" t="s">
+      <c r="S44" s="73" t="s">
         <v>10</v>
       </c>
-      <c r="T44" s="86"/>
-      <c r="U44" s="86"/>
-      <c r="V44" s="86"/>
+      <c r="T44" s="74"/>
+      <c r="U44" s="74"/>
+      <c r="V44" s="74"/>
     </row>
     <row r="45" spans="1:23" ht="5.0999999999999996" customHeight="1" x14ac:dyDescent="0.3">
       <c r="I45" s="16"/>
@@ -3396,21 +3401,21 @@
     <row r="46" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="I46" s="16"/>
       <c r="J46" s="15"/>
-      <c r="K46" s="83" t="s">
+      <c r="K46" s="71" t="s">
         <v>5</v>
       </c>
-      <c r="L46" s="84"/>
-      <c r="M46" s="84"/>
-      <c r="N46" s="84"/>
-      <c r="O46" s="84"/>
+      <c r="L46" s="72"/>
+      <c r="M46" s="72"/>
+      <c r="N46" s="72"/>
+      <c r="O46" s="72"/>
       <c r="Q46" s="16"/>
       <c r="R46" s="15"/>
-      <c r="S46" s="85" t="s">
+      <c r="S46" s="73" t="s">
         <v>11</v>
       </c>
-      <c r="T46" s="86"/>
-      <c r="U46" s="86"/>
-      <c r="V46" s="86"/>
+      <c r="T46" s="74"/>
+      <c r="U46" s="74"/>
+      <c r="V46" s="74"/>
     </row>
     <row r="47" spans="1:23" ht="5.0999999999999996" customHeight="1" x14ac:dyDescent="0.3">
       <c r="I47" s="16"/>
@@ -3419,22 +3424,22 @@
     <row r="48" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="I48" s="16"/>
       <c r="J48" s="15"/>
-      <c r="K48" s="83" t="s">
+      <c r="K48" s="71" t="s">
         <v>7</v>
       </c>
-      <c r="L48" s="84"/>
-      <c r="M48" s="84"/>
-      <c r="N48" s="84"/>
-      <c r="O48" s="84"/>
+      <c r="L48" s="72"/>
+      <c r="M48" s="72"/>
+      <c r="N48" s="72"/>
+      <c r="O48" s="72"/>
       <c r="Q48" s="16"/>
       <c r="R48" s="15"/>
-      <c r="S48" s="85" t="s">
+      <c r="S48" s="73" t="s">
         <v>34</v>
       </c>
-      <c r="T48" s="86"/>
-      <c r="U48" s="86"/>
-      <c r="V48" s="86"/>
-      <c r="W48" s="86"/>
+      <c r="T48" s="74"/>
+      <c r="U48" s="74"/>
+      <c r="V48" s="74"/>
+      <c r="W48" s="74"/>
     </row>
     <row r="49" spans="1:23" ht="5.0999999999999996" customHeight="1" x14ac:dyDescent="0.3">
       <c r="I49" s="16"/>
@@ -3443,20 +3448,20 @@
     <row r="50" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="I50" s="16"/>
       <c r="J50" s="15"/>
-      <c r="K50" s="83" t="s">
+      <c r="K50" s="71" t="s">
         <v>17</v>
       </c>
-      <c r="L50" s="84"/>
-      <c r="M50" s="84"/>
-      <c r="N50" s="84"/>
-      <c r="O50" s="84"/>
+      <c r="L50" s="72"/>
+      <c r="M50" s="72"/>
+      <c r="N50" s="72"/>
+      <c r="O50" s="72"/>
       <c r="Q50" s="16"/>
       <c r="R50" s="15"/>
-      <c r="S50" s="85" t="s">
+      <c r="S50" s="73" t="s">
         <v>12</v>
       </c>
-      <c r="T50" s="86"/>
-      <c r="U50" s="86"/>
+      <c r="T50" s="74"/>
+      <c r="U50" s="74"/>
     </row>
     <row r="51" spans="1:23" ht="5.0999999999999996" customHeight="1" x14ac:dyDescent="0.3">
       <c r="I51" s="16"/>
@@ -3464,12 +3469,12 @@
     </row>
     <row r="52" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="I52" s="16"/>
-      <c r="J52" s="98"/>
-      <c r="K52" s="98"/>
-      <c r="L52" s="98"/>
-      <c r="M52" s="98"/>
-      <c r="N52" s="98"/>
-      <c r="O52" s="98"/>
+      <c r="J52" s="75"/>
+      <c r="K52" s="75"/>
+      <c r="L52" s="75"/>
+      <c r="M52" s="75"/>
+      <c r="N52" s="75"/>
+      <c r="O52" s="75"/>
       <c r="Q52" s="16"/>
       <c r="R52" s="15"/>
       <c r="S52" s="21" t="s">
@@ -3484,11 +3489,11 @@
     <row r="54" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="Q54" s="16"/>
       <c r="R54" s="15"/>
-      <c r="S54" s="85" t="s">
+      <c r="S54" s="73" t="s">
         <v>14</v>
       </c>
-      <c r="T54" s="86"/>
-      <c r="U54" s="86"/>
+      <c r="T54" s="74"/>
+      <c r="U54" s="74"/>
     </row>
     <row r="55" spans="1:23" ht="5.0999999999999996" customHeight="1" x14ac:dyDescent="0.3">
       <c r="Q55" s="16"/>
@@ -3496,24 +3501,24 @@
     <row r="56" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="Q56" s="16"/>
       <c r="R56" s="15"/>
-      <c r="S56" s="83" t="s">
+      <c r="S56" s="71" t="s">
         <v>17</v>
       </c>
-      <c r="T56" s="84"/>
-      <c r="U56" s="84"/>
-      <c r="V56" s="84"/>
+      <c r="T56" s="72"/>
+      <c r="U56" s="72"/>
+      <c r="V56" s="72"/>
     </row>
     <row r="57" spans="1:23" ht="5.0999999999999996" customHeight="1" x14ac:dyDescent="0.3">
       <c r="Q57" s="16"/>
     </row>
     <row r="58" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="Q58" s="16"/>
-      <c r="R58" s="98"/>
-      <c r="S58" s="98"/>
-      <c r="T58" s="98"/>
-      <c r="U58" s="98"/>
-      <c r="V58" s="98"/>
-      <c r="W58" s="98"/>
+      <c r="R58" s="75"/>
+      <c r="S58" s="75"/>
+      <c r="T58" s="75"/>
+      <c r="U58" s="75"/>
+      <c r="V58" s="75"/>
+      <c r="W58" s="75"/>
     </row>
     <row r="59" spans="1:23" ht="5.0999999999999996" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="60" spans="1:23" ht="5.0999999999999996" customHeight="1" x14ac:dyDescent="0.3">
@@ -3543,24 +3548,24 @@
     </row>
     <row r="61" spans="1:23" ht="5.0999999999999996" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="62" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A62" s="76" t="s">
+      <c r="A62" s="69" t="s">
         <v>38</v>
       </c>
-      <c r="B62" s="76"/>
-      <c r="C62" s="76"/>
-      <c r="D62" s="76"/>
-      <c r="E62" s="76"/>
+      <c r="B62" s="69"/>
+      <c r="C62" s="69"/>
+      <c r="D62" s="69"/>
+      <c r="E62" s="69"/>
       <c r="F62" s="18"/>
     </row>
     <row r="63" spans="1:23" ht="5.0999999999999996" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="64" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A64" s="76" t="s">
+      <c r="A64" s="69" t="s">
         <v>53</v>
       </c>
-      <c r="B64" s="76"/>
-      <c r="C64" s="76"/>
-      <c r="D64" s="76"/>
-      <c r="E64" s="76"/>
+      <c r="B64" s="69"/>
+      <c r="C64" s="69"/>
+      <c r="D64" s="69"/>
+      <c r="E64" s="69"/>
       <c r="F64" s="18"/>
     </row>
     <row r="65" spans="1:23" ht="5.0999999999999996" customHeight="1" x14ac:dyDescent="0.3">
@@ -3573,45 +3578,45 @@
     </row>
     <row r="66" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B66" s="15"/>
-      <c r="C66" s="89" t="s">
+      <c r="C66" s="70" t="s">
         <v>54</v>
       </c>
-      <c r="D66" s="76"/>
-      <c r="E66" s="76"/>
-      <c r="F66" s="76"/>
-      <c r="G66" s="76"/>
+      <c r="D66" s="69"/>
+      <c r="E66" s="69"/>
+      <c r="F66" s="69"/>
+      <c r="G66" s="69"/>
     </row>
     <row r="67" spans="1:23" ht="5.0999999999999996" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="68" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C68" s="20" t="s">
         <v>31</v>
       </c>
-      <c r="D68" s="96"/>
-      <c r="E68" s="96"/>
-      <c r="F68" s="96"/>
-      <c r="G68" s="96"/>
-      <c r="H68" s="71" t="s">
+      <c r="D68" s="85"/>
+      <c r="E68" s="85"/>
+      <c r="F68" s="85"/>
+      <c r="G68" s="85"/>
+      <c r="H68" s="79" t="s">
         <v>33</v>
       </c>
-      <c r="I68" s="71"/>
-      <c r="J68" s="71"/>
-      <c r="K68" s="95"/>
-      <c r="L68" s="95"/>
+      <c r="I68" s="79"/>
+      <c r="J68" s="79"/>
+      <c r="K68" s="84"/>
+      <c r="L68" s="84"/>
       <c r="M68" s="24" t="s">
         <v>50</v>
       </c>
       <c r="N68" s="27"/>
       <c r="P68" s="15"/>
-      <c r="Q68" s="89" t="s">
+      <c r="Q68" s="70" t="s">
         <v>1</v>
       </c>
-      <c r="R68" s="76"/>
-      <c r="S68" s="76"/>
+      <c r="R68" s="69"/>
+      <c r="S68" s="69"/>
       <c r="U68" s="15"/>
-      <c r="V68" s="89" t="s">
+      <c r="V68" s="70" t="s">
         <v>2</v>
       </c>
-      <c r="W68" s="76"/>
+      <c r="W68" s="69"/>
     </row>
     <row r="69" spans="1:23" ht="5.0999999999999996" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C69" s="12"/>
@@ -3620,8 +3625,8 @@
       <c r="C70" s="20" t="s">
         <v>32</v>
       </c>
-      <c r="D70" s="97"/>
-      <c r="E70" s="97"/>
+      <c r="D70" s="86"/>
+      <c r="E70" s="86"/>
       <c r="F70" s="3" t="s">
         <v>50</v>
       </c>
@@ -3631,193 +3636,193 @@
       <c r="N70" s="4"/>
       <c r="O70" s="4"/>
       <c r="P70" s="15"/>
-      <c r="Q70" s="90" t="s">
+      <c r="Q70" s="78" t="s">
         <v>36</v>
       </c>
-      <c r="R70" s="90"/>
-      <c r="S70" s="90"/>
-      <c r="T70" s="90"/>
-      <c r="U70" s="90"/>
-      <c r="V70" s="90"/>
-      <c r="W70" s="90"/>
+      <c r="R70" s="78"/>
+      <c r="S70" s="78"/>
+      <c r="T70" s="78"/>
+      <c r="U70" s="78"/>
+      <c r="V70" s="78"/>
+      <c r="W70" s="78"/>
     </row>
     <row r="71" spans="1:23" ht="5.0999999999999996" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="Q71" s="90"/>
-      <c r="R71" s="90"/>
-      <c r="S71" s="90"/>
-      <c r="T71" s="90"/>
-      <c r="U71" s="90"/>
-      <c r="V71" s="90"/>
-      <c r="W71" s="90"/>
+      <c r="Q71" s="78"/>
+      <c r="R71" s="78"/>
+      <c r="S71" s="78"/>
+      <c r="T71" s="78"/>
+      <c r="U71" s="78"/>
+      <c r="V71" s="78"/>
+      <c r="W71" s="78"/>
     </row>
     <row r="72" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B72" s="15"/>
-      <c r="C72" s="89" t="s">
+      <c r="C72" s="70" t="s">
         <v>20</v>
       </c>
-      <c r="D72" s="76"/>
-      <c r="E72" s="76"/>
+      <c r="D72" s="69"/>
+      <c r="E72" s="69"/>
       <c r="F72" s="18"/>
-      <c r="Q72" s="90"/>
-      <c r="R72" s="90"/>
-      <c r="S72" s="90"/>
-      <c r="T72" s="90"/>
-      <c r="U72" s="90"/>
-      <c r="V72" s="90"/>
-      <c r="W72" s="90"/>
+      <c r="Q72" s="78"/>
+      <c r="R72" s="78"/>
+      <c r="S72" s="78"/>
+      <c r="T72" s="78"/>
+      <c r="U72" s="78"/>
+      <c r="V72" s="78"/>
+      <c r="W72" s="78"/>
     </row>
     <row r="73" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B73" s="94" t="s">
+      <c r="B73" s="83" t="s">
         <v>44</v>
       </c>
-      <c r="C73" s="94"/>
-      <c r="D73" s="94"/>
-      <c r="E73" s="94"/>
-      <c r="F73" s="94"/>
-      <c r="G73" s="94"/>
-      <c r="H73" s="94"/>
-      <c r="I73" s="94"/>
-      <c r="J73" s="94"/>
-      <c r="K73" s="94"/>
-      <c r="L73" s="94"/>
-      <c r="M73" s="94"/>
-      <c r="N73" s="94"/>
-      <c r="O73" s="94"/>
-      <c r="Q73" s="90"/>
-      <c r="R73" s="90"/>
-      <c r="S73" s="90"/>
-      <c r="T73" s="90"/>
-      <c r="U73" s="90"/>
-      <c r="V73" s="90"/>
-      <c r="W73" s="90"/>
+      <c r="C73" s="83"/>
+      <c r="D73" s="83"/>
+      <c r="E73" s="83"/>
+      <c r="F73" s="83"/>
+      <c r="G73" s="83"/>
+      <c r="H73" s="83"/>
+      <c r="I73" s="83"/>
+      <c r="J73" s="83"/>
+      <c r="K73" s="83"/>
+      <c r="L73" s="83"/>
+      <c r="M73" s="83"/>
+      <c r="N73" s="83"/>
+      <c r="O73" s="83"/>
+      <c r="Q73" s="78"/>
+      <c r="R73" s="78"/>
+      <c r="S73" s="78"/>
+      <c r="T73" s="78"/>
+      <c r="U73" s="78"/>
+      <c r="V73" s="78"/>
+      <c r="W73" s="78"/>
     </row>
     <row r="74" spans="1:23" ht="5.0999999999999996" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="75" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A75" s="90" t="s">
+      <c r="A75" s="78" t="s">
         <v>45</v>
       </c>
-      <c r="B75" s="90"/>
-      <c r="C75" s="90"/>
-      <c r="D75" s="90"/>
-      <c r="E75" s="90"/>
-      <c r="F75" s="90"/>
-      <c r="G75" s="90"/>
-      <c r="H75" s="90"/>
-      <c r="I75" s="90"/>
-      <c r="J75" s="90"/>
-      <c r="K75" s="90"/>
-      <c r="L75" s="90"/>
-      <c r="M75" s="90"/>
-      <c r="N75" s="90"/>
-      <c r="O75" s="90"/>
-      <c r="P75" s="90"/>
-      <c r="Q75" s="90"/>
-      <c r="R75" s="90"/>
-      <c r="S75" s="90"/>
-      <c r="T75" s="90"/>
-      <c r="U75" s="90"/>
-      <c r="V75" s="90"/>
-      <c r="W75" s="90"/>
+      <c r="B75" s="78"/>
+      <c r="C75" s="78"/>
+      <c r="D75" s="78"/>
+      <c r="E75" s="78"/>
+      <c r="F75" s="78"/>
+      <c r="G75" s="78"/>
+      <c r="H75" s="78"/>
+      <c r="I75" s="78"/>
+      <c r="J75" s="78"/>
+      <c r="K75" s="78"/>
+      <c r="L75" s="78"/>
+      <c r="M75" s="78"/>
+      <c r="N75" s="78"/>
+      <c r="O75" s="78"/>
+      <c r="P75" s="78"/>
+      <c r="Q75" s="78"/>
+      <c r="R75" s="78"/>
+      <c r="S75" s="78"/>
+      <c r="T75" s="78"/>
+      <c r="U75" s="78"/>
+      <c r="V75" s="78"/>
+      <c r="W75" s="78"/>
     </row>
     <row r="76" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A76" s="90"/>
-      <c r="B76" s="90"/>
-      <c r="C76" s="90"/>
-      <c r="D76" s="90"/>
-      <c r="E76" s="90"/>
-      <c r="F76" s="90"/>
-      <c r="G76" s="90"/>
-      <c r="H76" s="90"/>
-      <c r="I76" s="90"/>
-      <c r="J76" s="90"/>
-      <c r="K76" s="90"/>
-      <c r="L76" s="90"/>
-      <c r="M76" s="90"/>
-      <c r="N76" s="90"/>
-      <c r="O76" s="90"/>
-      <c r="P76" s="90"/>
-      <c r="Q76" s="90"/>
-      <c r="R76" s="90"/>
-      <c r="S76" s="90"/>
-      <c r="T76" s="90"/>
-      <c r="U76" s="90"/>
-      <c r="V76" s="90"/>
-      <c r="W76" s="90"/>
+      <c r="A76" s="78"/>
+      <c r="B76" s="78"/>
+      <c r="C76" s="78"/>
+      <c r="D76" s="78"/>
+      <c r="E76" s="78"/>
+      <c r="F76" s="78"/>
+      <c r="G76" s="78"/>
+      <c r="H76" s="78"/>
+      <c r="I76" s="78"/>
+      <c r="J76" s="78"/>
+      <c r="K76" s="78"/>
+      <c r="L76" s="78"/>
+      <c r="M76" s="78"/>
+      <c r="N76" s="78"/>
+      <c r="O76" s="78"/>
+      <c r="P76" s="78"/>
+      <c r="Q76" s="78"/>
+      <c r="R76" s="78"/>
+      <c r="S76" s="78"/>
+      <c r="T76" s="78"/>
+      <c r="U76" s="78"/>
+      <c r="V76" s="78"/>
+      <c r="W76" s="78"/>
     </row>
     <row r="77" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A77" s="90"/>
-      <c r="B77" s="90"/>
-      <c r="C77" s="90"/>
-      <c r="D77" s="90"/>
-      <c r="E77" s="90"/>
-      <c r="F77" s="90"/>
-      <c r="G77" s="90"/>
-      <c r="H77" s="90"/>
-      <c r="I77" s="90"/>
-      <c r="J77" s="90"/>
-      <c r="K77" s="90"/>
-      <c r="L77" s="90"/>
-      <c r="M77" s="90"/>
-      <c r="N77" s="90"/>
-      <c r="O77" s="90"/>
-      <c r="P77" s="90"/>
-      <c r="Q77" s="90"/>
-      <c r="R77" s="90"/>
-      <c r="S77" s="90"/>
-      <c r="T77" s="90"/>
-      <c r="U77" s="90"/>
-      <c r="V77" s="90"/>
-      <c r="W77" s="90"/>
+      <c r="A77" s="78"/>
+      <c r="B77" s="78"/>
+      <c r="C77" s="78"/>
+      <c r="D77" s="78"/>
+      <c r="E77" s="78"/>
+      <c r="F77" s="78"/>
+      <c r="G77" s="78"/>
+      <c r="H77" s="78"/>
+      <c r="I77" s="78"/>
+      <c r="J77" s="78"/>
+      <c r="K77" s="78"/>
+      <c r="L77" s="78"/>
+      <c r="M77" s="78"/>
+      <c r="N77" s="78"/>
+      <c r="O77" s="78"/>
+      <c r="P77" s="78"/>
+      <c r="Q77" s="78"/>
+      <c r="R77" s="78"/>
+      <c r="S77" s="78"/>
+      <c r="T77" s="78"/>
+      <c r="U77" s="78"/>
+      <c r="V77" s="78"/>
+      <c r="W77" s="78"/>
     </row>
     <row r="78" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A78" s="90"/>
-      <c r="B78" s="90"/>
-      <c r="C78" s="90"/>
-      <c r="D78" s="90"/>
-      <c r="E78" s="90"/>
-      <c r="F78" s="90"/>
-      <c r="G78" s="90"/>
-      <c r="H78" s="90"/>
-      <c r="I78" s="90"/>
-      <c r="J78" s="90"/>
-      <c r="K78" s="90"/>
-      <c r="L78" s="90"/>
-      <c r="M78" s="90"/>
-      <c r="N78" s="90"/>
-      <c r="O78" s="90"/>
-      <c r="P78" s="90"/>
-      <c r="Q78" s="90"/>
-      <c r="R78" s="90"/>
-      <c r="S78" s="90"/>
-      <c r="T78" s="90"/>
-      <c r="U78" s="90"/>
-      <c r="V78" s="90"/>
-      <c r="W78" s="90"/>
+      <c r="A78" s="78"/>
+      <c r="B78" s="78"/>
+      <c r="C78" s="78"/>
+      <c r="D78" s="78"/>
+      <c r="E78" s="78"/>
+      <c r="F78" s="78"/>
+      <c r="G78" s="78"/>
+      <c r="H78" s="78"/>
+      <c r="I78" s="78"/>
+      <c r="J78" s="78"/>
+      <c r="K78" s="78"/>
+      <c r="L78" s="78"/>
+      <c r="M78" s="78"/>
+      <c r="N78" s="78"/>
+      <c r="O78" s="78"/>
+      <c r="P78" s="78"/>
+      <c r="Q78" s="78"/>
+      <c r="R78" s="78"/>
+      <c r="S78" s="78"/>
+      <c r="T78" s="78"/>
+      <c r="U78" s="78"/>
+      <c r="V78" s="78"/>
+      <c r="W78" s="78"/>
     </row>
     <row r="79" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A79" s="90"/>
-      <c r="B79" s="90"/>
-      <c r="C79" s="90"/>
-      <c r="D79" s="90"/>
-      <c r="E79" s="90"/>
-      <c r="F79" s="90"/>
-      <c r="G79" s="90"/>
-      <c r="H79" s="90"/>
-      <c r="I79" s="90"/>
-      <c r="J79" s="90"/>
-      <c r="K79" s="90"/>
-      <c r="L79" s="90"/>
-      <c r="M79" s="90"/>
-      <c r="N79" s="90"/>
-      <c r="O79" s="90"/>
-      <c r="P79" s="90"/>
-      <c r="Q79" s="90"/>
-      <c r="R79" s="90"/>
-      <c r="S79" s="90"/>
-      <c r="T79" s="90"/>
-      <c r="U79" s="90"/>
-      <c r="V79" s="90"/>
-      <c r="W79" s="90"/>
+      <c r="A79" s="78"/>
+      <c r="B79" s="78"/>
+      <c r="C79" s="78"/>
+      <c r="D79" s="78"/>
+      <c r="E79" s="78"/>
+      <c r="F79" s="78"/>
+      <c r="G79" s="78"/>
+      <c r="H79" s="78"/>
+      <c r="I79" s="78"/>
+      <c r="J79" s="78"/>
+      <c r="K79" s="78"/>
+      <c r="L79" s="78"/>
+      <c r="M79" s="78"/>
+      <c r="N79" s="78"/>
+      <c r="O79" s="78"/>
+      <c r="P79" s="78"/>
+      <c r="Q79" s="78"/>
+      <c r="R79" s="78"/>
+      <c r="S79" s="78"/>
+      <c r="T79" s="78"/>
+      <c r="U79" s="78"/>
+      <c r="V79" s="78"/>
+      <c r="W79" s="78"/>
     </row>
     <row r="80" spans="1:23" ht="5.0999999999999996" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="81" spans="1:92" ht="30" customHeight="1" x14ac:dyDescent="0.3">
@@ -3826,16 +3831,16 @@
       <c r="F81" s="23"/>
       <c r="G81" s="23"/>
       <c r="H81" s="23"/>
-      <c r="I81" s="93">
+      <c r="I81" s="82">
         <f ca="1">TODAY()</f>
-        <v>46155</v>
-      </c>
-      <c r="J81" s="93"/>
-      <c r="K81" s="93"/>
-      <c r="L81" s="93"/>
-      <c r="M81" s="93"/>
-      <c r="N81" s="93"/>
-      <c r="O81" s="93"/>
+        <v>46156</v>
+      </c>
+      <c r="J81" s="82"/>
+      <c r="K81" s="82"/>
+      <c r="L81" s="82"/>
+      <c r="M81" s="82"/>
+      <c r="N81" s="82"/>
+      <c r="O81" s="82"/>
     </row>
     <row r="82" spans="1:92" ht="5.0999999999999996" customHeight="1" x14ac:dyDescent="0.3">
       <c r="G82"/>
@@ -3852,52 +3857,52 @@
       <c r="R82" s="17"/>
     </row>
     <row r="83" spans="1:92" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A83" s="88"/>
-      <c r="B83" s="88"/>
-      <c r="C83" s="88"/>
-      <c r="D83" s="88"/>
-      <c r="E83" s="88"/>
-      <c r="F83" s="88"/>
-      <c r="G83" s="88"/>
-      <c r="H83" s="88"/>
-      <c r="I83" s="88"/>
-      <c r="J83" s="88"/>
-      <c r="K83" s="88"/>
-      <c r="L83" s="88"/>
-      <c r="M83" s="88"/>
-      <c r="N83" s="88"/>
-      <c r="O83" s="88"/>
-      <c r="P83" s="88"/>
-      <c r="Q83" s="88"/>
+      <c r="A83" s="77"/>
+      <c r="B83" s="77"/>
+      <c r="C83" s="77"/>
+      <c r="D83" s="77"/>
+      <c r="E83" s="77"/>
+      <c r="F83" s="77"/>
+      <c r="G83" s="77"/>
+      <c r="H83" s="77"/>
+      <c r="I83" s="77"/>
+      <c r="J83" s="77"/>
+      <c r="K83" s="77"/>
+      <c r="L83" s="77"/>
+      <c r="M83" s="77"/>
+      <c r="N83" s="77"/>
+      <c r="O83" s="77"/>
+      <c r="P83" s="77"/>
+      <c r="Q83" s="77"/>
       <c r="R83"/>
-      <c r="S83" s="91" t="s">
+      <c r="S83" s="80" t="s">
         <v>51</v>
       </c>
-      <c r="T83" s="87"/>
-      <c r="U83" s="92"/>
-      <c r="V83" s="92"/>
-      <c r="W83" s="92"/>
+      <c r="T83" s="76"/>
+      <c r="U83" s="81"/>
+      <c r="V83" s="81"/>
+      <c r="W83" s="81"/>
     </row>
     <row r="84" spans="1:92" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A84" s="87" t="s">
+      <c r="A84" s="76" t="s">
         <v>35</v>
       </c>
-      <c r="B84" s="87"/>
-      <c r="C84" s="87"/>
-      <c r="D84" s="87"/>
-      <c r="E84" s="87"/>
-      <c r="F84" s="87"/>
-      <c r="G84" s="87"/>
-      <c r="H84" s="87"/>
-      <c r="I84" s="87"/>
-      <c r="J84" s="87"/>
-      <c r="K84" s="87"/>
-      <c r="L84" s="87"/>
-      <c r="M84" s="87"/>
-      <c r="N84" s="87"/>
-      <c r="O84" s="87"/>
-      <c r="P84" s="87"/>
-      <c r="Q84" s="87"/>
+      <c r="B84" s="76"/>
+      <c r="C84" s="76"/>
+      <c r="D84" s="76"/>
+      <c r="E84" s="76"/>
+      <c r="F84" s="76"/>
+      <c r="G84" s="76"/>
+      <c r="H84" s="76"/>
+      <c r="I84" s="76"/>
+      <c r="J84" s="76"/>
+      <c r="K84" s="76"/>
+      <c r="L84" s="76"/>
+      <c r="M84" s="76"/>
+      <c r="N84" s="76"/>
+      <c r="O84" s="76"/>
+      <c r="P84" s="76"/>
+      <c r="Q84" s="76"/>
       <c r="R84" s="13"/>
       <c r="S84" s="13"/>
       <c r="T84" s="13"/>
@@ -3976,42 +3981,19 @@
     </row>
   </sheetData>
   <mergeCells count="65">
-    <mergeCell ref="A62:E62"/>
-    <mergeCell ref="A64:E64"/>
-    <mergeCell ref="C66:G66"/>
-    <mergeCell ref="K50:O50"/>
-    <mergeCell ref="S50:U50"/>
-    <mergeCell ref="J52:O52"/>
-    <mergeCell ref="S54:U54"/>
-    <mergeCell ref="S56:V56"/>
-    <mergeCell ref="R58:W58"/>
-    <mergeCell ref="A84:Q84"/>
-    <mergeCell ref="A83:Q83"/>
-    <mergeCell ref="Q68:S68"/>
-    <mergeCell ref="V68:W68"/>
-    <mergeCell ref="Q70:W73"/>
-    <mergeCell ref="C72:E72"/>
-    <mergeCell ref="H68:J68"/>
-    <mergeCell ref="S83:T83"/>
-    <mergeCell ref="U83:W83"/>
-    <mergeCell ref="I81:O81"/>
-    <mergeCell ref="A75:W79"/>
-    <mergeCell ref="B73:O73"/>
-    <mergeCell ref="K68:L68"/>
-    <mergeCell ref="D68:G68"/>
-    <mergeCell ref="D70:E70"/>
-    <mergeCell ref="K44:O44"/>
-    <mergeCell ref="S44:V44"/>
-    <mergeCell ref="K46:O46"/>
-    <mergeCell ref="S46:V46"/>
-    <mergeCell ref="K48:O48"/>
-    <mergeCell ref="S48:W48"/>
-    <mergeCell ref="A39:H39"/>
-    <mergeCell ref="I39:P39"/>
-    <mergeCell ref="Q39:W39"/>
-    <mergeCell ref="C42:G42"/>
-    <mergeCell ref="K42:O42"/>
-    <mergeCell ref="S42:V42"/>
+    <mergeCell ref="A11:C11"/>
+    <mergeCell ref="D11:W11"/>
+    <mergeCell ref="A13:C13"/>
+    <mergeCell ref="D13:W13"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="G1:R3"/>
+    <mergeCell ref="A2:E2"/>
+    <mergeCell ref="B5:W5"/>
+    <mergeCell ref="A7:E7"/>
+    <mergeCell ref="A9:C9"/>
+    <mergeCell ref="D9:E9"/>
+    <mergeCell ref="T9:V9"/>
+    <mergeCell ref="J9:K9"/>
     <mergeCell ref="T15:W15"/>
     <mergeCell ref="B17:W17"/>
     <mergeCell ref="A19:E19"/>
@@ -4028,19 +4010,42 @@
     <mergeCell ref="K15:L15"/>
     <mergeCell ref="N15:P15"/>
     <mergeCell ref="Q15:S15"/>
-    <mergeCell ref="A11:C11"/>
-    <mergeCell ref="D11:W11"/>
-    <mergeCell ref="A13:C13"/>
-    <mergeCell ref="D13:W13"/>
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="G1:R3"/>
-    <mergeCell ref="A2:E2"/>
-    <mergeCell ref="B5:W5"/>
-    <mergeCell ref="A7:E7"/>
-    <mergeCell ref="A9:C9"/>
-    <mergeCell ref="D9:E9"/>
-    <mergeCell ref="T9:V9"/>
-    <mergeCell ref="J9:K9"/>
+    <mergeCell ref="A39:H39"/>
+    <mergeCell ref="I39:P39"/>
+    <mergeCell ref="Q39:W39"/>
+    <mergeCell ref="C42:G42"/>
+    <mergeCell ref="K42:O42"/>
+    <mergeCell ref="S42:V42"/>
+    <mergeCell ref="K44:O44"/>
+    <mergeCell ref="S44:V44"/>
+    <mergeCell ref="K46:O46"/>
+    <mergeCell ref="S46:V46"/>
+    <mergeCell ref="K48:O48"/>
+    <mergeCell ref="S48:W48"/>
+    <mergeCell ref="A84:Q84"/>
+    <mergeCell ref="A83:Q83"/>
+    <mergeCell ref="Q68:S68"/>
+    <mergeCell ref="V68:W68"/>
+    <mergeCell ref="Q70:W73"/>
+    <mergeCell ref="C72:E72"/>
+    <mergeCell ref="H68:J68"/>
+    <mergeCell ref="S83:T83"/>
+    <mergeCell ref="U83:W83"/>
+    <mergeCell ref="I81:O81"/>
+    <mergeCell ref="A75:W79"/>
+    <mergeCell ref="B73:O73"/>
+    <mergeCell ref="K68:L68"/>
+    <mergeCell ref="D68:G68"/>
+    <mergeCell ref="D70:E70"/>
+    <mergeCell ref="A62:E62"/>
+    <mergeCell ref="A64:E64"/>
+    <mergeCell ref="C66:G66"/>
+    <mergeCell ref="K50:O50"/>
+    <mergeCell ref="S50:U50"/>
+    <mergeCell ref="J52:O52"/>
+    <mergeCell ref="S54:U54"/>
+    <mergeCell ref="S56:V56"/>
+    <mergeCell ref="R58:W58"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.19685039370078741" right="0.19685039370078741" top="0.39370078740157483" bottom="0.39370078740157483" header="0" footer="0"/>
@@ -4091,26 +4096,26 @@
       <c r="F1" s="29"/>
       <c r="G1" s="29"/>
       <c r="H1" s="29"/>
-      <c r="I1" s="105" t="s">
+      <c r="I1" s="108" t="s">
         <v>69</v>
       </c>
-      <c r="J1" s="105"/>
-      <c r="K1" s="105"/>
-      <c r="L1" s="105"/>
-      <c r="M1" s="105"/>
-      <c r="N1" s="105"/>
-      <c r="O1" s="105"/>
-      <c r="P1" s="105"/>
-      <c r="Q1" s="105"/>
-      <c r="R1" s="105"/>
-      <c r="S1" s="105"/>
-      <c r="T1" s="105"/>
-      <c r="U1" s="105"/>
-      <c r="V1" s="105"/>
-      <c r="W1" s="105"/>
-      <c r="X1" s="105"/>
-      <c r="Y1" s="105"/>
-      <c r="Z1" s="105"/>
+      <c r="J1" s="108"/>
+      <c r="K1" s="108"/>
+      <c r="L1" s="108"/>
+      <c r="M1" s="108"/>
+      <c r="N1" s="108"/>
+      <c r="O1" s="108"/>
+      <c r="P1" s="108"/>
+      <c r="Q1" s="108"/>
+      <c r="R1" s="108"/>
+      <c r="S1" s="108"/>
+      <c r="T1" s="108"/>
+      <c r="U1" s="108"/>
+      <c r="V1" s="108"/>
+      <c r="W1" s="108"/>
+      <c r="X1" s="108"/>
+      <c r="Y1" s="108"/>
+      <c r="Z1" s="108"/>
     </row>
     <row r="2" spans="1:32" ht="14.55" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B2" s="29"/>
@@ -4119,24 +4124,24 @@
       <c r="F2" s="29"/>
       <c r="G2" s="29"/>
       <c r="H2" s="29"/>
-      <c r="I2" s="105"/>
-      <c r="J2" s="105"/>
-      <c r="K2" s="105"/>
-      <c r="L2" s="105"/>
-      <c r="M2" s="105"/>
-      <c r="N2" s="105"/>
-      <c r="O2" s="105"/>
-      <c r="P2" s="105"/>
-      <c r="Q2" s="105"/>
-      <c r="R2" s="105"/>
-      <c r="S2" s="105"/>
-      <c r="T2" s="105"/>
-      <c r="U2" s="105"/>
-      <c r="V2" s="105"/>
-      <c r="W2" s="105"/>
-      <c r="X2" s="105"/>
-      <c r="Y2" s="105"/>
-      <c r="Z2" s="105"/>
+      <c r="I2" s="108"/>
+      <c r="J2" s="108"/>
+      <c r="K2" s="108"/>
+      <c r="L2" s="108"/>
+      <c r="M2" s="108"/>
+      <c r="N2" s="108"/>
+      <c r="O2" s="108"/>
+      <c r="P2" s="108"/>
+      <c r="Q2" s="108"/>
+      <c r="R2" s="108"/>
+      <c r="S2" s="108"/>
+      <c r="T2" s="108"/>
+      <c r="U2" s="108"/>
+      <c r="V2" s="108"/>
+      <c r="W2" s="108"/>
+      <c r="X2" s="108"/>
+      <c r="Y2" s="108"/>
+      <c r="Z2" s="108"/>
     </row>
     <row r="3" spans="1:32" ht="14.55" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B3" s="29"/>
@@ -4145,24 +4150,24 @@
       <c r="F3" s="29"/>
       <c r="G3" s="29"/>
       <c r="H3" s="29"/>
-      <c r="I3" s="105"/>
-      <c r="J3" s="105"/>
-      <c r="K3" s="105"/>
-      <c r="L3" s="105"/>
-      <c r="M3" s="105"/>
-      <c r="N3" s="105"/>
-      <c r="O3" s="105"/>
-      <c r="P3" s="105"/>
-      <c r="Q3" s="105"/>
-      <c r="R3" s="105"/>
-      <c r="S3" s="105"/>
-      <c r="T3" s="105"/>
-      <c r="U3" s="105"/>
-      <c r="V3" s="105"/>
-      <c r="W3" s="105"/>
-      <c r="X3" s="105"/>
-      <c r="Y3" s="105"/>
-      <c r="Z3" s="105"/>
+      <c r="I3" s="108"/>
+      <c r="J3" s="108"/>
+      <c r="K3" s="108"/>
+      <c r="L3" s="108"/>
+      <c r="M3" s="108"/>
+      <c r="N3" s="108"/>
+      <c r="O3" s="108"/>
+      <c r="P3" s="108"/>
+      <c r="Q3" s="108"/>
+      <c r="R3" s="108"/>
+      <c r="S3" s="108"/>
+      <c r="T3" s="108"/>
+      <c r="U3" s="108"/>
+      <c r="V3" s="108"/>
+      <c r="W3" s="108"/>
+      <c r="X3" s="108"/>
+      <c r="Y3" s="108"/>
+      <c r="Z3" s="108"/>
     </row>
     <row r="4" spans="1:32" ht="14.55" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B4" s="29"/>
@@ -4171,45 +4176,45 @@
       <c r="F4" s="29"/>
       <c r="G4" s="29"/>
       <c r="H4" s="29"/>
-      <c r="I4" s="105"/>
-      <c r="J4" s="105"/>
-      <c r="K4" s="105"/>
-      <c r="L4" s="105"/>
-      <c r="M4" s="105"/>
-      <c r="N4" s="105"/>
-      <c r="O4" s="105"/>
-      <c r="P4" s="105"/>
-      <c r="Q4" s="105"/>
-      <c r="R4" s="105"/>
-      <c r="S4" s="105"/>
-      <c r="T4" s="105"/>
-      <c r="U4" s="105"/>
-      <c r="V4" s="105"/>
-      <c r="W4" s="105"/>
-      <c r="X4" s="105"/>
-      <c r="Y4" s="105"/>
-      <c r="Z4" s="105"/>
+      <c r="I4" s="108"/>
+      <c r="J4" s="108"/>
+      <c r="K4" s="108"/>
+      <c r="L4" s="108"/>
+      <c r="M4" s="108"/>
+      <c r="N4" s="108"/>
+      <c r="O4" s="108"/>
+      <c r="P4" s="108"/>
+      <c r="Q4" s="108"/>
+      <c r="R4" s="108"/>
+      <c r="S4" s="108"/>
+      <c r="T4" s="108"/>
+      <c r="U4" s="108"/>
+      <c r="V4" s="108"/>
+      <c r="W4" s="108"/>
+      <c r="X4" s="108"/>
+      <c r="Y4" s="108"/>
+      <c r="Z4" s="108"/>
     </row>
     <row r="5" spans="1:32" ht="14.55" customHeight="1" x14ac:dyDescent="0.35">
       <c r="H5" s="6"/>
-      <c r="I5" s="105"/>
-      <c r="J5" s="105"/>
-      <c r="K5" s="105"/>
-      <c r="L5" s="105"/>
-      <c r="M5" s="105"/>
-      <c r="N5" s="105"/>
-      <c r="O5" s="105"/>
-      <c r="P5" s="105"/>
-      <c r="Q5" s="105"/>
-      <c r="R5" s="105"/>
-      <c r="S5" s="105"/>
-      <c r="T5" s="105"/>
-      <c r="U5" s="105"/>
-      <c r="V5" s="105"/>
-      <c r="W5" s="105"/>
-      <c r="X5" s="105"/>
-      <c r="Y5" s="105"/>
-      <c r="Z5" s="105"/>
+      <c r="I5" s="108"/>
+      <c r="J5" s="108"/>
+      <c r="K5" s="108"/>
+      <c r="L5" s="108"/>
+      <c r="M5" s="108"/>
+      <c r="N5" s="108"/>
+      <c r="O5" s="108"/>
+      <c r="P5" s="108"/>
+      <c r="Q5" s="108"/>
+      <c r="R5" s="108"/>
+      <c r="S5" s="108"/>
+      <c r="T5" s="108"/>
+      <c r="U5" s="108"/>
+      <c r="V5" s="108"/>
+      <c r="W5" s="108"/>
+      <c r="X5" s="108"/>
+      <c r="Y5" s="108"/>
+      <c r="Z5" s="108"/>
     </row>
     <row r="6" spans="1:32" ht="5.0999999999999996" customHeight="1" x14ac:dyDescent="0.35">
       <c r="H6" s="2"/>
@@ -4233,50 +4238,50 @@
       <c r="Z6" s="2"/>
     </row>
     <row r="7" spans="1:32" ht="5.0999999999999996" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="67"/>
-      <c r="B7" s="68"/>
-      <c r="C7" s="68"/>
-      <c r="D7" s="104"/>
-      <c r="E7" s="104"/>
-      <c r="F7" s="104"/>
-      <c r="G7" s="104"/>
-      <c r="H7" s="104"/>
-      <c r="I7" s="104"/>
-      <c r="J7" s="104"/>
-      <c r="K7" s="104"/>
-      <c r="L7" s="104"/>
-      <c r="M7" s="104"/>
-      <c r="N7" s="104"/>
-      <c r="O7" s="104"/>
-      <c r="P7" s="104"/>
-      <c r="Q7" s="104"/>
-      <c r="R7" s="104"/>
-      <c r="S7" s="104"/>
-      <c r="T7" s="104"/>
-      <c r="U7" s="104"/>
-      <c r="V7" s="104"/>
-      <c r="W7" s="104"/>
-      <c r="X7" s="104"/>
-      <c r="Y7" s="104"/>
-      <c r="Z7" s="104"/>
-      <c r="AA7" s="104"/>
-      <c r="AB7" s="104"/>
-      <c r="AC7" s="104"/>
-      <c r="AD7" s="104"/>
-      <c r="AE7" s="104"/>
-      <c r="AF7" s="104"/>
+      <c r="A7" s="65"/>
+      <c r="B7" s="66"/>
+      <c r="C7" s="66"/>
+      <c r="D7" s="107"/>
+      <c r="E7" s="107"/>
+      <c r="F7" s="107"/>
+      <c r="G7" s="107"/>
+      <c r="H7" s="107"/>
+      <c r="I7" s="107"/>
+      <c r="J7" s="107"/>
+      <c r="K7" s="107"/>
+      <c r="L7" s="107"/>
+      <c r="M7" s="107"/>
+      <c r="N7" s="107"/>
+      <c r="O7" s="107"/>
+      <c r="P7" s="107"/>
+      <c r="Q7" s="107"/>
+      <c r="R7" s="107"/>
+      <c r="S7" s="107"/>
+      <c r="T7" s="107"/>
+      <c r="U7" s="107"/>
+      <c r="V7" s="107"/>
+      <c r="W7" s="107"/>
+      <c r="X7" s="107"/>
+      <c r="Y7" s="107"/>
+      <c r="Z7" s="107"/>
+      <c r="AA7" s="107"/>
+      <c r="AB7" s="107"/>
+      <c r="AC7" s="107"/>
+      <c r="AD7" s="107"/>
+      <c r="AE7" s="107"/>
+      <c r="AF7" s="107"/>
     </row>
     <row r="8" spans="1:32" ht="5.0999999999999996" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="9" spans="1:32" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B9" s="106" t="s">
+      <c r="B9" s="100" t="s">
         <v>64</v>
       </c>
-      <c r="C9" s="106"/>
-      <c r="D9" s="106"/>
-      <c r="E9" s="106"/>
-      <c r="F9" s="106"/>
-      <c r="G9" s="106"/>
-      <c r="H9" s="106"/>
+      <c r="C9" s="100"/>
+      <c r="D9" s="100"/>
+      <c r="E9" s="100"/>
+      <c r="F9" s="100"/>
+      <c r="G9" s="100"/>
+      <c r="H9" s="100"/>
       <c r="I9" s="31"/>
       <c r="J9" s="31"/>
       <c r="K9" s="31"/>
@@ -4325,43 +4330,43 @@
       <c r="Z10" s="2"/>
     </row>
     <row r="11" spans="1:32" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B11" s="99" t="s">
+      <c r="B11" s="97" t="s">
         <v>72</v>
       </c>
-      <c r="C11" s="99"/>
-      <c r="D11" s="99"/>
-      <c r="E11" s="99"/>
-      <c r="F11" s="103"/>
-      <c r="G11" s="103"/>
-      <c r="H11" s="103"/>
+      <c r="C11" s="97"/>
+      <c r="D11" s="97"/>
+      <c r="E11" s="97"/>
+      <c r="F11" s="98"/>
+      <c r="G11" s="98"/>
+      <c r="H11" s="98"/>
       <c r="I11" s="31"/>
-      <c r="J11" s="99" t="s">
+      <c r="J11" s="97" t="s">
         <v>23</v>
       </c>
-      <c r="K11" s="99"/>
-      <c r="L11" s="99"/>
+      <c r="K11" s="97"/>
+      <c r="L11" s="97"/>
       <c r="M11" s="36"/>
       <c r="N11" s="36"/>
       <c r="O11" s="33"/>
-      <c r="P11" s="108" t="s">
+      <c r="P11" s="101" t="s">
         <v>73</v>
       </c>
-      <c r="Q11" s="108"/>
-      <c r="R11" s="108"/>
-      <c r="S11" s="108"/>
-      <c r="T11" s="108"/>
-      <c r="U11" s="108"/>
-      <c r="V11" s="108"/>
-      <c r="W11" s="108"/>
-      <c r="X11" s="108"/>
-      <c r="Y11" s="107"/>
-      <c r="Z11" s="107"/>
-      <c r="AA11" s="107"/>
-      <c r="AB11" s="99" t="s">
+      <c r="Q11" s="101"/>
+      <c r="R11" s="101"/>
+      <c r="S11" s="101"/>
+      <c r="T11" s="101"/>
+      <c r="U11" s="101"/>
+      <c r="V11" s="101"/>
+      <c r="W11" s="101"/>
+      <c r="X11" s="101"/>
+      <c r="Y11" s="109"/>
+      <c r="Z11" s="109"/>
+      <c r="AA11" s="109"/>
+      <c r="AB11" s="97" t="s">
         <v>22</v>
       </c>
-      <c r="AC11" s="99"/>
-      <c r="AD11" s="66"/>
+      <c r="AC11" s="97"/>
+      <c r="AD11" s="36"/>
       <c r="AE11" s="29"/>
       <c r="AF11" s="31"/>
     </row>
@@ -4387,39 +4392,39 @@
       <c r="Z12" s="2"/>
     </row>
     <row r="13" spans="1:32" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B13" s="99" t="s">
+      <c r="B13" s="97" t="s">
         <v>48</v>
       </c>
-      <c r="C13" s="99"/>
-      <c r="D13" s="99"/>
-      <c r="E13" s="99"/>
-      <c r="F13" s="103"/>
-      <c r="G13" s="103"/>
-      <c r="H13" s="103"/>
-      <c r="I13" s="103"/>
-      <c r="J13" s="103"/>
-      <c r="K13" s="103"/>
-      <c r="L13" s="103"/>
-      <c r="M13" s="103"/>
-      <c r="N13" s="103"/>
-      <c r="O13" s="103"/>
-      <c r="P13" s="103"/>
-      <c r="Q13" s="103"/>
-      <c r="R13" s="103"/>
-      <c r="S13" s="103"/>
-      <c r="T13" s="103"/>
-      <c r="U13" s="103"/>
-      <c r="V13" s="103"/>
-      <c r="W13" s="103"/>
-      <c r="X13" s="103"/>
-      <c r="Y13" s="103"/>
-      <c r="Z13" s="103"/>
-      <c r="AA13" s="103"/>
-      <c r="AB13" s="103"/>
-      <c r="AC13" s="103"/>
-      <c r="AD13" s="103"/>
-      <c r="AE13" s="103"/>
-      <c r="AF13" s="103"/>
+      <c r="C13" s="97"/>
+      <c r="D13" s="97"/>
+      <c r="E13" s="97"/>
+      <c r="F13" s="114"/>
+      <c r="G13" s="114"/>
+      <c r="H13" s="114"/>
+      <c r="I13" s="114"/>
+      <c r="J13" s="114"/>
+      <c r="K13" s="114"/>
+      <c r="L13" s="114"/>
+      <c r="M13" s="114"/>
+      <c r="N13" s="114"/>
+      <c r="O13" s="114"/>
+      <c r="P13" s="114"/>
+      <c r="Q13" s="114"/>
+      <c r="R13" s="114"/>
+      <c r="S13" s="114"/>
+      <c r="T13" s="114"/>
+      <c r="U13" s="114"/>
+      <c r="V13" s="114"/>
+      <c r="W13" s="114"/>
+      <c r="X13" s="114"/>
+      <c r="Y13" s="114"/>
+      <c r="Z13" s="114"/>
+      <c r="AA13" s="114"/>
+      <c r="AB13" s="114"/>
+      <c r="AC13" s="114"/>
+      <c r="AD13" s="114"/>
+      <c r="AE13" s="114"/>
+      <c r="AF13" s="114"/>
     </row>
     <row r="14" spans="1:32" ht="5.0999999999999996" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B14" s="34"/>
@@ -4428,12 +4433,12 @@
       <c r="E14" s="35"/>
     </row>
     <row r="15" spans="1:32" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B15" s="99" t="s">
+      <c r="B15" s="97" t="s">
         <v>25</v>
       </c>
-      <c r="C15" s="99"/>
-      <c r="D15" s="99"/>
-      <c r="E15" s="99"/>
+      <c r="C15" s="97"/>
+      <c r="D15" s="97"/>
+      <c r="E15" s="97"/>
       <c r="F15" s="36"/>
       <c r="G15" s="36"/>
       <c r="H15" s="36"/>
@@ -4469,45 +4474,45 @@
       <c r="E16" s="35"/>
     </row>
     <row r="17" spans="2:32" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B17" s="99" t="s">
+      <c r="B17" s="97" t="s">
         <v>49</v>
       </c>
-      <c r="C17" s="99"/>
-      <c r="D17" s="99"/>
-      <c r="E17" s="99"/>
-      <c r="F17" s="103"/>
-      <c r="G17" s="103"/>
-      <c r="H17" s="103"/>
-      <c r="I17" s="103"/>
+      <c r="C17" s="97"/>
+      <c r="D17" s="97"/>
+      <c r="E17" s="97"/>
+      <c r="F17" s="98"/>
+      <c r="G17" s="98"/>
+      <c r="H17" s="98"/>
+      <c r="I17" s="98"/>
       <c r="J17" s="37"/>
       <c r="K17" s="34" t="s">
         <v>43</v>
       </c>
-      <c r="L17" s="101"/>
-      <c r="M17" s="101"/>
+      <c r="L17" s="98"/>
+      <c r="M17" s="98"/>
       <c r="N17" s="29"/>
       <c r="O17" s="29" t="s">
         <v>27</v>
       </c>
       <c r="P17" s="29"/>
       <c r="Q17"/>
-      <c r="R17" s="101"/>
-      <c r="S17" s="101"/>
-      <c r="T17" s="101"/>
-      <c r="U17" s="101"/>
-      <c r="V17" s="101"/>
-      <c r="W17" s="99" t="s">
+      <c r="R17" s="98"/>
+      <c r="S17" s="98"/>
+      <c r="T17" s="98"/>
+      <c r="U17" s="98"/>
+      <c r="V17" s="98"/>
+      <c r="W17" s="97" t="s">
         <v>28</v>
       </c>
-      <c r="X17" s="99"/>
-      <c r="Y17" s="99"/>
-      <c r="Z17" s="99"/>
-      <c r="AA17" s="66"/>
-      <c r="AB17" s="66"/>
-      <c r="AC17" s="66"/>
-      <c r="AD17" s="66"/>
-      <c r="AE17" s="66"/>
-      <c r="AF17" s="66"/>
+      <c r="X17" s="97"/>
+      <c r="Y17" s="97"/>
+      <c r="Z17" s="97"/>
+      <c r="AA17" s="36"/>
+      <c r="AB17" s="64"/>
+      <c r="AC17" s="64"/>
+      <c r="AD17" s="64"/>
+      <c r="AE17" s="64"/>
+      <c r="AF17" s="64"/>
     </row>
     <row r="18" spans="2:32" ht="5.0999999999999996" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B18" s="34"/>
@@ -4543,37 +4548,37 @@
       <c r="AF18" s="38"/>
     </row>
     <row r="19" spans="2:32" ht="4.05" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B19" s="68"/>
-      <c r="C19" s="68"/>
-      <c r="D19" s="68"/>
-      <c r="E19" s="68"/>
-      <c r="F19" s="68"/>
-      <c r="G19" s="68"/>
-      <c r="H19" s="68"/>
-      <c r="I19" s="68"/>
-      <c r="J19" s="68"/>
-      <c r="K19" s="68"/>
-      <c r="L19" s="68"/>
-      <c r="M19" s="68"/>
-      <c r="N19" s="68"/>
-      <c r="O19" s="68"/>
-      <c r="P19" s="68"/>
-      <c r="Q19" s="68"/>
-      <c r="R19" s="68"/>
-      <c r="S19" s="68"/>
-      <c r="T19" s="68"/>
-      <c r="U19" s="68"/>
-      <c r="V19" s="68"/>
-      <c r="W19" s="68"/>
-      <c r="X19" s="68"/>
-      <c r="Y19" s="68"/>
-      <c r="Z19" s="68"/>
-      <c r="AA19" s="68"/>
-      <c r="AB19" s="68"/>
-      <c r="AC19" s="68"/>
-      <c r="AD19" s="68"/>
-      <c r="AE19" s="68"/>
-      <c r="AF19" s="68"/>
+      <c r="B19" s="66"/>
+      <c r="C19" s="66"/>
+      <c r="D19" s="66"/>
+      <c r="E19" s="66"/>
+      <c r="F19" s="66"/>
+      <c r="G19" s="66"/>
+      <c r="H19" s="66"/>
+      <c r="I19" s="66"/>
+      <c r="J19" s="66"/>
+      <c r="K19" s="66"/>
+      <c r="L19" s="66"/>
+      <c r="M19" s="66"/>
+      <c r="N19" s="66"/>
+      <c r="O19" s="66"/>
+      <c r="P19" s="66"/>
+      <c r="Q19" s="66"/>
+      <c r="R19" s="66"/>
+      <c r="S19" s="66"/>
+      <c r="T19" s="66"/>
+      <c r="U19" s="66"/>
+      <c r="V19" s="66"/>
+      <c r="W19" s="66"/>
+      <c r="X19" s="66"/>
+      <c r="Y19" s="66"/>
+      <c r="Z19" s="66"/>
+      <c r="AA19" s="66"/>
+      <c r="AB19" s="66"/>
+      <c r="AC19" s="66"/>
+      <c r="AD19" s="66"/>
+      <c r="AE19" s="66"/>
+      <c r="AF19" s="66"/>
     </row>
     <row r="20" spans="2:32" ht="5.0999999999999996" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B20" s="31"/>
@@ -4609,19 +4614,19 @@
       <c r="AF20" s="31"/>
     </row>
     <row r="21" spans="2:32" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B21" s="102" t="s">
+      <c r="B21" s="111" t="s">
         <v>65</v>
       </c>
-      <c r="C21" s="102"/>
-      <c r="D21" s="102"/>
-      <c r="E21" s="102"/>
-      <c r="F21" s="102"/>
-      <c r="G21" s="102"/>
-      <c r="H21" s="102"/>
-      <c r="I21" s="102"/>
-      <c r="J21" s="102"/>
-      <c r="K21" s="102"/>
-      <c r="L21" s="102"/>
+      <c r="C21" s="111"/>
+      <c r="D21" s="111"/>
+      <c r="E21" s="111"/>
+      <c r="F21" s="111"/>
+      <c r="G21" s="111"/>
+      <c r="H21" s="111"/>
+      <c r="I21" s="111"/>
+      <c r="J21" s="111"/>
+      <c r="K21" s="111"/>
+      <c r="L21" s="111"/>
     </row>
     <row r="22" spans="2:32" ht="5.0999999999999996" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B22" s="39"/>
@@ -4635,23 +4640,23 @@
     <row r="23" spans="2:32" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B23" s="39"/>
       <c r="C23" s="39"/>
-      <c r="D23" s="106" t="s">
+      <c r="D23" s="100" t="s">
         <v>63</v>
       </c>
-      <c r="E23" s="106"/>
-      <c r="F23" s="106"/>
-      <c r="G23" s="106"/>
-      <c r="H23" s="106"/>
-      <c r="I23" s="106"/>
-      <c r="J23" s="106"/>
-      <c r="K23" s="106"/>
-      <c r="L23" s="106"/>
-      <c r="M23" s="106"/>
-      <c r="N23" s="106"/>
-      <c r="O23" s="106"/>
-      <c r="P23" s="106"/>
-      <c r="Q23" s="106"/>
-      <c r="R23" s="106"/>
+      <c r="E23" s="100"/>
+      <c r="F23" s="100"/>
+      <c r="G23" s="100"/>
+      <c r="H23" s="100"/>
+      <c r="I23" s="100"/>
+      <c r="J23" s="100"/>
+      <c r="K23" s="100"/>
+      <c r="L23" s="100"/>
+      <c r="M23" s="100"/>
+      <c r="N23" s="100"/>
+      <c r="O23" s="100"/>
+      <c r="P23" s="100"/>
+      <c r="Q23" s="100"/>
+      <c r="R23" s="100"/>
     </row>
     <row r="24" spans="2:32" ht="5.0999999999999996" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B24" s="39"/>
@@ -4665,11 +4670,11 @@
     <row r="25" spans="2:32" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B25" s="39"/>
       <c r="C25" s="39"/>
-      <c r="D25" s="40"/>
+      <c r="D25" s="112"/>
       <c r="E25" s="32" t="s">
         <v>57</v>
       </c>
-      <c r="F25" s="40"/>
+      <c r="F25" s="112"/>
       <c r="G25" s="32" t="s">
         <v>58</v>
       </c>
@@ -4697,39 +4702,39 @@
       <c r="Z26" s="2"/>
     </row>
     <row r="27" spans="2:32" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B27" s="99" t="s">
+      <c r="B27" s="97" t="s">
         <v>55</v>
       </c>
-      <c r="C27" s="99"/>
-      <c r="D27" s="99"/>
-      <c r="E27" s="99"/>
-      <c r="F27" s="103"/>
-      <c r="G27" s="103"/>
-      <c r="H27" s="103"/>
-      <c r="I27" s="103"/>
-      <c r="J27" s="103"/>
-      <c r="K27" s="103"/>
-      <c r="L27" s="103"/>
-      <c r="M27" s="103"/>
-      <c r="N27" s="103"/>
-      <c r="O27" s="103"/>
-      <c r="P27" s="103"/>
-      <c r="Q27" s="103"/>
-      <c r="R27" s="103"/>
-      <c r="S27" s="103"/>
-      <c r="T27" s="103"/>
-      <c r="U27" s="103"/>
-      <c r="V27" s="103"/>
-      <c r="W27" s="103"/>
-      <c r="X27" s="103"/>
-      <c r="Y27" s="103"/>
-      <c r="Z27" s="103"/>
-      <c r="AA27" s="103"/>
-      <c r="AB27" s="103"/>
-      <c r="AC27" s="103"/>
-      <c r="AD27" s="103"/>
-      <c r="AE27" s="103"/>
-      <c r="AF27" s="103"/>
+      <c r="C27" s="97"/>
+      <c r="D27" s="97"/>
+      <c r="E27" s="97"/>
+      <c r="F27" s="114"/>
+      <c r="G27" s="114"/>
+      <c r="H27" s="114"/>
+      <c r="I27" s="114"/>
+      <c r="J27" s="114"/>
+      <c r="K27" s="114"/>
+      <c r="L27" s="114"/>
+      <c r="M27" s="114"/>
+      <c r="N27" s="114"/>
+      <c r="O27" s="114"/>
+      <c r="P27" s="114"/>
+      <c r="Q27" s="114"/>
+      <c r="R27" s="114"/>
+      <c r="S27" s="114"/>
+      <c r="T27" s="114"/>
+      <c r="U27" s="114"/>
+      <c r="V27" s="114"/>
+      <c r="W27" s="114"/>
+      <c r="X27" s="114"/>
+      <c r="Y27" s="114"/>
+      <c r="Z27" s="114"/>
+      <c r="AA27" s="114"/>
+      <c r="AB27" s="114"/>
+      <c r="AC27" s="114"/>
+      <c r="AD27" s="114"/>
+      <c r="AE27" s="114"/>
+      <c r="AF27" s="114"/>
     </row>
     <row r="28" spans="2:32" ht="5.0999999999999996" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B28" s="34"/>
@@ -4738,39 +4743,39 @@
       <c r="E28" s="35"/>
     </row>
     <row r="29" spans="2:32" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B29" s="99" t="s">
+      <c r="B29" s="97" t="s">
         <v>25</v>
       </c>
-      <c r="C29" s="99"/>
-      <c r="D29" s="99"/>
-      <c r="E29" s="99"/>
-      <c r="F29" s="103"/>
-      <c r="G29" s="103"/>
-      <c r="H29" s="103"/>
-      <c r="I29" s="103"/>
-      <c r="J29" s="103"/>
-      <c r="K29" s="103"/>
-      <c r="L29" s="103"/>
-      <c r="M29" s="103"/>
-      <c r="N29" s="103"/>
-      <c r="O29" s="103"/>
-      <c r="P29" s="103"/>
-      <c r="Q29" s="103"/>
-      <c r="R29" s="103"/>
-      <c r="S29" s="103"/>
-      <c r="T29" s="103"/>
-      <c r="U29" s="103"/>
-      <c r="V29" s="103"/>
-      <c r="W29" s="103"/>
-      <c r="X29" s="103"/>
-      <c r="Y29" s="103"/>
-      <c r="Z29" s="103"/>
-      <c r="AA29" s="103"/>
-      <c r="AB29" s="103"/>
-      <c r="AC29" s="103"/>
-      <c r="AD29" s="103"/>
-      <c r="AE29" s="103"/>
-      <c r="AF29" s="103"/>
+      <c r="C29" s="97"/>
+      <c r="D29" s="97"/>
+      <c r="E29" s="97"/>
+      <c r="F29" s="98"/>
+      <c r="G29" s="98"/>
+      <c r="H29" s="98"/>
+      <c r="I29" s="98"/>
+      <c r="J29" s="98"/>
+      <c r="K29" s="98"/>
+      <c r="L29" s="98"/>
+      <c r="M29" s="98"/>
+      <c r="N29" s="98"/>
+      <c r="O29" s="98"/>
+      <c r="P29" s="98"/>
+      <c r="Q29" s="98"/>
+      <c r="R29" s="98"/>
+      <c r="S29" s="98"/>
+      <c r="T29" s="98"/>
+      <c r="U29" s="98"/>
+      <c r="V29" s="98"/>
+      <c r="W29" s="98"/>
+      <c r="X29" s="98"/>
+      <c r="Y29" s="98"/>
+      <c r="Z29" s="98"/>
+      <c r="AA29" s="98"/>
+      <c r="AB29" s="98"/>
+      <c r="AC29" s="98"/>
+      <c r="AD29" s="98"/>
+      <c r="AE29" s="98"/>
+      <c r="AF29" s="98"/>
     </row>
     <row r="30" spans="2:32" ht="5.0999999999999996" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B30" s="35"/>
@@ -4779,81 +4784,81 @@
       <c r="E30" s="35"/>
     </row>
     <row r="31" spans="2:32" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B31" s="99" t="s">
+      <c r="B31" s="97" t="s">
         <v>26</v>
       </c>
-      <c r="C31" s="99"/>
-      <c r="D31" s="99"/>
-      <c r="E31" s="99"/>
-      <c r="F31" s="103"/>
-      <c r="G31" s="103"/>
-      <c r="H31" s="103"/>
-      <c r="I31" s="103"/>
+      <c r="C31" s="97"/>
+      <c r="D31" s="97"/>
+      <c r="E31" s="97"/>
+      <c r="F31" s="98"/>
+      <c r="G31" s="98"/>
+      <c r="H31" s="98"/>
+      <c r="I31" s="98"/>
       <c r="J31" s="37"/>
       <c r="K31" s="34" t="s">
         <v>43</v>
       </c>
-      <c r="L31" s="101"/>
-      <c r="M31" s="101"/>
+      <c r="L31" s="98"/>
+      <c r="M31" s="98"/>
       <c r="N31" s="29"/>
       <c r="O31" s="29" t="s">
         <v>27</v>
       </c>
       <c r="P31" s="29"/>
       <c r="Q31"/>
-      <c r="R31" s="114"/>
-      <c r="S31" s="114"/>
-      <c r="T31" s="114"/>
-      <c r="U31" s="114"/>
-      <c r="V31" s="114"/>
-      <c r="W31" s="99" t="s">
+      <c r="R31" s="113"/>
+      <c r="S31" s="113"/>
+      <c r="T31" s="113"/>
+      <c r="U31" s="113"/>
+      <c r="V31" s="113"/>
+      <c r="W31" s="97" t="s">
         <v>28</v>
       </c>
-      <c r="X31" s="99"/>
-      <c r="Y31" s="99"/>
-      <c r="Z31" s="99"/>
-      <c r="AA31" s="66"/>
-      <c r="AB31" s="66"/>
-      <c r="AC31" s="66"/>
-      <c r="AD31" s="66"/>
-      <c r="AE31" s="66"/>
-      <c r="AF31" s="66"/>
+      <c r="X31" s="97"/>
+      <c r="Y31" s="97"/>
+      <c r="Z31" s="97"/>
+      <c r="AA31" s="36"/>
+      <c r="AB31" s="64"/>
+      <c r="AC31" s="64"/>
+      <c r="AD31" s="64"/>
+      <c r="AE31" s="64"/>
+      <c r="AF31" s="64"/>
     </row>
     <row r="32" spans="2:32" ht="5.0999999999999996" customHeight="1" x14ac:dyDescent="0.35">
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
     </row>
     <row r="33" spans="2:32" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B33" s="99" t="s">
+      <c r="B33" s="97" t="s">
         <v>59</v>
       </c>
-      <c r="C33" s="99"/>
-      <c r="D33" s="99"/>
-      <c r="E33" s="99"/>
-      <c r="F33" s="101"/>
-      <c r="G33" s="101"/>
-      <c r="H33" s="101"/>
-      <c r="I33" s="101"/>
+      <c r="C33" s="97"/>
+      <c r="D33" s="97"/>
+      <c r="E33" s="97"/>
+      <c r="F33" s="99"/>
+      <c r="G33" s="99"/>
+      <c r="H33" s="99"/>
+      <c r="I33" s="99"/>
       <c r="J33" s="38"/>
-      <c r="K33" s="99" t="s">
+      <c r="K33" s="97" t="s">
         <v>70</v>
       </c>
-      <c r="L33" s="99"/>
-      <c r="M33" s="99"/>
-      <c r="N33" s="99"/>
-      <c r="O33" s="99"/>
-      <c r="P33" s="99"/>
-      <c r="Q33" s="66"/>
-      <c r="R33" s="66"/>
-      <c r="S33" s="66"/>
-      <c r="T33" s="66"/>
-      <c r="U33" s="66"/>
-      <c r="V33" s="66"/>
-      <c r="W33" s="66"/>
-      <c r="X33" s="66"/>
-      <c r="Y33" s="66"/>
-      <c r="Z33" s="66"/>
-      <c r="AA33" s="66"/>
+      <c r="L33" s="97"/>
+      <c r="M33" s="97"/>
+      <c r="N33" s="97"/>
+      <c r="O33" s="97"/>
+      <c r="P33" s="97"/>
+      <c r="Q33" s="64"/>
+      <c r="R33" s="64"/>
+      <c r="S33" s="64"/>
+      <c r="T33" s="64"/>
+      <c r="U33" s="64"/>
+      <c r="V33" s="64"/>
+      <c r="W33" s="64"/>
+      <c r="X33" s="64"/>
+      <c r="Y33" s="64"/>
+      <c r="Z33" s="64"/>
+      <c r="AA33" s="64"/>
       <c r="AB33" s="31"/>
       <c r="AC33" s="31"/>
       <c r="AD33" s="31"/>
@@ -4865,37 +4870,37 @@
       <c r="O34" s="2"/>
     </row>
     <row r="35" spans="2:32" ht="4.05" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B35" s="68"/>
-      <c r="C35" s="68"/>
-      <c r="D35" s="68"/>
-      <c r="E35" s="68"/>
-      <c r="F35" s="68"/>
-      <c r="G35" s="68"/>
-      <c r="H35" s="68"/>
-      <c r="I35" s="68"/>
-      <c r="J35" s="68"/>
-      <c r="K35" s="68"/>
-      <c r="L35" s="68"/>
-      <c r="M35" s="68"/>
-      <c r="N35" s="68"/>
-      <c r="O35" s="68"/>
-      <c r="P35" s="68"/>
-      <c r="Q35" s="68"/>
-      <c r="R35" s="68"/>
-      <c r="S35" s="68"/>
-      <c r="T35" s="68"/>
-      <c r="U35" s="68"/>
-      <c r="V35" s="68"/>
-      <c r="W35" s="68"/>
-      <c r="X35" s="68"/>
-      <c r="Y35" s="68"/>
-      <c r="Z35" s="68"/>
-      <c r="AA35" s="68"/>
-      <c r="AB35" s="68"/>
-      <c r="AC35" s="68"/>
-      <c r="AD35" s="68"/>
-      <c r="AE35" s="68"/>
-      <c r="AF35" s="68"/>
+      <c r="B35" s="66"/>
+      <c r="C35" s="66"/>
+      <c r="D35" s="66"/>
+      <c r="E35" s="66"/>
+      <c r="F35" s="66"/>
+      <c r="G35" s="66"/>
+      <c r="H35" s="66"/>
+      <c r="I35" s="66"/>
+      <c r="J35" s="66"/>
+      <c r="K35" s="66"/>
+      <c r="L35" s="66"/>
+      <c r="M35" s="66"/>
+      <c r="N35" s="66"/>
+      <c r="O35" s="66"/>
+      <c r="P35" s="66"/>
+      <c r="Q35" s="66"/>
+      <c r="R35" s="66"/>
+      <c r="S35" s="66"/>
+      <c r="T35" s="66"/>
+      <c r="U35" s="66"/>
+      <c r="V35" s="66"/>
+      <c r="W35" s="66"/>
+      <c r="X35" s="66"/>
+      <c r="Y35" s="66"/>
+      <c r="Z35" s="66"/>
+      <c r="AA35" s="66"/>
+      <c r="AB35" s="66"/>
+      <c r="AC35" s="66"/>
+      <c r="AD35" s="66"/>
+      <c r="AE35" s="66"/>
+      <c r="AF35" s="66"/>
     </row>
     <row r="36" spans="2:32" ht="5.0999999999999996" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="37" spans="2:32" ht="30" customHeight="1" x14ac:dyDescent="0.35">
@@ -4934,22 +4939,22 @@
       <c r="H39" s="31"/>
       <c r="I39" s="31"/>
       <c r="J39" s="31"/>
-      <c r="K39" s="99" t="s">
+      <c r="K39" s="97" t="s">
         <v>30</v>
       </c>
-      <c r="L39" s="99"/>
-      <c r="M39" s="99"/>
-      <c r="N39" s="103"/>
-      <c r="O39" s="103"/>
-      <c r="P39" s="103"/>
-      <c r="Q39" s="103"/>
-      <c r="R39" s="99" t="s">
+      <c r="L39" s="97"/>
+      <c r="M39" s="97"/>
+      <c r="N39" s="98"/>
+      <c r="O39" s="98"/>
+      <c r="P39" s="98"/>
+      <c r="Q39" s="98"/>
+      <c r="R39" s="97" t="s">
         <v>19</v>
       </c>
-      <c r="S39" s="99"/>
-      <c r="T39" s="99"/>
-      <c r="U39" s="99"/>
-      <c r="V39" s="99"/>
+      <c r="S39" s="97"/>
+      <c r="T39" s="97"/>
+      <c r="U39" s="97"/>
+      <c r="V39" s="97"/>
       <c r="W39" s="36"/>
       <c r="X39" s="36"/>
       <c r="Y39" s="36"/>
@@ -4963,61 +4968,61 @@
     </row>
     <row r="40" spans="2:32" ht="5.0999999999999996" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="41" spans="2:32" ht="4.05" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B41" s="68"/>
-      <c r="C41" s="68"/>
-      <c r="D41" s="68"/>
-      <c r="E41" s="68"/>
-      <c r="F41" s="68"/>
-      <c r="G41" s="68"/>
-      <c r="H41" s="68"/>
-      <c r="I41" s="68"/>
-      <c r="J41" s="68"/>
-      <c r="K41" s="68"/>
-      <c r="L41" s="68"/>
-      <c r="M41" s="68"/>
-      <c r="N41" s="68"/>
-      <c r="O41" s="68"/>
-      <c r="P41" s="68"/>
-      <c r="Q41" s="68"/>
-      <c r="R41" s="68"/>
-      <c r="S41" s="68"/>
-      <c r="T41" s="68"/>
-      <c r="U41" s="68"/>
-      <c r="V41" s="68"/>
-      <c r="W41" s="68"/>
-      <c r="X41" s="68"/>
-      <c r="Y41" s="68"/>
-      <c r="Z41" s="68"/>
-      <c r="AA41" s="68"/>
-      <c r="AB41" s="68"/>
-      <c r="AC41" s="68"/>
-      <c r="AD41" s="68"/>
-      <c r="AE41" s="68"/>
-      <c r="AF41" s="68"/>
+      <c r="B41" s="66"/>
+      <c r="C41" s="66"/>
+      <c r="D41" s="66"/>
+      <c r="E41" s="66"/>
+      <c r="F41" s="66"/>
+      <c r="G41" s="66"/>
+      <c r="H41" s="66"/>
+      <c r="I41" s="66"/>
+      <c r="J41" s="66"/>
+      <c r="K41" s="66"/>
+      <c r="L41" s="66"/>
+      <c r="M41" s="66"/>
+      <c r="N41" s="66"/>
+      <c r="O41" s="66"/>
+      <c r="P41" s="66"/>
+      <c r="Q41" s="66"/>
+      <c r="R41" s="66"/>
+      <c r="S41" s="66"/>
+      <c r="T41" s="66"/>
+      <c r="U41" s="66"/>
+      <c r="V41" s="66"/>
+      <c r="W41" s="66"/>
+      <c r="X41" s="66"/>
+      <c r="Y41" s="66"/>
+      <c r="Z41" s="66"/>
+      <c r="AA41" s="66"/>
+      <c r="AB41" s="66"/>
+      <c r="AC41" s="66"/>
+      <c r="AD41" s="66"/>
+      <c r="AE41" s="66"/>
+      <c r="AF41" s="66"/>
     </row>
     <row r="42" spans="2:32" ht="5.0999999999999996" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="43" spans="2:32" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B43" s="106" t="s">
+      <c r="B43" s="100" t="s">
         <v>67</v>
       </c>
-      <c r="C43" s="106"/>
-      <c r="D43" s="106"/>
-      <c r="E43" s="106"/>
-      <c r="F43" s="106"/>
-      <c r="G43" s="106"/>
-      <c r="H43" s="106"/>
+      <c r="C43" s="100"/>
+      <c r="D43" s="100"/>
+      <c r="E43" s="100"/>
+      <c r="F43" s="100"/>
+      <c r="G43" s="100"/>
+      <c r="H43" s="100"/>
     </row>
     <row r="44" spans="2:32" ht="5.0999999999999996" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="45" spans="2:32" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B45" s="106" t="s">
+      <c r="B45" s="100" t="s">
         <v>53</v>
       </c>
-      <c r="C45" s="106"/>
-      <c r="D45" s="106"/>
-      <c r="E45" s="106"/>
-      <c r="F45" s="106"/>
-      <c r="G45" s="106"/>
-      <c r="H45" s="106"/>
+      <c r="C45" s="100"/>
+      <c r="D45" s="100"/>
+      <c r="E45" s="100"/>
+      <c r="F45" s="100"/>
+      <c r="G45" s="100"/>
+      <c r="H45" s="100"/>
     </row>
     <row r="46" spans="2:32" ht="5.0999999999999996" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B46" s="32"/>
@@ -5030,211 +5035,211 @@
     </row>
     <row r="47" spans="2:32" ht="12" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B47" s="32"/>
-      <c r="C47" s="41"/>
-      <c r="D47" s="42"/>
-      <c r="E47" s="42"/>
-      <c r="F47" s="42"/>
-      <c r="G47" s="42"/>
-      <c r="H47" s="42"/>
-      <c r="I47" s="43"/>
-      <c r="J47" s="43"/>
-      <c r="K47" s="43"/>
-      <c r="L47" s="43"/>
-      <c r="M47" s="43"/>
-      <c r="N47" s="43"/>
-      <c r="O47" s="43"/>
-      <c r="P47" s="43"/>
-      <c r="Q47" s="43"/>
-      <c r="R47" s="43"/>
-      <c r="S47" s="43"/>
-      <c r="T47" s="43"/>
-      <c r="U47" s="44"/>
-      <c r="V47" s="45"/>
-      <c r="W47" s="46"/>
-      <c r="X47" s="43"/>
-      <c r="Y47" s="43"/>
-      <c r="Z47" s="43"/>
-      <c r="AA47" s="43"/>
-      <c r="AB47" s="43"/>
-      <c r="AC47" s="43"/>
-      <c r="AD47" s="43"/>
-      <c r="AE47" s="44"/>
+      <c r="C47" s="40"/>
+      <c r="D47" s="41"/>
+      <c r="E47" s="41"/>
+      <c r="F47" s="41"/>
+      <c r="G47" s="41"/>
+      <c r="H47" s="41"/>
+      <c r="I47" s="42"/>
+      <c r="J47" s="42"/>
+      <c r="K47" s="42"/>
+      <c r="L47" s="42"/>
+      <c r="M47" s="42"/>
+      <c r="N47" s="42"/>
+      <c r="O47" s="42"/>
+      <c r="P47" s="42"/>
+      <c r="Q47" s="42"/>
+      <c r="R47" s="42"/>
+      <c r="S47" s="42"/>
+      <c r="T47" s="42"/>
+      <c r="U47" s="43"/>
+      <c r="V47" s="44"/>
+      <c r="W47" s="45"/>
+      <c r="X47" s="42"/>
+      <c r="Y47" s="42"/>
+      <c r="Z47" s="42"/>
+      <c r="AA47" s="42"/>
+      <c r="AB47" s="42"/>
+      <c r="AC47" s="42"/>
+      <c r="AD47" s="42"/>
+      <c r="AE47" s="43"/>
     </row>
     <row r="48" spans="2:32" ht="5.0999999999999996" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B48" s="32"/>
-      <c r="C48" s="65"/>
+      <c r="C48" s="63"/>
       <c r="D48" s="32"/>
       <c r="E48" s="32"/>
       <c r="F48" s="32"/>
       <c r="G48" s="32"/>
       <c r="H48" s="32"/>
-      <c r="U48" s="48"/>
-      <c r="W48" s="47"/>
-      <c r="AE48" s="48"/>
+      <c r="U48" s="47"/>
+      <c r="W48" s="46"/>
+      <c r="AE48" s="47"/>
     </row>
     <row r="49" spans="2:101" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="C49" s="47"/>
-      <c r="D49" s="40"/>
-      <c r="E49" s="110" t="s">
+      <c r="C49" s="46"/>
+      <c r="D49" s="112"/>
+      <c r="E49" s="103" t="s">
         <v>56</v>
       </c>
-      <c r="F49" s="106"/>
-      <c r="G49" s="106"/>
-      <c r="H49" s="106"/>
+      <c r="F49" s="100"/>
+      <c r="G49" s="100"/>
+      <c r="H49" s="100"/>
       <c r="I49" s="32"/>
       <c r="J49" s="32"/>
       <c r="K49" s="32"/>
-      <c r="U49" s="48"/>
-      <c r="W49" s="47"/>
-      <c r="X49" s="40"/>
+      <c r="U49" s="47"/>
+      <c r="W49" s="46"/>
+      <c r="X49" s="112"/>
       <c r="Y49" s="29" t="s">
         <v>60</v>
       </c>
-      <c r="AE49" s="48"/>
+      <c r="AE49" s="47"/>
     </row>
     <row r="50" spans="2:101" ht="5.0999999999999996" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="C50" s="47"/>
-      <c r="U50" s="48"/>
-      <c r="W50" s="47"/>
-      <c r="AE50" s="48"/>
+      <c r="C50" s="46"/>
+      <c r="U50" s="47"/>
+      <c r="W50" s="46"/>
+      <c r="AE50" s="47"/>
     </row>
     <row r="51" spans="2:101" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="C51" s="47"/>
+      <c r="C51" s="46"/>
       <c r="E51" s="34" t="s">
         <v>31</v>
       </c>
-      <c r="F51" s="101"/>
-      <c r="G51" s="101"/>
-      <c r="H51" s="101"/>
-      <c r="I51" s="101"/>
+      <c r="F51" s="98"/>
+      <c r="G51" s="98"/>
+      <c r="H51" s="98"/>
+      <c r="I51" s="98"/>
       <c r="J51" s="33"/>
       <c r="K51" s="33"/>
       <c r="L51" s="31"/>
       <c r="M51" s="29" t="s">
         <v>33</v>
       </c>
-      <c r="N51" s="101"/>
-      <c r="O51" s="101"/>
-      <c r="P51" s="101"/>
-      <c r="Q51" s="101"/>
-      <c r="R51" s="101"/>
-      <c r="S51" s="49" t="s">
+      <c r="N51" s="98"/>
+      <c r="O51" s="98"/>
+      <c r="P51" s="98"/>
+      <c r="Q51" s="98"/>
+      <c r="R51" s="98"/>
+      <c r="S51" s="48" t="s">
         <v>50</v>
       </c>
-      <c r="T51" s="66"/>
-      <c r="U51" s="48"/>
-      <c r="W51" s="47"/>
-      <c r="X51" s="100" t="s">
+      <c r="T51" s="36"/>
+      <c r="U51" s="47"/>
+      <c r="W51" s="46"/>
+      <c r="X51" s="110" t="s">
         <v>21</v>
       </c>
-      <c r="Y51" s="100"/>
-      <c r="Z51" s="100"/>
-      <c r="AA51" s="100"/>
-      <c r="AB51" s="100"/>
-      <c r="AC51" s="100"/>
-      <c r="AD51" s="100"/>
-      <c r="AE51" s="50"/>
-      <c r="AF51" s="51"/>
+      <c r="Y51" s="110"/>
+      <c r="Z51" s="110"/>
+      <c r="AA51" s="110"/>
+      <c r="AB51" s="110"/>
+      <c r="AC51" s="110"/>
+      <c r="AD51" s="110"/>
+      <c r="AE51" s="49"/>
+      <c r="AF51" s="50"/>
     </row>
     <row r="52" spans="2:101" ht="5.0999999999999996" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="C52" s="47"/>
+      <c r="C52" s="46"/>
       <c r="E52" s="35"/>
       <c r="I52" s="31"/>
       <c r="J52" s="31"/>
       <c r="K52" s="31"/>
-      <c r="U52" s="48"/>
-      <c r="W52" s="47"/>
-      <c r="X52" s="100"/>
-      <c r="Y52" s="100"/>
-      <c r="Z52" s="100"/>
-      <c r="AA52" s="100"/>
-      <c r="AB52" s="100"/>
-      <c r="AC52" s="100"/>
-      <c r="AD52" s="100"/>
-      <c r="AE52" s="50"/>
-      <c r="AF52" s="51"/>
+      <c r="U52" s="47"/>
+      <c r="W52" s="46"/>
+      <c r="X52" s="110"/>
+      <c r="Y52" s="110"/>
+      <c r="Z52" s="110"/>
+      <c r="AA52" s="110"/>
+      <c r="AB52" s="110"/>
+      <c r="AC52" s="110"/>
+      <c r="AD52" s="110"/>
+      <c r="AE52" s="49"/>
+      <c r="AF52" s="50"/>
     </row>
     <row r="53" spans="2:101" ht="5.0999999999999996" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="C53" s="47"/>
+      <c r="C53" s="46"/>
       <c r="E53" s="35"/>
       <c r="I53" s="31"/>
       <c r="J53" s="31"/>
       <c r="K53" s="31"/>
-      <c r="U53" s="48"/>
-      <c r="W53" s="47"/>
-      <c r="X53" s="100"/>
-      <c r="Y53" s="100"/>
-      <c r="Z53" s="100"/>
-      <c r="AA53" s="100"/>
-      <c r="AB53" s="100"/>
-      <c r="AC53" s="100"/>
-      <c r="AD53" s="100"/>
-      <c r="AE53" s="50"/>
-      <c r="AF53" s="51"/>
+      <c r="U53" s="47"/>
+      <c r="W53" s="46"/>
+      <c r="X53" s="110"/>
+      <c r="Y53" s="110"/>
+      <c r="Z53" s="110"/>
+      <c r="AA53" s="110"/>
+      <c r="AB53" s="110"/>
+      <c r="AC53" s="110"/>
+      <c r="AD53" s="110"/>
+      <c r="AE53" s="49"/>
+      <c r="AF53" s="50"/>
     </row>
     <row r="54" spans="2:101" ht="5.0999999999999996" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="C54" s="47"/>
+      <c r="C54" s="46"/>
       <c r="E54" s="35"/>
       <c r="I54" s="31"/>
       <c r="J54" s="31"/>
       <c r="K54" s="31"/>
-      <c r="U54" s="48"/>
-      <c r="W54" s="47"/>
-      <c r="X54" s="100"/>
-      <c r="Y54" s="100"/>
-      <c r="Z54" s="100"/>
-      <c r="AA54" s="100"/>
-      <c r="AB54" s="100"/>
-      <c r="AC54" s="100"/>
-      <c r="AD54" s="100"/>
-      <c r="AE54" s="50"/>
-      <c r="AF54" s="51"/>
+      <c r="U54" s="47"/>
+      <c r="W54" s="46"/>
+      <c r="X54" s="110"/>
+      <c r="Y54" s="110"/>
+      <c r="Z54" s="110"/>
+      <c r="AA54" s="110"/>
+      <c r="AB54" s="110"/>
+      <c r="AC54" s="110"/>
+      <c r="AD54" s="110"/>
+      <c r="AE54" s="49"/>
+      <c r="AF54" s="50"/>
     </row>
     <row r="55" spans="2:101" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="C55" s="47"/>
+      <c r="C55" s="46"/>
       <c r="E55" s="34" t="s">
         <v>32</v>
       </c>
-      <c r="F55" s="101"/>
-      <c r="G55" s="101"/>
-      <c r="H55" s="101"/>
-      <c r="I55" s="101"/>
-      <c r="J55" s="49" t="s">
+      <c r="F55" s="98"/>
+      <c r="G55" s="98"/>
+      <c r="H55" s="98"/>
+      <c r="I55" s="98"/>
+      <c r="J55" s="48" t="s">
         <v>50</v>
       </c>
-      <c r="K55" s="66"/>
-      <c r="N55" s="52"/>
+      <c r="K55" s="36"/>
+      <c r="N55" s="112"/>
       <c r="O55" s="32" t="s">
         <v>61</v>
       </c>
-      <c r="P55" s="53"/>
+      <c r="P55" s="51"/>
       <c r="Q55" s="32"/>
-      <c r="R55" s="52"/>
-      <c r="S55" s="110" t="s">
+      <c r="R55" s="112"/>
+      <c r="S55" s="103" t="s">
         <v>62</v>
       </c>
-      <c r="T55" s="106"/>
-      <c r="U55" s="54"/>
+      <c r="T55" s="100"/>
+      <c r="U55" s="52"/>
       <c r="V55" s="32"/>
-      <c r="W55" s="47"/>
-      <c r="X55" s="100"/>
-      <c r="Y55" s="100"/>
-      <c r="Z55" s="100"/>
-      <c r="AA55" s="100"/>
-      <c r="AB55" s="100"/>
-      <c r="AC55" s="100"/>
-      <c r="AD55" s="100"/>
-      <c r="AE55" s="50"/>
-      <c r="AF55" s="51"/>
+      <c r="W55" s="46"/>
+      <c r="X55" s="110"/>
+      <c r="Y55" s="110"/>
+      <c r="Z55" s="110"/>
+      <c r="AA55" s="110"/>
+      <c r="AB55" s="110"/>
+      <c r="AC55" s="110"/>
+      <c r="AD55" s="110"/>
+      <c r="AE55" s="49"/>
+      <c r="AF55" s="50"/>
     </row>
     <row r="56" spans="2:101" ht="5.0999999999999996" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="C56" s="47"/>
+      <c r="C56" s="46"/>
       <c r="E56" s="34"/>
       <c r="F56" s="38"/>
       <c r="G56" s="38"/>
       <c r="H56" s="38"/>
       <c r="I56" s="38"/>
-      <c r="J56" s="49"/>
+      <c r="J56" s="48"/>
       <c r="K56" s="31"/>
       <c r="N56" s="31"/>
       <c r="O56" s="31"/>
@@ -5243,86 +5248,86 @@
       <c r="R56" s="31"/>
       <c r="S56" s="32"/>
       <c r="T56" s="32"/>
-      <c r="U56" s="54"/>
+      <c r="U56" s="52"/>
       <c r="V56" s="32"/>
-      <c r="W56" s="47"/>
-      <c r="X56" s="55"/>
-      <c r="Y56" s="55"/>
-      <c r="Z56" s="55"/>
-      <c r="AA56" s="55"/>
-      <c r="AB56" s="55"/>
-      <c r="AC56" s="55"/>
-      <c r="AD56" s="55"/>
-      <c r="AE56" s="50"/>
-      <c r="AF56" s="51"/>
+      <c r="W56" s="46"/>
+      <c r="X56" s="53"/>
+      <c r="Y56" s="53"/>
+      <c r="Z56" s="53"/>
+      <c r="AA56" s="53"/>
+      <c r="AB56" s="53"/>
+      <c r="AC56" s="53"/>
+      <c r="AD56" s="53"/>
+      <c r="AE56" s="49"/>
+      <c r="AF56" s="50"/>
     </row>
     <row r="57" spans="2:101" ht="12" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="C57" s="56"/>
-      <c r="D57" s="57"/>
-      <c r="E57" s="57"/>
-      <c r="F57" s="57"/>
-      <c r="G57" s="57"/>
-      <c r="H57" s="57"/>
-      <c r="I57" s="57"/>
-      <c r="J57" s="57"/>
-      <c r="K57" s="57"/>
-      <c r="L57" s="57"/>
-      <c r="M57" s="57"/>
-      <c r="N57" s="57"/>
-      <c r="O57" s="57"/>
-      <c r="P57" s="57"/>
-      <c r="Q57" s="57"/>
-      <c r="R57" s="57"/>
-      <c r="S57" s="57"/>
-      <c r="T57" s="57"/>
-      <c r="U57" s="58"/>
-      <c r="V57" s="59"/>
-      <c r="W57" s="56"/>
-      <c r="X57" s="60"/>
-      <c r="Y57" s="60"/>
-      <c r="Z57" s="60"/>
-      <c r="AA57" s="60"/>
-      <c r="AB57" s="60"/>
-      <c r="AC57" s="60"/>
-      <c r="AD57" s="60"/>
-      <c r="AE57" s="61"/>
-      <c r="AF57" s="51"/>
+      <c r="C57" s="54"/>
+      <c r="D57" s="55"/>
+      <c r="E57" s="55"/>
+      <c r="F57" s="55"/>
+      <c r="G57" s="55"/>
+      <c r="H57" s="55"/>
+      <c r="I57" s="55"/>
+      <c r="J57" s="55"/>
+      <c r="K57" s="55"/>
+      <c r="L57" s="55"/>
+      <c r="M57" s="55"/>
+      <c r="N57" s="55"/>
+      <c r="O57" s="55"/>
+      <c r="P57" s="55"/>
+      <c r="Q57" s="55"/>
+      <c r="R57" s="55"/>
+      <c r="S57" s="55"/>
+      <c r="T57" s="55"/>
+      <c r="U57" s="56"/>
+      <c r="V57" s="57"/>
+      <c r="W57" s="54"/>
+      <c r="X57" s="58"/>
+      <c r="Y57" s="58"/>
+      <c r="Z57" s="58"/>
+      <c r="AA57" s="58"/>
+      <c r="AB57" s="58"/>
+      <c r="AC57" s="58"/>
+      <c r="AD57" s="58"/>
+      <c r="AE57" s="59"/>
+      <c r="AF57" s="50"/>
     </row>
     <row r="58" spans="2:101" ht="5.0999999999999996" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="59" spans="2:101" s="62" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B59" s="113" t="s">
+    <row r="59" spans="2:101" s="60" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B59" s="106" t="s">
         <v>71</v>
       </c>
-      <c r="C59" s="113"/>
-      <c r="D59" s="113"/>
-      <c r="E59" s="113"/>
-      <c r="F59" s="113"/>
-      <c r="G59" s="113"/>
-      <c r="H59" s="113"/>
-      <c r="I59" s="113"/>
-      <c r="J59" s="113"/>
-      <c r="K59" s="113"/>
-      <c r="L59" s="113"/>
-      <c r="M59" s="113"/>
-      <c r="N59" s="113"/>
-      <c r="O59" s="113"/>
-      <c r="P59" s="113"/>
-      <c r="Q59" s="113"/>
-      <c r="R59" s="113"/>
-      <c r="S59" s="113"/>
-      <c r="T59" s="113"/>
-      <c r="U59" s="113"/>
-      <c r="V59" s="113"/>
-      <c r="W59" s="113"/>
-      <c r="X59" s="113"/>
-      <c r="Y59" s="113"/>
-      <c r="Z59" s="113"/>
-      <c r="AA59" s="113"/>
-      <c r="AB59" s="113"/>
-      <c r="AC59" s="113"/>
-      <c r="AD59" s="113"/>
-      <c r="AE59" s="113"/>
-      <c r="AF59" s="113"/>
+      <c r="C59" s="106"/>
+      <c r="D59" s="106"/>
+      <c r="E59" s="106"/>
+      <c r="F59" s="106"/>
+      <c r="G59" s="106"/>
+      <c r="H59" s="106"/>
+      <c r="I59" s="106"/>
+      <c r="J59" s="106"/>
+      <c r="K59" s="106"/>
+      <c r="L59" s="106"/>
+      <c r="M59" s="106"/>
+      <c r="N59" s="106"/>
+      <c r="O59" s="106"/>
+      <c r="P59" s="106"/>
+      <c r="Q59" s="106"/>
+      <c r="R59" s="106"/>
+      <c r="S59" s="106"/>
+      <c r="T59" s="106"/>
+      <c r="U59" s="106"/>
+      <c r="V59" s="106"/>
+      <c r="W59" s="106"/>
+      <c r="X59" s="106"/>
+      <c r="Y59" s="106"/>
+      <c r="Z59" s="106"/>
+      <c r="AA59" s="106"/>
+      <c r="AB59" s="106"/>
+      <c r="AC59" s="106"/>
+      <c r="AD59" s="106"/>
+      <c r="AE59" s="106"/>
+      <c r="AF59" s="106"/>
       <c r="AG59" s="31"/>
       <c r="AH59" s="31"/>
       <c r="AI59" s="31"/>
@@ -5393,38 +5398,38 @@
       <c r="CV59" s="31"/>
       <c r="CW59" s="31"/>
     </row>
-    <row r="60" spans="2:101" s="62" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B60" s="113"/>
-      <c r="C60" s="113"/>
-      <c r="D60" s="113"/>
-      <c r="E60" s="113"/>
-      <c r="F60" s="113"/>
-      <c r="G60" s="113"/>
-      <c r="H60" s="113"/>
-      <c r="I60" s="113"/>
-      <c r="J60" s="113"/>
-      <c r="K60" s="113"/>
-      <c r="L60" s="113"/>
-      <c r="M60" s="113"/>
-      <c r="N60" s="113"/>
-      <c r="O60" s="113"/>
-      <c r="P60" s="113"/>
-      <c r="Q60" s="113"/>
-      <c r="R60" s="113"/>
-      <c r="S60" s="113"/>
-      <c r="T60" s="113"/>
-      <c r="U60" s="113"/>
-      <c r="V60" s="113"/>
-      <c r="W60" s="113"/>
-      <c r="X60" s="113"/>
-      <c r="Y60" s="113"/>
-      <c r="Z60" s="113"/>
-      <c r="AA60" s="113"/>
-      <c r="AB60" s="113"/>
-      <c r="AC60" s="113"/>
-      <c r="AD60" s="113"/>
-      <c r="AE60" s="113"/>
-      <c r="AF60" s="113"/>
+    <row r="60" spans="2:101" s="60" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B60" s="106"/>
+      <c r="C60" s="106"/>
+      <c r="D60" s="106"/>
+      <c r="E60" s="106"/>
+      <c r="F60" s="106"/>
+      <c r="G60" s="106"/>
+      <c r="H60" s="106"/>
+      <c r="I60" s="106"/>
+      <c r="J60" s="106"/>
+      <c r="K60" s="106"/>
+      <c r="L60" s="106"/>
+      <c r="M60" s="106"/>
+      <c r="N60" s="106"/>
+      <c r="O60" s="106"/>
+      <c r="P60" s="106"/>
+      <c r="Q60" s="106"/>
+      <c r="R60" s="106"/>
+      <c r="S60" s="106"/>
+      <c r="T60" s="106"/>
+      <c r="U60" s="106"/>
+      <c r="V60" s="106"/>
+      <c r="W60" s="106"/>
+      <c r="X60" s="106"/>
+      <c r="Y60" s="106"/>
+      <c r="Z60" s="106"/>
+      <c r="AA60" s="106"/>
+      <c r="AB60" s="106"/>
+      <c r="AC60" s="106"/>
+      <c r="AD60" s="106"/>
+      <c r="AE60" s="106"/>
+      <c r="AF60" s="106"/>
       <c r="AG60" s="31"/>
       <c r="AH60" s="31"/>
       <c r="AI60" s="31"/>
@@ -5495,38 +5500,38 @@
       <c r="CV60" s="31"/>
       <c r="CW60" s="31"/>
     </row>
-    <row r="61" spans="2:101" s="62" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B61" s="113"/>
-      <c r="C61" s="113"/>
-      <c r="D61" s="113"/>
-      <c r="E61" s="113"/>
-      <c r="F61" s="113"/>
-      <c r="G61" s="113"/>
-      <c r="H61" s="113"/>
-      <c r="I61" s="113"/>
-      <c r="J61" s="113"/>
-      <c r="K61" s="113"/>
-      <c r="L61" s="113"/>
-      <c r="M61" s="113"/>
-      <c r="N61" s="113"/>
-      <c r="O61" s="113"/>
-      <c r="P61" s="113"/>
-      <c r="Q61" s="113"/>
-      <c r="R61" s="113"/>
-      <c r="S61" s="113"/>
-      <c r="T61" s="113"/>
-      <c r="U61" s="113"/>
-      <c r="V61" s="113"/>
-      <c r="W61" s="113"/>
-      <c r="X61" s="113"/>
-      <c r="Y61" s="113"/>
-      <c r="Z61" s="113"/>
-      <c r="AA61" s="113"/>
-      <c r="AB61" s="113"/>
-      <c r="AC61" s="113"/>
-      <c r="AD61" s="113"/>
-      <c r="AE61" s="113"/>
-      <c r="AF61" s="113"/>
+    <row r="61" spans="2:101" s="60" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B61" s="106"/>
+      <c r="C61" s="106"/>
+      <c r="D61" s="106"/>
+      <c r="E61" s="106"/>
+      <c r="F61" s="106"/>
+      <c r="G61" s="106"/>
+      <c r="H61" s="106"/>
+      <c r="I61" s="106"/>
+      <c r="J61" s="106"/>
+      <c r="K61" s="106"/>
+      <c r="L61" s="106"/>
+      <c r="M61" s="106"/>
+      <c r="N61" s="106"/>
+      <c r="O61" s="106"/>
+      <c r="P61" s="106"/>
+      <c r="Q61" s="106"/>
+      <c r="R61" s="106"/>
+      <c r="S61" s="106"/>
+      <c r="T61" s="106"/>
+      <c r="U61" s="106"/>
+      <c r="V61" s="106"/>
+      <c r="W61" s="106"/>
+      <c r="X61" s="106"/>
+      <c r="Y61" s="106"/>
+      <c r="Z61" s="106"/>
+      <c r="AA61" s="106"/>
+      <c r="AB61" s="106"/>
+      <c r="AC61" s="106"/>
+      <c r="AD61" s="106"/>
+      <c r="AE61" s="106"/>
+      <c r="AF61" s="106"/>
       <c r="AG61" s="31"/>
       <c r="AH61" s="31"/>
       <c r="AI61" s="31"/>
@@ -5597,38 +5602,38 @@
       <c r="CV61" s="31"/>
       <c r="CW61" s="31"/>
     </row>
-    <row r="62" spans="2:101" s="62" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B62" s="113"/>
-      <c r="C62" s="113"/>
-      <c r="D62" s="113"/>
-      <c r="E62" s="113"/>
-      <c r="F62" s="113"/>
-      <c r="G62" s="113"/>
-      <c r="H62" s="113"/>
-      <c r="I62" s="113"/>
-      <c r="J62" s="113"/>
-      <c r="K62" s="113"/>
-      <c r="L62" s="113"/>
-      <c r="M62" s="113"/>
-      <c r="N62" s="113"/>
-      <c r="O62" s="113"/>
-      <c r="P62" s="113"/>
-      <c r="Q62" s="113"/>
-      <c r="R62" s="113"/>
-      <c r="S62" s="113"/>
-      <c r="T62" s="113"/>
-      <c r="U62" s="113"/>
-      <c r="V62" s="113"/>
-      <c r="W62" s="113"/>
-      <c r="X62" s="113"/>
-      <c r="Y62" s="113"/>
-      <c r="Z62" s="113"/>
-      <c r="AA62" s="113"/>
-      <c r="AB62" s="113"/>
-      <c r="AC62" s="113"/>
-      <c r="AD62" s="113"/>
-      <c r="AE62" s="113"/>
-      <c r="AF62" s="113"/>
+    <row r="62" spans="2:101" s="60" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B62" s="106"/>
+      <c r="C62" s="106"/>
+      <c r="D62" s="106"/>
+      <c r="E62" s="106"/>
+      <c r="F62" s="106"/>
+      <c r="G62" s="106"/>
+      <c r="H62" s="106"/>
+      <c r="I62" s="106"/>
+      <c r="J62" s="106"/>
+      <c r="K62" s="106"/>
+      <c r="L62" s="106"/>
+      <c r="M62" s="106"/>
+      <c r="N62" s="106"/>
+      <c r="O62" s="106"/>
+      <c r="P62" s="106"/>
+      <c r="Q62" s="106"/>
+      <c r="R62" s="106"/>
+      <c r="S62" s="106"/>
+      <c r="T62" s="106"/>
+      <c r="U62" s="106"/>
+      <c r="V62" s="106"/>
+      <c r="W62" s="106"/>
+      <c r="X62" s="106"/>
+      <c r="Y62" s="106"/>
+      <c r="Z62" s="106"/>
+      <c r="AA62" s="106"/>
+      <c r="AB62" s="106"/>
+      <c r="AC62" s="106"/>
+      <c r="AD62" s="106"/>
+      <c r="AE62" s="106"/>
+      <c r="AF62" s="106"/>
       <c r="AG62" s="31"/>
       <c r="AH62" s="31"/>
       <c r="AI62" s="31"/>
@@ -5699,38 +5704,38 @@
       <c r="CV62" s="31"/>
       <c r="CW62" s="31"/>
     </row>
-    <row r="63" spans="2:101" s="62" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B63" s="113"/>
-      <c r="C63" s="113"/>
-      <c r="D63" s="113"/>
-      <c r="E63" s="113"/>
-      <c r="F63" s="113"/>
-      <c r="G63" s="113"/>
-      <c r="H63" s="113"/>
-      <c r="I63" s="113"/>
-      <c r="J63" s="113"/>
-      <c r="K63" s="113"/>
-      <c r="L63" s="113"/>
-      <c r="M63" s="113"/>
-      <c r="N63" s="113"/>
-      <c r="O63" s="113"/>
-      <c r="P63" s="113"/>
-      <c r="Q63" s="113"/>
-      <c r="R63" s="113"/>
-      <c r="S63" s="113"/>
-      <c r="T63" s="113"/>
-      <c r="U63" s="113"/>
-      <c r="V63" s="113"/>
-      <c r="W63" s="113"/>
-      <c r="X63" s="113"/>
-      <c r="Y63" s="113"/>
-      <c r="Z63" s="113"/>
-      <c r="AA63" s="113"/>
-      <c r="AB63" s="113"/>
-      <c r="AC63" s="113"/>
-      <c r="AD63" s="113"/>
-      <c r="AE63" s="113"/>
-      <c r="AF63" s="113"/>
+    <row r="63" spans="2:101" s="60" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B63" s="106"/>
+      <c r="C63" s="106"/>
+      <c r="D63" s="106"/>
+      <c r="E63" s="106"/>
+      <c r="F63" s="106"/>
+      <c r="G63" s="106"/>
+      <c r="H63" s="106"/>
+      <c r="I63" s="106"/>
+      <c r="J63" s="106"/>
+      <c r="K63" s="106"/>
+      <c r="L63" s="106"/>
+      <c r="M63" s="106"/>
+      <c r="N63" s="106"/>
+      <c r="O63" s="106"/>
+      <c r="P63" s="106"/>
+      <c r="Q63" s="106"/>
+      <c r="R63" s="106"/>
+      <c r="S63" s="106"/>
+      <c r="T63" s="106"/>
+      <c r="U63" s="106"/>
+      <c r="V63" s="106"/>
+      <c r="W63" s="106"/>
+      <c r="X63" s="106"/>
+      <c r="Y63" s="106"/>
+      <c r="Z63" s="106"/>
+      <c r="AA63" s="106"/>
+      <c r="AB63" s="106"/>
+      <c r="AC63" s="106"/>
+      <c r="AD63" s="106"/>
+      <c r="AE63" s="106"/>
+      <c r="AF63" s="106"/>
       <c r="AG63" s="31"/>
       <c r="AH63" s="31"/>
       <c r="AI63" s="31"/>
@@ -5801,38 +5806,38 @@
       <c r="CV63" s="31"/>
       <c r="CW63" s="31"/>
     </row>
-    <row r="64" spans="2:101" s="62" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B64" s="113"/>
-      <c r="C64" s="113"/>
-      <c r="D64" s="113"/>
-      <c r="E64" s="113"/>
-      <c r="F64" s="113"/>
-      <c r="G64" s="113"/>
-      <c r="H64" s="113"/>
-      <c r="I64" s="113"/>
-      <c r="J64" s="113"/>
-      <c r="K64" s="113"/>
-      <c r="L64" s="113"/>
-      <c r="M64" s="113"/>
-      <c r="N64" s="113"/>
-      <c r="O64" s="113"/>
-      <c r="P64" s="113"/>
-      <c r="Q64" s="113"/>
-      <c r="R64" s="113"/>
-      <c r="S64" s="113"/>
-      <c r="T64" s="113"/>
-      <c r="U64" s="113"/>
-      <c r="V64" s="113"/>
-      <c r="W64" s="113"/>
-      <c r="X64" s="113"/>
-      <c r="Y64" s="113"/>
-      <c r="Z64" s="113"/>
-      <c r="AA64" s="113"/>
-      <c r="AB64" s="113"/>
-      <c r="AC64" s="113"/>
-      <c r="AD64" s="113"/>
-      <c r="AE64" s="113"/>
-      <c r="AF64" s="113"/>
+    <row r="64" spans="2:101" s="60" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B64" s="106"/>
+      <c r="C64" s="106"/>
+      <c r="D64" s="106"/>
+      <c r="E64" s="106"/>
+      <c r="F64" s="106"/>
+      <c r="G64" s="106"/>
+      <c r="H64" s="106"/>
+      <c r="I64" s="106"/>
+      <c r="J64" s="106"/>
+      <c r="K64" s="106"/>
+      <c r="L64" s="106"/>
+      <c r="M64" s="106"/>
+      <c r="N64" s="106"/>
+      <c r="O64" s="106"/>
+      <c r="P64" s="106"/>
+      <c r="Q64" s="106"/>
+      <c r="R64" s="106"/>
+      <c r="S64" s="106"/>
+      <c r="T64" s="106"/>
+      <c r="U64" s="106"/>
+      <c r="V64" s="106"/>
+      <c r="W64" s="106"/>
+      <c r="X64" s="106"/>
+      <c r="Y64" s="106"/>
+      <c r="Z64" s="106"/>
+      <c r="AA64" s="106"/>
+      <c r="AB64" s="106"/>
+      <c r="AC64" s="106"/>
+      <c r="AD64" s="106"/>
+      <c r="AE64" s="106"/>
+      <c r="AF64" s="106"/>
       <c r="AG64" s="31"/>
       <c r="AH64" s="31"/>
       <c r="AI64" s="31"/>
@@ -5903,38 +5908,38 @@
       <c r="CV64" s="31"/>
       <c r="CW64" s="31"/>
     </row>
-    <row r="65" spans="2:101" s="62" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B65" s="113"/>
-      <c r="C65" s="113"/>
-      <c r="D65" s="113"/>
-      <c r="E65" s="113"/>
-      <c r="F65" s="113"/>
-      <c r="G65" s="113"/>
-      <c r="H65" s="113"/>
-      <c r="I65" s="113"/>
-      <c r="J65" s="113"/>
-      <c r="K65" s="113"/>
-      <c r="L65" s="113"/>
-      <c r="M65" s="113"/>
-      <c r="N65" s="113"/>
-      <c r="O65" s="113"/>
-      <c r="P65" s="113"/>
-      <c r="Q65" s="113"/>
-      <c r="R65" s="113"/>
-      <c r="S65" s="113"/>
-      <c r="T65" s="113"/>
-      <c r="U65" s="113"/>
-      <c r="V65" s="113"/>
-      <c r="W65" s="113"/>
-      <c r="X65" s="113"/>
-      <c r="Y65" s="113"/>
-      <c r="Z65" s="113"/>
-      <c r="AA65" s="113"/>
-      <c r="AB65" s="113"/>
-      <c r="AC65" s="113"/>
-      <c r="AD65" s="113"/>
-      <c r="AE65" s="113"/>
-      <c r="AF65" s="113"/>
+    <row r="65" spans="2:101" s="60" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B65" s="106"/>
+      <c r="C65" s="106"/>
+      <c r="D65" s="106"/>
+      <c r="E65" s="106"/>
+      <c r="F65" s="106"/>
+      <c r="G65" s="106"/>
+      <c r="H65" s="106"/>
+      <c r="I65" s="106"/>
+      <c r="J65" s="106"/>
+      <c r="K65" s="106"/>
+      <c r="L65" s="106"/>
+      <c r="M65" s="106"/>
+      <c r="N65" s="106"/>
+      <c r="O65" s="106"/>
+      <c r="P65" s="106"/>
+      <c r="Q65" s="106"/>
+      <c r="R65" s="106"/>
+      <c r="S65" s="106"/>
+      <c r="T65" s="106"/>
+      <c r="U65" s="106"/>
+      <c r="V65" s="106"/>
+      <c r="W65" s="106"/>
+      <c r="X65" s="106"/>
+      <c r="Y65" s="106"/>
+      <c r="Z65" s="106"/>
+      <c r="AA65" s="106"/>
+      <c r="AB65" s="106"/>
+      <c r="AC65" s="106"/>
+      <c r="AD65" s="106"/>
+      <c r="AE65" s="106"/>
+      <c r="AF65" s="106"/>
       <c r="AG65" s="31"/>
       <c r="AH65" s="31"/>
       <c r="AI65" s="31"/>
@@ -6006,192 +6011,192 @@
       <c r="CW65" s="31"/>
     </row>
     <row r="66" spans="2:101" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B66" s="113"/>
-      <c r="C66" s="113"/>
-      <c r="D66" s="113"/>
-      <c r="E66" s="113"/>
-      <c r="F66" s="113"/>
-      <c r="G66" s="113"/>
-      <c r="H66" s="113"/>
-      <c r="I66" s="113"/>
-      <c r="J66" s="113"/>
-      <c r="K66" s="113"/>
-      <c r="L66" s="113"/>
-      <c r="M66" s="113"/>
-      <c r="N66" s="113"/>
-      <c r="O66" s="113"/>
-      <c r="P66" s="113"/>
-      <c r="Q66" s="113"/>
-      <c r="R66" s="113"/>
-      <c r="S66" s="113"/>
-      <c r="T66" s="113"/>
-      <c r="U66" s="113"/>
-      <c r="V66" s="113"/>
-      <c r="W66" s="113"/>
-      <c r="X66" s="113"/>
-      <c r="Y66" s="113"/>
-      <c r="Z66" s="113"/>
-      <c r="AA66" s="113"/>
-      <c r="AB66" s="113"/>
-      <c r="AC66" s="113"/>
-      <c r="AD66" s="113"/>
-      <c r="AE66" s="113"/>
-      <c r="AF66" s="113"/>
+      <c r="B66" s="106"/>
+      <c r="C66" s="106"/>
+      <c r="D66" s="106"/>
+      <c r="E66" s="106"/>
+      <c r="F66" s="106"/>
+      <c r="G66" s="106"/>
+      <c r="H66" s="106"/>
+      <c r="I66" s="106"/>
+      <c r="J66" s="106"/>
+      <c r="K66" s="106"/>
+      <c r="L66" s="106"/>
+      <c r="M66" s="106"/>
+      <c r="N66" s="106"/>
+      <c r="O66" s="106"/>
+      <c r="P66" s="106"/>
+      <c r="Q66" s="106"/>
+      <c r="R66" s="106"/>
+      <c r="S66" s="106"/>
+      <c r="T66" s="106"/>
+      <c r="U66" s="106"/>
+      <c r="V66" s="106"/>
+      <c r="W66" s="106"/>
+      <c r="X66" s="106"/>
+      <c r="Y66" s="106"/>
+      <c r="Z66" s="106"/>
+      <c r="AA66" s="106"/>
+      <c r="AB66" s="106"/>
+      <c r="AC66" s="106"/>
+      <c r="AD66" s="106"/>
+      <c r="AE66" s="106"/>
+      <c r="AF66" s="106"/>
     </row>
     <row r="67" spans="2:101" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B67" s="113"/>
-      <c r="C67" s="113"/>
-      <c r="D67" s="113"/>
-      <c r="E67" s="113"/>
-      <c r="F67" s="113"/>
-      <c r="G67" s="113"/>
-      <c r="H67" s="113"/>
-      <c r="I67" s="113"/>
-      <c r="J67" s="113"/>
-      <c r="K67" s="113"/>
-      <c r="L67" s="113"/>
-      <c r="M67" s="113"/>
-      <c r="N67" s="113"/>
-      <c r="O67" s="113"/>
-      <c r="P67" s="113"/>
-      <c r="Q67" s="113"/>
-      <c r="R67" s="113"/>
-      <c r="S67" s="113"/>
-      <c r="T67" s="113"/>
-      <c r="U67" s="113"/>
-      <c r="V67" s="113"/>
-      <c r="W67" s="113"/>
-      <c r="X67" s="113"/>
-      <c r="Y67" s="113"/>
-      <c r="Z67" s="113"/>
-      <c r="AA67" s="113"/>
-      <c r="AB67" s="113"/>
-      <c r="AC67" s="113"/>
-      <c r="AD67" s="113"/>
-      <c r="AE67" s="113"/>
-      <c r="AF67" s="113"/>
+      <c r="B67" s="106"/>
+      <c r="C67" s="106"/>
+      <c r="D67" s="106"/>
+      <c r="E67" s="106"/>
+      <c r="F67" s="106"/>
+      <c r="G67" s="106"/>
+      <c r="H67" s="106"/>
+      <c r="I67" s="106"/>
+      <c r="J67" s="106"/>
+      <c r="K67" s="106"/>
+      <c r="L67" s="106"/>
+      <c r="M67" s="106"/>
+      <c r="N67" s="106"/>
+      <c r="O67" s="106"/>
+      <c r="P67" s="106"/>
+      <c r="Q67" s="106"/>
+      <c r="R67" s="106"/>
+      <c r="S67" s="106"/>
+      <c r="T67" s="106"/>
+      <c r="U67" s="106"/>
+      <c r="V67" s="106"/>
+      <c r="W67" s="106"/>
+      <c r="X67" s="106"/>
+      <c r="Y67" s="106"/>
+      <c r="Z67" s="106"/>
+      <c r="AA67" s="106"/>
+      <c r="AB67" s="106"/>
+      <c r="AC67" s="106"/>
+      <c r="AD67" s="106"/>
+      <c r="AE67" s="106"/>
+      <c r="AF67" s="106"/>
     </row>
     <row r="68" spans="2:101" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B68" s="113"/>
-      <c r="C68" s="113"/>
-      <c r="D68" s="113"/>
-      <c r="E68" s="113"/>
-      <c r="F68" s="113"/>
-      <c r="G68" s="113"/>
-      <c r="H68" s="113"/>
-      <c r="I68" s="113"/>
-      <c r="J68" s="113"/>
-      <c r="K68" s="113"/>
-      <c r="L68" s="113"/>
-      <c r="M68" s="113"/>
-      <c r="N68" s="113"/>
-      <c r="O68" s="113"/>
-      <c r="P68" s="113"/>
-      <c r="Q68" s="113"/>
-      <c r="R68" s="113"/>
-      <c r="S68" s="113"/>
-      <c r="T68" s="113"/>
-      <c r="U68" s="113"/>
-      <c r="V68" s="113"/>
-      <c r="W68" s="113"/>
-      <c r="X68" s="113"/>
-      <c r="Y68" s="113"/>
-      <c r="Z68" s="113"/>
-      <c r="AA68" s="113"/>
-      <c r="AB68" s="113"/>
-      <c r="AC68" s="113"/>
-      <c r="AD68" s="113"/>
-      <c r="AE68" s="113"/>
-      <c r="AF68" s="113"/>
+      <c r="B68" s="106"/>
+      <c r="C68" s="106"/>
+      <c r="D68" s="106"/>
+      <c r="E68" s="106"/>
+      <c r="F68" s="106"/>
+      <c r="G68" s="106"/>
+      <c r="H68" s="106"/>
+      <c r="I68" s="106"/>
+      <c r="J68" s="106"/>
+      <c r="K68" s="106"/>
+      <c r="L68" s="106"/>
+      <c r="M68" s="106"/>
+      <c r="N68" s="106"/>
+      <c r="O68" s="106"/>
+      <c r="P68" s="106"/>
+      <c r="Q68" s="106"/>
+      <c r="R68" s="106"/>
+      <c r="S68" s="106"/>
+      <c r="T68" s="106"/>
+      <c r="U68" s="106"/>
+      <c r="V68" s="106"/>
+      <c r="W68" s="106"/>
+      <c r="X68" s="106"/>
+      <c r="Y68" s="106"/>
+      <c r="Z68" s="106"/>
+      <c r="AA68" s="106"/>
+      <c r="AB68" s="106"/>
+      <c r="AC68" s="106"/>
+      <c r="AD68" s="106"/>
+      <c r="AE68" s="106"/>
+      <c r="AF68" s="106"/>
     </row>
     <row r="69" spans="2:101" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B69" s="113"/>
-      <c r="C69" s="113"/>
-      <c r="D69" s="113"/>
-      <c r="E69" s="113"/>
-      <c r="F69" s="113"/>
-      <c r="G69" s="113"/>
-      <c r="H69" s="113"/>
-      <c r="I69" s="113"/>
-      <c r="J69" s="113"/>
-      <c r="K69" s="113"/>
-      <c r="L69" s="113"/>
-      <c r="M69" s="113"/>
-      <c r="N69" s="113"/>
-      <c r="O69" s="113"/>
-      <c r="P69" s="113"/>
-      <c r="Q69" s="113"/>
-      <c r="R69" s="113"/>
-      <c r="S69" s="113"/>
-      <c r="T69" s="113"/>
-      <c r="U69" s="113"/>
-      <c r="V69" s="113"/>
-      <c r="W69" s="113"/>
-      <c r="X69" s="113"/>
-      <c r="Y69" s="113"/>
-      <c r="Z69" s="113"/>
-      <c r="AA69" s="113"/>
-      <c r="AB69" s="113"/>
-      <c r="AC69" s="113"/>
-      <c r="AD69" s="113"/>
-      <c r="AE69" s="113"/>
-      <c r="AF69" s="113"/>
+      <c r="B69" s="106"/>
+      <c r="C69" s="106"/>
+      <c r="D69" s="106"/>
+      <c r="E69" s="106"/>
+      <c r="F69" s="106"/>
+      <c r="G69" s="106"/>
+      <c r="H69" s="106"/>
+      <c r="I69" s="106"/>
+      <c r="J69" s="106"/>
+      <c r="K69" s="106"/>
+      <c r="L69" s="106"/>
+      <c r="M69" s="106"/>
+      <c r="N69" s="106"/>
+      <c r="O69" s="106"/>
+      <c r="P69" s="106"/>
+      <c r="Q69" s="106"/>
+      <c r="R69" s="106"/>
+      <c r="S69" s="106"/>
+      <c r="T69" s="106"/>
+      <c r="U69" s="106"/>
+      <c r="V69" s="106"/>
+      <c r="W69" s="106"/>
+      <c r="X69" s="106"/>
+      <c r="Y69" s="106"/>
+      <c r="Z69" s="106"/>
+      <c r="AA69" s="106"/>
+      <c r="AB69" s="106"/>
+      <c r="AC69" s="106"/>
+      <c r="AD69" s="106"/>
+      <c r="AE69" s="106"/>
+      <c r="AF69" s="106"/>
     </row>
     <row r="70" spans="2:101" ht="5.0999999999999996" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B70" s="51"/>
-      <c r="C70" s="51"/>
-      <c r="D70" s="51"/>
-      <c r="E70" s="51"/>
-      <c r="F70" s="51"/>
-      <c r="G70" s="51"/>
-      <c r="H70" s="51"/>
-      <c r="I70" s="51"/>
-      <c r="J70" s="51"/>
-      <c r="K70" s="51"/>
-      <c r="L70" s="51"/>
-      <c r="M70" s="51"/>
-      <c r="N70" s="51"/>
-      <c r="O70" s="51"/>
-      <c r="P70" s="51"/>
-      <c r="Q70" s="51"/>
-      <c r="R70" s="51"/>
-      <c r="S70" s="51"/>
-      <c r="T70" s="51"/>
-      <c r="U70" s="51"/>
-      <c r="V70" s="51"/>
-      <c r="W70" s="51"/>
-      <c r="X70" s="51"/>
-      <c r="Y70" s="51"/>
-      <c r="Z70" s="51"/>
-      <c r="AA70" s="51"/>
-      <c r="AB70" s="51"/>
-      <c r="AC70" s="51"/>
-      <c r="AD70" s="51"/>
-      <c r="AE70" s="51"/>
-      <c r="AF70" s="51"/>
+      <c r="B70" s="50"/>
+      <c r="C70" s="50"/>
+      <c r="D70" s="50"/>
+      <c r="E70" s="50"/>
+      <c r="F70" s="50"/>
+      <c r="G70" s="50"/>
+      <c r="H70" s="50"/>
+      <c r="I70" s="50"/>
+      <c r="J70" s="50"/>
+      <c r="K70" s="50"/>
+      <c r="L70" s="50"/>
+      <c r="M70" s="50"/>
+      <c r="N70" s="50"/>
+      <c r="O70" s="50"/>
+      <c r="P70" s="50"/>
+      <c r="Q70" s="50"/>
+      <c r="R70" s="50"/>
+      <c r="S70" s="50"/>
+      <c r="T70" s="50"/>
+      <c r="U70" s="50"/>
+      <c r="V70" s="50"/>
+      <c r="W70" s="50"/>
+      <c r="X70" s="50"/>
+      <c r="Y70" s="50"/>
+      <c r="Z70" s="50"/>
+      <c r="AA70" s="50"/>
+      <c r="AB70" s="50"/>
+      <c r="AC70" s="50"/>
+      <c r="AD70" s="50"/>
+      <c r="AE70" s="50"/>
+      <c r="AF70" s="50"/>
     </row>
     <row r="71" spans="2:101" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="F71"/>
       <c r="G71"/>
-      <c r="H71" s="63"/>
-      <c r="I71" s="63"/>
-      <c r="J71" s="63"/>
-      <c r="K71" s="63"/>
-      <c r="L71" s="63"/>
-      <c r="M71" s="111">
+      <c r="H71" s="61"/>
+      <c r="I71" s="61"/>
+      <c r="J71" s="61"/>
+      <c r="K71" s="61"/>
+      <c r="L71" s="61"/>
+      <c r="M71" s="104">
         <f ca="1">TODAY()</f>
-        <v>46155</v>
-      </c>
-      <c r="N71" s="111"/>
-      <c r="O71" s="111"/>
-      <c r="P71" s="111"/>
-      <c r="Q71" s="111"/>
-      <c r="R71" s="111"/>
-      <c r="S71" s="111"/>
-      <c r="T71" s="111"/>
-      <c r="U71" s="111"/>
-      <c r="V71" s="111"/>
-      <c r="W71" s="111"/>
+        <v>46156</v>
+      </c>
+      <c r="N71" s="104"/>
+      <c r="O71" s="104"/>
+      <c r="P71" s="104"/>
+      <c r="Q71" s="104"/>
+      <c r="R71" s="104"/>
+      <c r="S71" s="104"/>
+      <c r="T71" s="104"/>
+      <c r="U71" s="104"/>
+      <c r="V71" s="104"/>
+      <c r="W71" s="104"/>
     </row>
     <row r="72" spans="2:101" ht="5.0999999999999996" customHeight="1" x14ac:dyDescent="0.35">
       <c r="I72" s="31"/>
@@ -6205,76 +6210,76 @@
       <c r="Q72" s="31"/>
       <c r="R72" s="31"/>
       <c r="S72" s="31"/>
-      <c r="T72" s="64"/>
-      <c r="U72" s="64"/>
-      <c r="V72" s="64"/>
-      <c r="W72" s="64"/>
-      <c r="X72" s="64"/>
-      <c r="Y72" s="64"/>
-      <c r="Z72" s="64"/>
+      <c r="T72" s="62"/>
+      <c r="U72" s="62"/>
+      <c r="V72" s="62"/>
+      <c r="W72" s="62"/>
+      <c r="X72" s="62"/>
+      <c r="Y72" s="62"/>
+      <c r="Z72" s="62"/>
     </row>
     <row r="73" spans="2:101" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B73" s="112"/>
-      <c r="C73" s="112"/>
-      <c r="D73" s="112"/>
-      <c r="E73" s="112"/>
-      <c r="F73" s="112"/>
-      <c r="G73" s="112"/>
-      <c r="H73" s="112"/>
-      <c r="I73" s="112"/>
-      <c r="J73" s="112"/>
-      <c r="K73" s="112"/>
-      <c r="L73" s="112"/>
-      <c r="M73" s="112"/>
-      <c r="N73" s="112"/>
-      <c r="O73" s="112"/>
-      <c r="P73" s="112"/>
-      <c r="Q73" s="112"/>
-      <c r="R73" s="112"/>
-      <c r="S73" s="112"/>
-      <c r="T73" s="112"/>
-      <c r="U73" s="112"/>
-      <c r="V73" s="112"/>
-      <c r="W73" s="112"/>
-      <c r="X73" s="112"/>
-      <c r="Y73" s="112"/>
+      <c r="B73" s="105"/>
+      <c r="C73" s="105"/>
+      <c r="D73" s="105"/>
+      <c r="E73" s="105"/>
+      <c r="F73" s="105"/>
+      <c r="G73" s="105"/>
+      <c r="H73" s="105"/>
+      <c r="I73" s="105"/>
+      <c r="J73" s="105"/>
+      <c r="K73" s="105"/>
+      <c r="L73" s="105"/>
+      <c r="M73" s="105"/>
+      <c r="N73" s="105"/>
+      <c r="O73" s="105"/>
+      <c r="P73" s="105"/>
+      <c r="Q73" s="105"/>
+      <c r="R73" s="105"/>
+      <c r="S73" s="105"/>
+      <c r="T73" s="105"/>
+      <c r="U73" s="105"/>
+      <c r="V73" s="105"/>
+      <c r="W73" s="105"/>
+      <c r="X73" s="105"/>
+      <c r="Y73" s="105"/>
       <c r="Z73" s="31"/>
-      <c r="AA73" s="109" t="s">
+      <c r="AA73" s="102" t="s">
         <v>51</v>
       </c>
-      <c r="AB73" s="108"/>
-      <c r="AC73" s="112"/>
-      <c r="AD73" s="112"/>
-      <c r="AE73" s="112"/>
-      <c r="AF73" s="112"/>
-    </row>
-    <row r="74" spans="2:101" s="62" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B74" s="108" t="s">
+      <c r="AB73" s="101"/>
+      <c r="AC73" s="115"/>
+      <c r="AD73" s="115"/>
+      <c r="AE73" s="115"/>
+      <c r="AF73" s="115"/>
+    </row>
+    <row r="74" spans="2:101" s="60" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B74" s="101" t="s">
         <v>68</v>
       </c>
-      <c r="C74" s="108"/>
-      <c r="D74" s="108"/>
-      <c r="E74" s="108"/>
-      <c r="F74" s="108"/>
-      <c r="G74" s="108"/>
-      <c r="H74" s="108"/>
-      <c r="I74" s="108"/>
-      <c r="J74" s="108"/>
-      <c r="K74" s="108"/>
-      <c r="L74" s="108"/>
-      <c r="M74" s="108"/>
-      <c r="N74" s="108"/>
-      <c r="O74" s="108"/>
-      <c r="P74" s="108"/>
-      <c r="Q74" s="108"/>
-      <c r="R74" s="108"/>
-      <c r="S74" s="108"/>
-      <c r="T74" s="108"/>
-      <c r="U74" s="108"/>
-      <c r="V74" s="108"/>
-      <c r="W74" s="108"/>
-      <c r="X74" s="108"/>
-      <c r="Y74" s="108"/>
+      <c r="C74" s="101"/>
+      <c r="D74" s="101"/>
+      <c r="E74" s="101"/>
+      <c r="F74" s="101"/>
+      <c r="G74" s="101"/>
+      <c r="H74" s="101"/>
+      <c r="I74" s="101"/>
+      <c r="J74" s="101"/>
+      <c r="K74" s="101"/>
+      <c r="L74" s="101"/>
+      <c r="M74" s="101"/>
+      <c r="N74" s="101"/>
+      <c r="O74" s="101"/>
+      <c r="P74" s="101"/>
+      <c r="Q74" s="101"/>
+      <c r="R74" s="101"/>
+      <c r="S74" s="101"/>
+      <c r="T74" s="101"/>
+      <c r="U74" s="101"/>
+      <c r="V74" s="101"/>
+      <c r="W74" s="101"/>
+      <c r="X74" s="101"/>
+      <c r="Y74" s="101"/>
       <c r="Z74" s="29"/>
       <c r="AA74" s="29"/>
       <c r="AB74" s="29"/>
@@ -6353,11 +6358,11 @@
       <c r="CW74" s="31"/>
     </row>
     <row r="75" spans="2:101" x14ac:dyDescent="0.35">
-      <c r="B75" s="69" t="s">
+      <c r="B75" s="67" t="s">
         <v>74</v>
       </c>
-      <c r="C75" s="70"/>
-      <c r="D75" s="70"/>
+      <c r="C75" s="68"/>
+      <c r="D75" s="68"/>
     </row>
     <row r="79" spans="2:101" x14ac:dyDescent="0.35">
       <c r="E79" s="31"/>
@@ -6614,14 +6619,30 @@
     </row>
   </sheetData>
   <mergeCells count="48">
-    <mergeCell ref="B13:E13"/>
-    <mergeCell ref="F13:AF13"/>
-    <mergeCell ref="F27:AF27"/>
-    <mergeCell ref="F17:I17"/>
-    <mergeCell ref="B17:E17"/>
-    <mergeCell ref="B15:E15"/>
-    <mergeCell ref="L17:M17"/>
-    <mergeCell ref="D23:R23"/>
+    <mergeCell ref="R31:V31"/>
+    <mergeCell ref="R17:V17"/>
+    <mergeCell ref="W17:Z17"/>
+    <mergeCell ref="X51:AD55"/>
+    <mergeCell ref="F51:I51"/>
+    <mergeCell ref="F55:I55"/>
+    <mergeCell ref="N51:R51"/>
+    <mergeCell ref="B21:L21"/>
+    <mergeCell ref="B27:E27"/>
+    <mergeCell ref="B33:E33"/>
+    <mergeCell ref="F33:I33"/>
+    <mergeCell ref="K39:M39"/>
+    <mergeCell ref="N39:Q39"/>
+    <mergeCell ref="R39:V39"/>
+    <mergeCell ref="K33:P33"/>
+    <mergeCell ref="D7:AF7"/>
+    <mergeCell ref="I1:Z5"/>
+    <mergeCell ref="B9:H9"/>
+    <mergeCell ref="F11:H11"/>
+    <mergeCell ref="J11:L11"/>
+    <mergeCell ref="AB11:AC11"/>
+    <mergeCell ref="B11:E11"/>
+    <mergeCell ref="Y11:AA11"/>
+    <mergeCell ref="P11:X11"/>
     <mergeCell ref="B74:Y74"/>
     <mergeCell ref="B29:E29"/>
     <mergeCell ref="F29:AF29"/>
@@ -6638,30 +6659,14 @@
     <mergeCell ref="L31:M31"/>
     <mergeCell ref="B59:AF69"/>
     <mergeCell ref="W31:Z31"/>
-    <mergeCell ref="D7:AF7"/>
-    <mergeCell ref="I1:Z5"/>
-    <mergeCell ref="B9:H9"/>
-    <mergeCell ref="F11:H11"/>
-    <mergeCell ref="J11:L11"/>
-    <mergeCell ref="AB11:AC11"/>
-    <mergeCell ref="B11:E11"/>
-    <mergeCell ref="Y11:AA11"/>
-    <mergeCell ref="P11:X11"/>
-    <mergeCell ref="R31:V31"/>
-    <mergeCell ref="R17:V17"/>
-    <mergeCell ref="W17:Z17"/>
-    <mergeCell ref="X51:AD55"/>
-    <mergeCell ref="F51:I51"/>
-    <mergeCell ref="F55:I55"/>
-    <mergeCell ref="N51:R51"/>
-    <mergeCell ref="B21:L21"/>
-    <mergeCell ref="B27:E27"/>
-    <mergeCell ref="B33:E33"/>
-    <mergeCell ref="F33:I33"/>
-    <mergeCell ref="K39:M39"/>
-    <mergeCell ref="N39:Q39"/>
-    <mergeCell ref="R39:V39"/>
-    <mergeCell ref="K33:P33"/>
+    <mergeCell ref="B13:E13"/>
+    <mergeCell ref="F13:AF13"/>
+    <mergeCell ref="F27:AF27"/>
+    <mergeCell ref="F17:I17"/>
+    <mergeCell ref="B17:E17"/>
+    <mergeCell ref="B15:E15"/>
+    <mergeCell ref="L17:M17"/>
+    <mergeCell ref="D23:R23"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.39370078740157483" right="0.39370078740157483" top="0.78740157480314965" bottom="0.39370078740157483" header="0" footer="0"/>
@@ -6675,21 +6680,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x01010095EF753253AC424BB919D030F322784C" ma:contentTypeVersion="11" ma:contentTypeDescription="Crie um novo documento." ma:contentTypeScope="" ma:versionID="5dee361c03f39daaba29bb6301110b52">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="61b10da2-a8bd-4c80-ada7-20e862ed4a55" xmlns:ns4="226b3370-e759-4194-8b3e-3f54776e6815" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="ba1a39153a8fc78cfabfc4e3ad702b04" ns3:_="" ns4:_="">
     <xsd:import namespace="61b10da2-a8bd-4c80-ada7-20e862ed4a55"/>
@@ -6898,10 +6888,36 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{42BA872A-576E-43AD-8084-92A56E3B6179}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6D498770-2854-44B7-AA88-0BB2DC723969}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="61b10da2-a8bd-4c80-ada7-20e862ed4a55"/>
+    <ds:schemaRef ds:uri="226b3370-e759-4194-8b3e-3f54776e6815"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -6924,20 +6940,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6D498770-2854-44B7-AA88-0BB2DC723969}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{42BA872A-576E-43AD-8084-92A56E3B6179}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="61b10da2-a8bd-4c80-ada7-20e862ed4a55"/>
-    <ds:schemaRef ds:uri="226b3370-e759-4194-8b3e-3f54776e6815"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/formularios/devolucao_credito.xlsx
+++ b/formularios/devolucao_credito.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CONTROLE DE QUALIDADE\formularios\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E43D89CC-0488-4EFF-A9AC-C726D6C754C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB7384A7-38B1-46E3-BA0D-A4540A531110}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -471,8 +471,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="[$-F800]dddd\,\ mmmm\ dd\,\ yyyy"/>
+    <numFmt numFmtId="166" formatCode="&quot;R$&quot;\ #,##0.00"/>
   </numFmts>
   <fonts count="17" x14ac:knownFonts="1">
     <font>
@@ -828,7 +829,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="116">
+  <cellXfs count="117">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
@@ -970,9 +971,6 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -984,102 +982,123 @@
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1095,34 +1114,19 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="3" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1656,66 +1660,66 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:23" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="95" t="s">
+      <c r="A1" s="71" t="s">
         <v>29</v>
       </c>
-      <c r="B1" s="95"/>
-      <c r="C1" s="95"/>
-      <c r="D1" s="95"/>
-      <c r="E1" s="95"/>
+      <c r="B1" s="71"/>
+      <c r="C1" s="71"/>
+      <c r="D1" s="71"/>
+      <c r="E1" s="71"/>
       <c r="F1" s="25"/>
-      <c r="G1" s="96" t="s">
+      <c r="G1" s="72" t="s">
         <v>0</v>
       </c>
-      <c r="H1" s="96"/>
-      <c r="I1" s="96"/>
-      <c r="J1" s="96"/>
-      <c r="K1" s="96"/>
-      <c r="L1" s="96"/>
-      <c r="M1" s="96"/>
-      <c r="N1" s="96"/>
-      <c r="O1" s="96"/>
-      <c r="P1" s="96"/>
-      <c r="Q1" s="96"/>
-      <c r="R1" s="96"/>
+      <c r="H1" s="72"/>
+      <c r="I1" s="72"/>
+      <c r="J1" s="72"/>
+      <c r="K1" s="72"/>
+      <c r="L1" s="72"/>
+      <c r="M1" s="72"/>
+      <c r="N1" s="72"/>
+      <c r="O1" s="72"/>
+      <c r="P1" s="72"/>
+      <c r="Q1" s="72"/>
+      <c r="R1" s="72"/>
     </row>
     <row r="2" spans="1:23" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="95" t="s">
+      <c r="A2" s="71" t="s">
         <v>39</v>
       </c>
-      <c r="B2" s="95"/>
-      <c r="C2" s="95"/>
-      <c r="D2" s="95"/>
-      <c r="E2" s="95"/>
+      <c r="B2" s="71"/>
+      <c r="C2" s="71"/>
+      <c r="D2" s="71"/>
+      <c r="E2" s="71"/>
       <c r="F2" s="25"/>
-      <c r="G2" s="96"/>
-      <c r="H2" s="96"/>
-      <c r="I2" s="96"/>
-      <c r="J2" s="96"/>
-      <c r="K2" s="96"/>
-      <c r="L2" s="96"/>
-      <c r="M2" s="96"/>
-      <c r="N2" s="96"/>
-      <c r="O2" s="96"/>
-      <c r="P2" s="96"/>
-      <c r="Q2" s="96"/>
-      <c r="R2" s="96"/>
+      <c r="G2" s="72"/>
+      <c r="H2" s="72"/>
+      <c r="I2" s="72"/>
+      <c r="J2" s="72"/>
+      <c r="K2" s="72"/>
+      <c r="L2" s="72"/>
+      <c r="M2" s="72"/>
+      <c r="N2" s="72"/>
+      <c r="O2" s="72"/>
+      <c r="P2" s="72"/>
+      <c r="Q2" s="72"/>
+      <c r="R2" s="72"/>
     </row>
     <row r="3" spans="1:23" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="E3" s="6"/>
       <c r="F3" s="6"/>
-      <c r="G3" s="96"/>
-      <c r="H3" s="96"/>
-      <c r="I3" s="96"/>
-      <c r="J3" s="96"/>
-      <c r="K3" s="96"/>
-      <c r="L3" s="96"/>
-      <c r="M3" s="96"/>
-      <c r="N3" s="96"/>
-      <c r="O3" s="96"/>
-      <c r="P3" s="96"/>
-      <c r="Q3" s="96"/>
-      <c r="R3" s="96"/>
+      <c r="G3" s="72"/>
+      <c r="H3" s="72"/>
+      <c r="I3" s="72"/>
+      <c r="J3" s="72"/>
+      <c r="K3" s="72"/>
+      <c r="L3" s="72"/>
+      <c r="M3" s="72"/>
+      <c r="N3" s="72"/>
+      <c r="O3" s="72"/>
+      <c r="P3" s="72"/>
+      <c r="Q3" s="72"/>
+      <c r="R3" s="72"/>
     </row>
     <row r="4" spans="1:23" ht="5.0999999999999996" customHeight="1" x14ac:dyDescent="0.3">
       <c r="E4" s="2"/>
@@ -1735,38 +1739,38 @@
     </row>
     <row r="5" spans="1:23" ht="5.0999999999999996" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="10"/>
-      <c r="B5" s="91"/>
-      <c r="C5" s="91"/>
-      <c r="D5" s="91"/>
-      <c r="E5" s="91"/>
-      <c r="F5" s="91"/>
-      <c r="G5" s="91"/>
-      <c r="H5" s="91"/>
-      <c r="I5" s="91"/>
-      <c r="J5" s="91"/>
-      <c r="K5" s="91"/>
-      <c r="L5" s="91"/>
-      <c r="M5" s="91"/>
-      <c r="N5" s="91"/>
-      <c r="O5" s="91"/>
-      <c r="P5" s="91"/>
-      <c r="Q5" s="91"/>
-      <c r="R5" s="91"/>
-      <c r="S5" s="91"/>
-      <c r="T5" s="91"/>
-      <c r="U5" s="91"/>
-      <c r="V5" s="91"/>
-      <c r="W5" s="91"/>
+      <c r="B5" s="73"/>
+      <c r="C5" s="73"/>
+      <c r="D5" s="73"/>
+      <c r="E5" s="73"/>
+      <c r="F5" s="73"/>
+      <c r="G5" s="73"/>
+      <c r="H5" s="73"/>
+      <c r="I5" s="73"/>
+      <c r="J5" s="73"/>
+      <c r="K5" s="73"/>
+      <c r="L5" s="73"/>
+      <c r="M5" s="73"/>
+      <c r="N5" s="73"/>
+      <c r="O5" s="73"/>
+      <c r="P5" s="73"/>
+      <c r="Q5" s="73"/>
+      <c r="R5" s="73"/>
+      <c r="S5" s="73"/>
+      <c r="T5" s="73"/>
+      <c r="U5" s="73"/>
+      <c r="V5" s="73"/>
+      <c r="W5" s="73"/>
     </row>
     <row r="6" spans="1:23" ht="5.0999999999999996" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="7" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="69" t="s">
+      <c r="A7" s="74" t="s">
         <v>46</v>
       </c>
-      <c r="B7" s="69"/>
-      <c r="C7" s="69"/>
-      <c r="D7" s="69"/>
-      <c r="E7" s="69"/>
+      <c r="B7" s="74"/>
+      <c r="C7" s="74"/>
+      <c r="D7" s="74"/>
+      <c r="E7" s="74"/>
       <c r="F7" s="18"/>
       <c r="G7" s="2"/>
       <c r="H7" s="2"/>
@@ -1801,29 +1805,29 @@
       <c r="R8" s="2"/>
     </row>
     <row r="9" spans="1:23" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="79" t="s">
+      <c r="A9" s="69" t="s">
         <v>40</v>
       </c>
-      <c r="B9" s="79"/>
-      <c r="C9" s="79"/>
-      <c r="D9" s="90"/>
-      <c r="E9" s="90"/>
+      <c r="B9" s="69"/>
+      <c r="C9" s="69"/>
+      <c r="D9" s="70"/>
+      <c r="E9" s="70"/>
       <c r="F9" s="26"/>
-      <c r="J9" s="87" t="s">
+      <c r="J9" s="75" t="s">
         <v>41</v>
       </c>
-      <c r="K9" s="87"/>
+      <c r="K9" s="75"/>
       <c r="L9" s="19"/>
       <c r="M9" s="19"/>
       <c r="N9" s="19"/>
       <c r="O9"/>
       <c r="R9"/>
       <c r="S9"/>
-      <c r="T9" s="79" t="s">
+      <c r="T9" s="69" t="s">
         <v>42</v>
       </c>
-      <c r="U9" s="79"/>
-      <c r="V9" s="79"/>
+      <c r="U9" s="69"/>
+      <c r="V9" s="69"/>
       <c r="W9" s="5"/>
     </row>
     <row r="10" spans="1:23" ht="5.0999999999999996" customHeight="1" x14ac:dyDescent="0.3">
@@ -1843,31 +1847,31 @@
       <c r="R10" s="2"/>
     </row>
     <row r="11" spans="1:23" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="79" t="s">
+      <c r="A11" s="69" t="s">
         <v>48</v>
       </c>
-      <c r="B11" s="79"/>
-      <c r="C11" s="79"/>
-      <c r="D11" s="90"/>
-      <c r="E11" s="90"/>
-      <c r="F11" s="90"/>
-      <c r="G11" s="90"/>
-      <c r="H11" s="90"/>
-      <c r="I11" s="90"/>
-      <c r="J11" s="90"/>
-      <c r="K11" s="90"/>
-      <c r="L11" s="90"/>
-      <c r="M11" s="90"/>
-      <c r="N11" s="90"/>
-      <c r="O11" s="90"/>
-      <c r="P11" s="90"/>
-      <c r="Q11" s="90"/>
-      <c r="R11" s="90"/>
-      <c r="S11" s="90"/>
-      <c r="T11" s="90"/>
-      <c r="U11" s="90"/>
-      <c r="V11" s="90"/>
-      <c r="W11" s="90"/>
+      <c r="B11" s="69"/>
+      <c r="C11" s="69"/>
+      <c r="D11" s="70"/>
+      <c r="E11" s="70"/>
+      <c r="F11" s="70"/>
+      <c r="G11" s="70"/>
+      <c r="H11" s="70"/>
+      <c r="I11" s="70"/>
+      <c r="J11" s="70"/>
+      <c r="K11" s="70"/>
+      <c r="L11" s="70"/>
+      <c r="M11" s="70"/>
+      <c r="N11" s="70"/>
+      <c r="O11" s="70"/>
+      <c r="P11" s="70"/>
+      <c r="Q11" s="70"/>
+      <c r="R11" s="70"/>
+      <c r="S11" s="70"/>
+      <c r="T11" s="70"/>
+      <c r="U11" s="70"/>
+      <c r="V11" s="70"/>
+      <c r="W11" s="70"/>
     </row>
     <row r="12" spans="1:23" ht="5.0999999999999996" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="11"/>
@@ -1875,31 +1879,31 @@
       <c r="C12" s="12"/>
     </row>
     <row r="13" spans="1:23" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="79" t="s">
+      <c r="A13" s="69" t="s">
         <v>25</v>
       </c>
-      <c r="B13" s="79"/>
-      <c r="C13" s="79"/>
-      <c r="D13" s="90"/>
-      <c r="E13" s="90"/>
-      <c r="F13" s="90"/>
-      <c r="G13" s="90"/>
-      <c r="H13" s="90"/>
-      <c r="I13" s="90"/>
-      <c r="J13" s="90"/>
-      <c r="K13" s="90"/>
-      <c r="L13" s="90"/>
-      <c r="M13" s="90"/>
-      <c r="N13" s="90"/>
-      <c r="O13" s="90"/>
-      <c r="P13" s="90"/>
-      <c r="Q13" s="90"/>
-      <c r="R13" s="90"/>
-      <c r="S13" s="90"/>
-      <c r="T13" s="90"/>
-      <c r="U13" s="90"/>
-      <c r="V13" s="90"/>
-      <c r="W13" s="90"/>
+      <c r="B13" s="69"/>
+      <c r="C13" s="69"/>
+      <c r="D13" s="70"/>
+      <c r="E13" s="70"/>
+      <c r="F13" s="70"/>
+      <c r="G13" s="70"/>
+      <c r="H13" s="70"/>
+      <c r="I13" s="70"/>
+      <c r="J13" s="70"/>
+      <c r="K13" s="70"/>
+      <c r="L13" s="70"/>
+      <c r="M13" s="70"/>
+      <c r="N13" s="70"/>
+      <c r="O13" s="70"/>
+      <c r="P13" s="70"/>
+      <c r="Q13" s="70"/>
+      <c r="R13" s="70"/>
+      <c r="S13" s="70"/>
+      <c r="T13" s="70"/>
+      <c r="U13" s="70"/>
+      <c r="V13" s="70"/>
+      <c r="W13" s="70"/>
     </row>
     <row r="14" spans="1:23" ht="5.0999999999999996" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="12"/>
@@ -1907,75 +1911,75 @@
       <c r="C14" s="12"/>
     </row>
     <row r="15" spans="1:23" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="79" t="s">
+      <c r="A15" s="69" t="s">
         <v>26</v>
       </c>
-      <c r="B15" s="79"/>
-      <c r="C15" s="79"/>
-      <c r="D15" s="90"/>
-      <c r="E15" s="90"/>
+      <c r="B15" s="69"/>
+      <c r="C15" s="69"/>
+      <c r="D15" s="70"/>
+      <c r="E15" s="70"/>
       <c r="F15" s="26"/>
       <c r="G15" s="24" t="s">
         <v>43</v>
       </c>
-      <c r="H15" s="90"/>
-      <c r="I15" s="90"/>
-      <c r="J15" s="90"/>
-      <c r="K15" s="79" t="s">
+      <c r="H15" s="70"/>
+      <c r="I15" s="70"/>
+      <c r="J15" s="70"/>
+      <c r="K15" s="69" t="s">
         <v>27</v>
       </c>
-      <c r="L15" s="79"/>
+      <c r="L15" s="69"/>
       <c r="M15" s="20"/>
-      <c r="N15" s="90"/>
-      <c r="O15" s="90"/>
-      <c r="P15" s="90"/>
-      <c r="Q15" s="87" t="s">
+      <c r="N15" s="70"/>
+      <c r="O15" s="70"/>
+      <c r="P15" s="70"/>
+      <c r="Q15" s="75" t="s">
         <v>28</v>
       </c>
-      <c r="R15" s="87"/>
-      <c r="S15" s="87"/>
-      <c r="T15" s="90"/>
-      <c r="U15" s="90"/>
-      <c r="V15" s="90"/>
-      <c r="W15" s="90"/>
+      <c r="R15" s="75"/>
+      <c r="S15" s="75"/>
+      <c r="T15" s="70"/>
+      <c r="U15" s="70"/>
+      <c r="V15" s="70"/>
+      <c r="W15" s="70"/>
     </row>
     <row r="16" spans="1:23" ht="5.0999999999999996" customHeight="1" x14ac:dyDescent="0.3">
       <c r="J16" s="2"/>
     </row>
     <row r="17" spans="1:92" ht="5.0999999999999996" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="10"/>
-      <c r="B17" s="91"/>
-      <c r="C17" s="91"/>
-      <c r="D17" s="91"/>
-      <c r="E17" s="91"/>
-      <c r="F17" s="91"/>
-      <c r="G17" s="91"/>
-      <c r="H17" s="91"/>
-      <c r="I17" s="91"/>
-      <c r="J17" s="91"/>
-      <c r="K17" s="91"/>
-      <c r="L17" s="91"/>
-      <c r="M17" s="91"/>
-      <c r="N17" s="91"/>
-      <c r="O17" s="91"/>
-      <c r="P17" s="91"/>
-      <c r="Q17" s="91"/>
-      <c r="R17" s="91"/>
-      <c r="S17" s="91"/>
-      <c r="T17" s="91"/>
-      <c r="U17" s="91"/>
-      <c r="V17" s="91"/>
-      <c r="W17" s="91"/>
+      <c r="B17" s="73"/>
+      <c r="C17" s="73"/>
+      <c r="D17" s="73"/>
+      <c r="E17" s="73"/>
+      <c r="F17" s="73"/>
+      <c r="G17" s="73"/>
+      <c r="H17" s="73"/>
+      <c r="I17" s="73"/>
+      <c r="J17" s="73"/>
+      <c r="K17" s="73"/>
+      <c r="L17" s="73"/>
+      <c r="M17" s="73"/>
+      <c r="N17" s="73"/>
+      <c r="O17" s="73"/>
+      <c r="P17" s="73"/>
+      <c r="Q17" s="73"/>
+      <c r="R17" s="73"/>
+      <c r="S17" s="73"/>
+      <c r="T17" s="73"/>
+      <c r="U17" s="73"/>
+      <c r="V17" s="73"/>
+      <c r="W17" s="73"/>
     </row>
     <row r="18" spans="1:92" ht="5.0999999999999996" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="19" spans="1:92" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="69" t="s">
+      <c r="A19" s="74" t="s">
         <v>18</v>
       </c>
-      <c r="B19" s="69"/>
-      <c r="C19" s="69"/>
-      <c r="D19" s="69"/>
-      <c r="E19" s="69"/>
+      <c r="B19" s="74"/>
+      <c r="C19" s="74"/>
+      <c r="D19" s="74"/>
+      <c r="E19" s="74"/>
       <c r="F19" s="18"/>
       <c r="G19" s="13"/>
       <c r="H19" s="13"/>
@@ -2065,31 +2069,31 @@
       <c r="CN19"/>
     </row>
     <row r="20" spans="1:92" s="1" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="92" t="s">
+      <c r="A20" s="76" t="s">
         <v>47</v>
       </c>
-      <c r="B20" s="92"/>
-      <c r="C20" s="92"/>
-      <c r="D20" s="92"/>
-      <c r="E20" s="92"/>
-      <c r="F20" s="92"/>
-      <c r="G20" s="92"/>
-      <c r="H20" s="92"/>
-      <c r="I20" s="92"/>
-      <c r="J20" s="92"/>
-      <c r="K20" s="92"/>
-      <c r="L20" s="92"/>
-      <c r="M20" s="92"/>
-      <c r="N20" s="92"/>
-      <c r="O20" s="92"/>
-      <c r="P20" s="92"/>
-      <c r="Q20" s="92"/>
-      <c r="R20" s="92"/>
-      <c r="S20" s="92"/>
-      <c r="T20" s="92"/>
-      <c r="U20" s="92"/>
-      <c r="V20" s="92"/>
-      <c r="W20" s="92"/>
+      <c r="B20" s="76"/>
+      <c r="C20" s="76"/>
+      <c r="D20" s="76"/>
+      <c r="E20" s="76"/>
+      <c r="F20" s="76"/>
+      <c r="G20" s="76"/>
+      <c r="H20" s="76"/>
+      <c r="I20" s="76"/>
+      <c r="J20" s="76"/>
+      <c r="K20" s="76"/>
+      <c r="L20" s="76"/>
+      <c r="M20" s="76"/>
+      <c r="N20" s="76"/>
+      <c r="O20" s="76"/>
+      <c r="P20" s="76"/>
+      <c r="Q20" s="76"/>
+      <c r="R20" s="76"/>
+      <c r="S20" s="76"/>
+      <c r="T20" s="76"/>
+      <c r="U20" s="76"/>
+      <c r="V20" s="76"/>
+      <c r="W20" s="76"/>
       <c r="X20"/>
       <c r="Y20"/>
       <c r="Z20"/>
@@ -2161,29 +2165,29 @@
       <c r="CN20"/>
     </row>
     <row r="21" spans="1:92" s="1" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="92"/>
-      <c r="B21" s="92"/>
-      <c r="C21" s="92"/>
-      <c r="D21" s="92"/>
-      <c r="E21" s="92"/>
-      <c r="F21" s="92"/>
-      <c r="G21" s="92"/>
-      <c r="H21" s="92"/>
-      <c r="I21" s="92"/>
-      <c r="J21" s="92"/>
-      <c r="K21" s="92"/>
-      <c r="L21" s="92"/>
-      <c r="M21" s="92"/>
-      <c r="N21" s="92"/>
-      <c r="O21" s="92"/>
-      <c r="P21" s="92"/>
-      <c r="Q21" s="92"/>
-      <c r="R21" s="92"/>
-      <c r="S21" s="92"/>
-      <c r="T21" s="92"/>
-      <c r="U21" s="92"/>
-      <c r="V21" s="92"/>
-      <c r="W21" s="92"/>
+      <c r="A21" s="76"/>
+      <c r="B21" s="76"/>
+      <c r="C21" s="76"/>
+      <c r="D21" s="76"/>
+      <c r="E21" s="76"/>
+      <c r="F21" s="76"/>
+      <c r="G21" s="76"/>
+      <c r="H21" s="76"/>
+      <c r="I21" s="76"/>
+      <c r="J21" s="76"/>
+      <c r="K21" s="76"/>
+      <c r="L21" s="76"/>
+      <c r="M21" s="76"/>
+      <c r="N21" s="76"/>
+      <c r="O21" s="76"/>
+      <c r="P21" s="76"/>
+      <c r="Q21" s="76"/>
+      <c r="R21" s="76"/>
+      <c r="S21" s="76"/>
+      <c r="T21" s="76"/>
+      <c r="U21" s="76"/>
+      <c r="V21" s="76"/>
+      <c r="W21" s="76"/>
       <c r="X21"/>
       <c r="Y21"/>
       <c r="Z21"/>
@@ -2255,29 +2259,29 @@
       <c r="CN21"/>
     </row>
     <row r="22" spans="1:92" s="1" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="92"/>
-      <c r="B22" s="92"/>
-      <c r="C22" s="92"/>
-      <c r="D22" s="92"/>
-      <c r="E22" s="92"/>
-      <c r="F22" s="92"/>
-      <c r="G22" s="92"/>
-      <c r="H22" s="92"/>
-      <c r="I22" s="92"/>
-      <c r="J22" s="92"/>
-      <c r="K22" s="92"/>
-      <c r="L22" s="92"/>
-      <c r="M22" s="92"/>
-      <c r="N22" s="92"/>
-      <c r="O22" s="92"/>
-      <c r="P22" s="92"/>
-      <c r="Q22" s="92"/>
-      <c r="R22" s="92"/>
-      <c r="S22" s="92"/>
-      <c r="T22" s="92"/>
-      <c r="U22" s="92"/>
-      <c r="V22" s="92"/>
-      <c r="W22" s="92"/>
+      <c r="A22" s="76"/>
+      <c r="B22" s="76"/>
+      <c r="C22" s="76"/>
+      <c r="D22" s="76"/>
+      <c r="E22" s="76"/>
+      <c r="F22" s="76"/>
+      <c r="G22" s="76"/>
+      <c r="H22" s="76"/>
+      <c r="I22" s="76"/>
+      <c r="J22" s="76"/>
+      <c r="K22" s="76"/>
+      <c r="L22" s="76"/>
+      <c r="M22" s="76"/>
+      <c r="N22" s="76"/>
+      <c r="O22" s="76"/>
+      <c r="P22" s="76"/>
+      <c r="Q22" s="76"/>
+      <c r="R22" s="76"/>
+      <c r="S22" s="76"/>
+      <c r="T22" s="76"/>
+      <c r="U22" s="76"/>
+      <c r="V22" s="76"/>
+      <c r="W22" s="76"/>
       <c r="X22"/>
       <c r="Y22"/>
       <c r="Z22"/>
@@ -2349,29 +2353,29 @@
       <c r="CN22"/>
     </row>
     <row r="23" spans="1:92" s="1" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="92"/>
-      <c r="B23" s="92"/>
-      <c r="C23" s="92"/>
-      <c r="D23" s="92"/>
-      <c r="E23" s="92"/>
-      <c r="F23" s="92"/>
-      <c r="G23" s="92"/>
-      <c r="H23" s="92"/>
-      <c r="I23" s="92"/>
-      <c r="J23" s="92"/>
-      <c r="K23" s="92"/>
-      <c r="L23" s="92"/>
-      <c r="M23" s="92"/>
-      <c r="N23" s="92"/>
-      <c r="O23" s="92"/>
-      <c r="P23" s="92"/>
-      <c r="Q23" s="92"/>
-      <c r="R23" s="92"/>
-      <c r="S23" s="92"/>
-      <c r="T23" s="92"/>
-      <c r="U23" s="92"/>
-      <c r="V23" s="92"/>
-      <c r="W23" s="92"/>
+      <c r="A23" s="76"/>
+      <c r="B23" s="76"/>
+      <c r="C23" s="76"/>
+      <c r="D23" s="76"/>
+      <c r="E23" s="76"/>
+      <c r="F23" s="76"/>
+      <c r="G23" s="76"/>
+      <c r="H23" s="76"/>
+      <c r="I23" s="76"/>
+      <c r="J23" s="76"/>
+      <c r="K23" s="76"/>
+      <c r="L23" s="76"/>
+      <c r="M23" s="76"/>
+      <c r="N23" s="76"/>
+      <c r="O23" s="76"/>
+      <c r="P23" s="76"/>
+      <c r="Q23" s="76"/>
+      <c r="R23" s="76"/>
+      <c r="S23" s="76"/>
+      <c r="T23" s="76"/>
+      <c r="U23" s="76"/>
+      <c r="V23" s="76"/>
+      <c r="W23" s="76"/>
       <c r="X23"/>
       <c r="Y23"/>
       <c r="Z23"/>
@@ -2443,29 +2447,29 @@
       <c r="CN23"/>
     </row>
     <row r="24" spans="1:92" s="1" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="92"/>
-      <c r="B24" s="92"/>
-      <c r="C24" s="92"/>
-      <c r="D24" s="92"/>
-      <c r="E24" s="92"/>
-      <c r="F24" s="92"/>
-      <c r="G24" s="92"/>
-      <c r="H24" s="92"/>
-      <c r="I24" s="92"/>
-      <c r="J24" s="92"/>
-      <c r="K24" s="92"/>
-      <c r="L24" s="92"/>
-      <c r="M24" s="92"/>
-      <c r="N24" s="92"/>
-      <c r="O24" s="92"/>
-      <c r="P24" s="92"/>
-      <c r="Q24" s="92"/>
-      <c r="R24" s="92"/>
-      <c r="S24" s="92"/>
-      <c r="T24" s="92"/>
-      <c r="U24" s="92"/>
-      <c r="V24" s="92"/>
-      <c r="W24" s="92"/>
+      <c r="A24" s="76"/>
+      <c r="B24" s="76"/>
+      <c r="C24" s="76"/>
+      <c r="D24" s="76"/>
+      <c r="E24" s="76"/>
+      <c r="F24" s="76"/>
+      <c r="G24" s="76"/>
+      <c r="H24" s="76"/>
+      <c r="I24" s="76"/>
+      <c r="J24" s="76"/>
+      <c r="K24" s="76"/>
+      <c r="L24" s="76"/>
+      <c r="M24" s="76"/>
+      <c r="N24" s="76"/>
+      <c r="O24" s="76"/>
+      <c r="P24" s="76"/>
+      <c r="Q24" s="76"/>
+      <c r="R24" s="76"/>
+      <c r="S24" s="76"/>
+      <c r="T24" s="76"/>
+      <c r="U24" s="76"/>
+      <c r="V24" s="76"/>
+      <c r="W24" s="76"/>
       <c r="X24"/>
       <c r="Y24"/>
       <c r="Z24"/>
@@ -2537,29 +2541,29 @@
       <c r="CN24"/>
     </row>
     <row r="25" spans="1:92" s="1" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="92"/>
-      <c r="B25" s="92"/>
-      <c r="C25" s="92"/>
-      <c r="D25" s="92"/>
-      <c r="E25" s="92"/>
-      <c r="F25" s="92"/>
-      <c r="G25" s="92"/>
-      <c r="H25" s="92"/>
-      <c r="I25" s="92"/>
-      <c r="J25" s="92"/>
-      <c r="K25" s="92"/>
-      <c r="L25" s="92"/>
-      <c r="M25" s="92"/>
-      <c r="N25" s="92"/>
-      <c r="O25" s="92"/>
-      <c r="P25" s="92"/>
-      <c r="Q25" s="92"/>
-      <c r="R25" s="92"/>
-      <c r="S25" s="92"/>
-      <c r="T25" s="92"/>
-      <c r="U25" s="92"/>
-      <c r="V25" s="92"/>
-      <c r="W25" s="92"/>
+      <c r="A25" s="76"/>
+      <c r="B25" s="76"/>
+      <c r="C25" s="76"/>
+      <c r="D25" s="76"/>
+      <c r="E25" s="76"/>
+      <c r="F25" s="76"/>
+      <c r="G25" s="76"/>
+      <c r="H25" s="76"/>
+      <c r="I25" s="76"/>
+      <c r="J25" s="76"/>
+      <c r="K25" s="76"/>
+      <c r="L25" s="76"/>
+      <c r="M25" s="76"/>
+      <c r="N25" s="76"/>
+      <c r="O25" s="76"/>
+      <c r="P25" s="76"/>
+      <c r="Q25" s="76"/>
+      <c r="R25" s="76"/>
+      <c r="S25" s="76"/>
+      <c r="T25" s="76"/>
+      <c r="U25" s="76"/>
+      <c r="V25" s="76"/>
+      <c r="W25" s="76"/>
       <c r="X25"/>
       <c r="Y25"/>
       <c r="Z25"/>
@@ -2631,29 +2635,29 @@
       <c r="CN25"/>
     </row>
     <row r="26" spans="1:92" s="1" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="92"/>
-      <c r="B26" s="92"/>
-      <c r="C26" s="92"/>
-      <c r="D26" s="92"/>
-      <c r="E26" s="92"/>
-      <c r="F26" s="92"/>
-      <c r="G26" s="92"/>
-      <c r="H26" s="92"/>
-      <c r="I26" s="92"/>
-      <c r="J26" s="92"/>
-      <c r="K26" s="92"/>
-      <c r="L26" s="92"/>
-      <c r="M26" s="92"/>
-      <c r="N26" s="92"/>
-      <c r="O26" s="92"/>
-      <c r="P26" s="92"/>
-      <c r="Q26" s="92"/>
-      <c r="R26" s="92"/>
-      <c r="S26" s="92"/>
-      <c r="T26" s="92"/>
-      <c r="U26" s="92"/>
-      <c r="V26" s="92"/>
-      <c r="W26" s="92"/>
+      <c r="A26" s="76"/>
+      <c r="B26" s="76"/>
+      <c r="C26" s="76"/>
+      <c r="D26" s="76"/>
+      <c r="E26" s="76"/>
+      <c r="F26" s="76"/>
+      <c r="G26" s="76"/>
+      <c r="H26" s="76"/>
+      <c r="I26" s="76"/>
+      <c r="J26" s="76"/>
+      <c r="K26" s="76"/>
+      <c r="L26" s="76"/>
+      <c r="M26" s="76"/>
+      <c r="N26" s="76"/>
+      <c r="O26" s="76"/>
+      <c r="P26" s="76"/>
+      <c r="Q26" s="76"/>
+      <c r="R26" s="76"/>
+      <c r="S26" s="76"/>
+      <c r="T26" s="76"/>
+      <c r="U26" s="76"/>
+      <c r="V26" s="76"/>
+      <c r="W26" s="76"/>
       <c r="X26"/>
       <c r="Y26"/>
       <c r="Z26"/>
@@ -2725,29 +2729,29 @@
       <c r="CN26"/>
     </row>
     <row r="27" spans="1:92" s="1" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="92"/>
-      <c r="B27" s="92"/>
-      <c r="C27" s="92"/>
-      <c r="D27" s="92"/>
-      <c r="E27" s="92"/>
-      <c r="F27" s="92"/>
-      <c r="G27" s="92"/>
-      <c r="H27" s="92"/>
-      <c r="I27" s="92"/>
-      <c r="J27" s="92"/>
-      <c r="K27" s="92"/>
-      <c r="L27" s="92"/>
-      <c r="M27" s="92"/>
-      <c r="N27" s="92"/>
-      <c r="O27" s="92"/>
-      <c r="P27" s="92"/>
-      <c r="Q27" s="92"/>
-      <c r="R27" s="92"/>
-      <c r="S27" s="92"/>
-      <c r="T27" s="92"/>
-      <c r="U27" s="92"/>
-      <c r="V27" s="92"/>
-      <c r="W27" s="92"/>
+      <c r="A27" s="76"/>
+      <c r="B27" s="76"/>
+      <c r="C27" s="76"/>
+      <c r="D27" s="76"/>
+      <c r="E27" s="76"/>
+      <c r="F27" s="76"/>
+      <c r="G27" s="76"/>
+      <c r="H27" s="76"/>
+      <c r="I27" s="76"/>
+      <c r="J27" s="76"/>
+      <c r="K27" s="76"/>
+      <c r="L27" s="76"/>
+      <c r="M27" s="76"/>
+      <c r="N27" s="76"/>
+      <c r="O27" s="76"/>
+      <c r="P27" s="76"/>
+      <c r="Q27" s="76"/>
+      <c r="R27" s="76"/>
+      <c r="S27" s="76"/>
+      <c r="T27" s="76"/>
+      <c r="U27" s="76"/>
+      <c r="V27" s="76"/>
+      <c r="W27" s="76"/>
       <c r="X27"/>
       <c r="Y27"/>
       <c r="Z27"/>
@@ -2819,29 +2823,29 @@
       <c r="CN27"/>
     </row>
     <row r="28" spans="1:92" s="1" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="92"/>
-      <c r="B28" s="92"/>
-      <c r="C28" s="92"/>
-      <c r="D28" s="92"/>
-      <c r="E28" s="92"/>
-      <c r="F28" s="92"/>
-      <c r="G28" s="92"/>
-      <c r="H28" s="92"/>
-      <c r="I28" s="92"/>
-      <c r="J28" s="92"/>
-      <c r="K28" s="92"/>
-      <c r="L28" s="92"/>
-      <c r="M28" s="92"/>
-      <c r="N28" s="92"/>
-      <c r="O28" s="92"/>
-      <c r="P28" s="92"/>
-      <c r="Q28" s="92"/>
-      <c r="R28" s="92"/>
-      <c r="S28" s="92"/>
-      <c r="T28" s="92"/>
-      <c r="U28" s="92"/>
-      <c r="V28" s="92"/>
-      <c r="W28" s="92"/>
+      <c r="A28" s="76"/>
+      <c r="B28" s="76"/>
+      <c r="C28" s="76"/>
+      <c r="D28" s="76"/>
+      <c r="E28" s="76"/>
+      <c r="F28" s="76"/>
+      <c r="G28" s="76"/>
+      <c r="H28" s="76"/>
+      <c r="I28" s="76"/>
+      <c r="J28" s="76"/>
+      <c r="K28" s="76"/>
+      <c r="L28" s="76"/>
+      <c r="M28" s="76"/>
+      <c r="N28" s="76"/>
+      <c r="O28" s="76"/>
+      <c r="P28" s="76"/>
+      <c r="Q28" s="76"/>
+      <c r="R28" s="76"/>
+      <c r="S28" s="76"/>
+      <c r="T28" s="76"/>
+      <c r="U28" s="76"/>
+      <c r="V28" s="76"/>
+      <c r="W28" s="76"/>
       <c r="X28"/>
       <c r="Y28"/>
       <c r="Z28"/>
@@ -2913,29 +2917,29 @@
       <c r="CN28"/>
     </row>
     <row r="29" spans="1:92" s="1" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="92"/>
-      <c r="B29" s="92"/>
-      <c r="C29" s="92"/>
-      <c r="D29" s="92"/>
-      <c r="E29" s="92"/>
-      <c r="F29" s="92"/>
-      <c r="G29" s="92"/>
-      <c r="H29" s="92"/>
-      <c r="I29" s="92"/>
-      <c r="J29" s="92"/>
-      <c r="K29" s="92"/>
-      <c r="L29" s="92"/>
-      <c r="M29" s="92"/>
-      <c r="N29" s="92"/>
-      <c r="O29" s="92"/>
-      <c r="P29" s="92"/>
-      <c r="Q29" s="92"/>
-      <c r="R29" s="92"/>
-      <c r="S29" s="92"/>
-      <c r="T29" s="92"/>
-      <c r="U29" s="92"/>
-      <c r="V29" s="92"/>
-      <c r="W29" s="92"/>
+      <c r="A29" s="76"/>
+      <c r="B29" s="76"/>
+      <c r="C29" s="76"/>
+      <c r="D29" s="76"/>
+      <c r="E29" s="76"/>
+      <c r="F29" s="76"/>
+      <c r="G29" s="76"/>
+      <c r="H29" s="76"/>
+      <c r="I29" s="76"/>
+      <c r="J29" s="76"/>
+      <c r="K29" s="76"/>
+      <c r="L29" s="76"/>
+      <c r="M29" s="76"/>
+      <c r="N29" s="76"/>
+      <c r="O29" s="76"/>
+      <c r="P29" s="76"/>
+      <c r="Q29" s="76"/>
+      <c r="R29" s="76"/>
+      <c r="S29" s="76"/>
+      <c r="T29" s="76"/>
+      <c r="U29" s="76"/>
+      <c r="V29" s="76"/>
+      <c r="W29" s="76"/>
       <c r="X29"/>
       <c r="Y29"/>
       <c r="Z29"/>
@@ -3007,29 +3011,29 @@
       <c r="CN29"/>
     </row>
     <row r="30" spans="1:92" s="1" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="92"/>
-      <c r="B30" s="92"/>
-      <c r="C30" s="92"/>
-      <c r="D30" s="92"/>
-      <c r="E30" s="92"/>
-      <c r="F30" s="92"/>
-      <c r="G30" s="92"/>
-      <c r="H30" s="92"/>
-      <c r="I30" s="92"/>
-      <c r="J30" s="92"/>
-      <c r="K30" s="92"/>
-      <c r="L30" s="92"/>
-      <c r="M30" s="92"/>
-      <c r="N30" s="92"/>
-      <c r="O30" s="92"/>
-      <c r="P30" s="92"/>
-      <c r="Q30" s="92"/>
-      <c r="R30" s="92"/>
-      <c r="S30" s="92"/>
-      <c r="T30" s="92"/>
-      <c r="U30" s="92"/>
-      <c r="V30" s="92"/>
-      <c r="W30" s="92"/>
+      <c r="A30" s="76"/>
+      <c r="B30" s="76"/>
+      <c r="C30" s="76"/>
+      <c r="D30" s="76"/>
+      <c r="E30" s="76"/>
+      <c r="F30" s="76"/>
+      <c r="G30" s="76"/>
+      <c r="H30" s="76"/>
+      <c r="I30" s="76"/>
+      <c r="J30" s="76"/>
+      <c r="K30" s="76"/>
+      <c r="L30" s="76"/>
+      <c r="M30" s="76"/>
+      <c r="N30" s="76"/>
+      <c r="O30" s="76"/>
+      <c r="P30" s="76"/>
+      <c r="Q30" s="76"/>
+      <c r="R30" s="76"/>
+      <c r="S30" s="76"/>
+      <c r="T30" s="76"/>
+      <c r="U30" s="76"/>
+      <c r="V30" s="76"/>
+      <c r="W30" s="76"/>
       <c r="X30"/>
       <c r="Y30"/>
       <c r="Z30"/>
@@ -3101,29 +3105,29 @@
       <c r="CN30"/>
     </row>
     <row r="31" spans="1:92" s="1" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="92"/>
-      <c r="B31" s="92"/>
-      <c r="C31" s="92"/>
-      <c r="D31" s="92"/>
-      <c r="E31" s="92"/>
-      <c r="F31" s="92"/>
-      <c r="G31" s="92"/>
-      <c r="H31" s="92"/>
-      <c r="I31" s="92"/>
-      <c r="J31" s="92"/>
-      <c r="K31" s="92"/>
-      <c r="L31" s="92"/>
-      <c r="M31" s="92"/>
-      <c r="N31" s="92"/>
-      <c r="O31" s="92"/>
-      <c r="P31" s="92"/>
-      <c r="Q31" s="92"/>
-      <c r="R31" s="92"/>
-      <c r="S31" s="92"/>
-      <c r="T31" s="92"/>
-      <c r="U31" s="92"/>
-      <c r="V31" s="92"/>
-      <c r="W31" s="92"/>
+      <c r="A31" s="76"/>
+      <c r="B31" s="76"/>
+      <c r="C31" s="76"/>
+      <c r="D31" s="76"/>
+      <c r="E31" s="76"/>
+      <c r="F31" s="76"/>
+      <c r="G31" s="76"/>
+      <c r="H31" s="76"/>
+      <c r="I31" s="76"/>
+      <c r="J31" s="76"/>
+      <c r="K31" s="76"/>
+      <c r="L31" s="76"/>
+      <c r="M31" s="76"/>
+      <c r="N31" s="76"/>
+      <c r="O31" s="76"/>
+      <c r="P31" s="76"/>
+      <c r="Q31" s="76"/>
+      <c r="R31" s="76"/>
+      <c r="S31" s="76"/>
+      <c r="T31" s="76"/>
+      <c r="U31" s="76"/>
+      <c r="V31" s="76"/>
+      <c r="W31" s="76"/>
       <c r="X31"/>
       <c r="Y31"/>
       <c r="Z31"/>
@@ -3195,29 +3199,29 @@
       <c r="CN31"/>
     </row>
     <row r="32" spans="1:92" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="92"/>
-      <c r="B32" s="92"/>
-      <c r="C32" s="92"/>
-      <c r="D32" s="92"/>
-      <c r="E32" s="92"/>
-      <c r="F32" s="92"/>
-      <c r="G32" s="92"/>
-      <c r="H32" s="92"/>
-      <c r="I32" s="92"/>
-      <c r="J32" s="92"/>
-      <c r="K32" s="92"/>
-      <c r="L32" s="92"/>
-      <c r="M32" s="92"/>
-      <c r="N32" s="92"/>
-      <c r="O32" s="92"/>
-      <c r="P32" s="92"/>
-      <c r="Q32" s="92"/>
-      <c r="R32" s="92"/>
-      <c r="S32" s="92"/>
-      <c r="T32" s="92"/>
-      <c r="U32" s="92"/>
-      <c r="V32" s="92"/>
-      <c r="W32" s="92"/>
+      <c r="A32" s="76"/>
+      <c r="B32" s="76"/>
+      <c r="C32" s="76"/>
+      <c r="D32" s="76"/>
+      <c r="E32" s="76"/>
+      <c r="F32" s="76"/>
+      <c r="G32" s="76"/>
+      <c r="H32" s="76"/>
+      <c r="I32" s="76"/>
+      <c r="J32" s="76"/>
+      <c r="K32" s="76"/>
+      <c r="L32" s="76"/>
+      <c r="M32" s="76"/>
+      <c r="N32" s="76"/>
+      <c r="O32" s="76"/>
+      <c r="P32" s="76"/>
+      <c r="Q32" s="76"/>
+      <c r="R32" s="76"/>
+      <c r="S32" s="76"/>
+      <c r="T32" s="76"/>
+      <c r="U32" s="76"/>
+      <c r="V32" s="76"/>
+      <c r="W32" s="76"/>
     </row>
     <row r="33" spans="1:23" ht="5.0999999999999996" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="10"/>
@@ -3252,64 +3256,64 @@
     </row>
     <row r="36" spans="1:23" ht="5.0999999999999996" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="37" spans="1:23" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="79" t="s">
+      <c r="A37" s="69" t="s">
         <v>30</v>
       </c>
-      <c r="B37" s="79"/>
-      <c r="C37" s="79"/>
-      <c r="D37" s="90"/>
-      <c r="E37" s="90"/>
-      <c r="F37" s="90"/>
-      <c r="G37" s="90"/>
-      <c r="I37" s="79" t="s">
+      <c r="B37" s="69"/>
+      <c r="C37" s="69"/>
+      <c r="D37" s="70"/>
+      <c r="E37" s="70"/>
+      <c r="F37" s="70"/>
+      <c r="G37" s="70"/>
+      <c r="I37" s="69" t="s">
         <v>19</v>
       </c>
-      <c r="J37" s="79"/>
-      <c r="K37" s="79"/>
-      <c r="L37" s="93"/>
-      <c r="M37" s="93"/>
-      <c r="N37" s="93"/>
-      <c r="Q37" s="79" t="s">
+      <c r="J37" s="69"/>
+      <c r="K37" s="69"/>
+      <c r="L37" s="77"/>
+      <c r="M37" s="77"/>
+      <c r="N37" s="77"/>
+      <c r="Q37" s="69" t="s">
         <v>24</v>
       </c>
-      <c r="R37" s="79"/>
-      <c r="S37" s="79"/>
-      <c r="T37" s="79"/>
-      <c r="U37" s="94"/>
-      <c r="V37" s="94"/>
-      <c r="W37" s="94"/>
+      <c r="R37" s="69"/>
+      <c r="S37" s="69"/>
+      <c r="T37" s="69"/>
+      <c r="U37" s="78"/>
+      <c r="V37" s="78"/>
+      <c r="W37" s="78"/>
     </row>
     <row r="38" spans="1:23" ht="5.0999999999999996" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="39" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="87" t="s">
+      <c r="A39" s="75" t="s">
         <v>3</v>
       </c>
-      <c r="B39" s="87"/>
-      <c r="C39" s="87"/>
-      <c r="D39" s="87"/>
-      <c r="E39" s="87"/>
-      <c r="F39" s="87"/>
-      <c r="G39" s="87"/>
-      <c r="H39" s="87"/>
-      <c r="I39" s="87" t="s">
+      <c r="B39" s="75"/>
+      <c r="C39" s="75"/>
+      <c r="D39" s="75"/>
+      <c r="E39" s="75"/>
+      <c r="F39" s="75"/>
+      <c r="G39" s="75"/>
+      <c r="H39" s="75"/>
+      <c r="I39" s="75" t="s">
         <v>52</v>
       </c>
-      <c r="J39" s="87"/>
-      <c r="K39" s="87"/>
-      <c r="L39" s="87"/>
-      <c r="M39" s="87"/>
-      <c r="N39" s="87"/>
-      <c r="O39" s="87"/>
-      <c r="P39" s="87"/>
-      <c r="Q39" s="87" t="s">
+      <c r="J39" s="75"/>
+      <c r="K39" s="75"/>
+      <c r="L39" s="75"/>
+      <c r="M39" s="75"/>
+      <c r="N39" s="75"/>
+      <c r="O39" s="75"/>
+      <c r="P39" s="75"/>
+      <c r="Q39" s="75" t="s">
         <v>4</v>
       </c>
-      <c r="R39" s="87"/>
-      <c r="S39" s="87"/>
-      <c r="T39" s="87"/>
-      <c r="U39" s="87"/>
-      <c r="V39" s="87"/>
-      <c r="W39" s="87"/>
+      <c r="R39" s="75"/>
+      <c r="S39" s="75"/>
+      <c r="T39" s="75"/>
+      <c r="U39" s="75"/>
+      <c r="V39" s="75"/>
+      <c r="W39" s="75"/>
     </row>
     <row r="40" spans="1:23" ht="5.0999999999999996" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="41" spans="1:23" ht="5.0999999999999996" customHeight="1" x14ac:dyDescent="0.3">
@@ -3338,30 +3342,30 @@
     </row>
     <row r="42" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B42" s="15"/>
-      <c r="C42" s="88" t="s">
+      <c r="C42" s="79" t="s">
         <v>15</v>
       </c>
-      <c r="D42" s="89"/>
-      <c r="E42" s="89"/>
-      <c r="F42" s="89"/>
-      <c r="G42" s="89"/>
+      <c r="D42" s="80"/>
+      <c r="E42" s="80"/>
+      <c r="F42" s="80"/>
+      <c r="G42" s="80"/>
       <c r="I42" s="16"/>
       <c r="J42" s="15"/>
-      <c r="K42" s="71" t="s">
+      <c r="K42" s="81" t="s">
         <v>6</v>
       </c>
-      <c r="L42" s="72"/>
-      <c r="M42" s="72"/>
-      <c r="N42" s="72"/>
-      <c r="O42" s="72"/>
+      <c r="L42" s="82"/>
+      <c r="M42" s="82"/>
+      <c r="N42" s="82"/>
+      <c r="O42" s="82"/>
       <c r="Q42" s="16"/>
       <c r="R42" s="15"/>
-      <c r="S42" s="73" t="s">
+      <c r="S42" s="83" t="s">
         <v>9</v>
       </c>
-      <c r="T42" s="74"/>
-      <c r="U42" s="74"/>
-      <c r="V42" s="74"/>
+      <c r="T42" s="84"/>
+      <c r="U42" s="84"/>
+      <c r="V42" s="84"/>
     </row>
     <row r="43" spans="1:23" ht="5.0999999999999996" customHeight="1" x14ac:dyDescent="0.3">
       <c r="I43" s="16"/>
@@ -3378,21 +3382,21 @@
       <c r="G44" s="8"/>
       <c r="I44" s="16"/>
       <c r="J44" s="15"/>
-      <c r="K44" s="71" t="s">
+      <c r="K44" s="81" t="s">
         <v>8</v>
       </c>
-      <c r="L44" s="72"/>
-      <c r="M44" s="72"/>
-      <c r="N44" s="72"/>
-      <c r="O44" s="72"/>
+      <c r="L44" s="82"/>
+      <c r="M44" s="82"/>
+      <c r="N44" s="82"/>
+      <c r="O44" s="82"/>
       <c r="Q44" s="16"/>
       <c r="R44" s="15"/>
-      <c r="S44" s="73" t="s">
+      <c r="S44" s="83" t="s">
         <v>10</v>
       </c>
-      <c r="T44" s="74"/>
-      <c r="U44" s="74"/>
-      <c r="V44" s="74"/>
+      <c r="T44" s="84"/>
+      <c r="U44" s="84"/>
+      <c r="V44" s="84"/>
     </row>
     <row r="45" spans="1:23" ht="5.0999999999999996" customHeight="1" x14ac:dyDescent="0.3">
       <c r="I45" s="16"/>
@@ -3401,21 +3405,21 @@
     <row r="46" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="I46" s="16"/>
       <c r="J46" s="15"/>
-      <c r="K46" s="71" t="s">
+      <c r="K46" s="81" t="s">
         <v>5</v>
       </c>
-      <c r="L46" s="72"/>
-      <c r="M46" s="72"/>
-      <c r="N46" s="72"/>
-      <c r="O46" s="72"/>
+      <c r="L46" s="82"/>
+      <c r="M46" s="82"/>
+      <c r="N46" s="82"/>
+      <c r="O46" s="82"/>
       <c r="Q46" s="16"/>
       <c r="R46" s="15"/>
-      <c r="S46" s="73" t="s">
+      <c r="S46" s="83" t="s">
         <v>11</v>
       </c>
-      <c r="T46" s="74"/>
-      <c r="U46" s="74"/>
-      <c r="V46" s="74"/>
+      <c r="T46" s="84"/>
+      <c r="U46" s="84"/>
+      <c r="V46" s="84"/>
     </row>
     <row r="47" spans="1:23" ht="5.0999999999999996" customHeight="1" x14ac:dyDescent="0.3">
       <c r="I47" s="16"/>
@@ -3424,22 +3428,22 @@
     <row r="48" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="I48" s="16"/>
       <c r="J48" s="15"/>
-      <c r="K48" s="71" t="s">
+      <c r="K48" s="81" t="s">
         <v>7</v>
       </c>
-      <c r="L48" s="72"/>
-      <c r="M48" s="72"/>
-      <c r="N48" s="72"/>
-      <c r="O48" s="72"/>
+      <c r="L48" s="82"/>
+      <c r="M48" s="82"/>
+      <c r="N48" s="82"/>
+      <c r="O48" s="82"/>
       <c r="Q48" s="16"/>
       <c r="R48" s="15"/>
-      <c r="S48" s="73" t="s">
+      <c r="S48" s="83" t="s">
         <v>34</v>
       </c>
-      <c r="T48" s="74"/>
-      <c r="U48" s="74"/>
-      <c r="V48" s="74"/>
-      <c r="W48" s="74"/>
+      <c r="T48" s="84"/>
+      <c r="U48" s="84"/>
+      <c r="V48" s="84"/>
+      <c r="W48" s="84"/>
     </row>
     <row r="49" spans="1:23" ht="5.0999999999999996" customHeight="1" x14ac:dyDescent="0.3">
       <c r="I49" s="16"/>
@@ -3448,20 +3452,20 @@
     <row r="50" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="I50" s="16"/>
       <c r="J50" s="15"/>
-      <c r="K50" s="71" t="s">
+      <c r="K50" s="81" t="s">
         <v>17</v>
       </c>
-      <c r="L50" s="72"/>
-      <c r="M50" s="72"/>
-      <c r="N50" s="72"/>
-      <c r="O50" s="72"/>
+      <c r="L50" s="82"/>
+      <c r="M50" s="82"/>
+      <c r="N50" s="82"/>
+      <c r="O50" s="82"/>
       <c r="Q50" s="16"/>
       <c r="R50" s="15"/>
-      <c r="S50" s="73" t="s">
+      <c r="S50" s="83" t="s">
         <v>12</v>
       </c>
-      <c r="T50" s="74"/>
-      <c r="U50" s="74"/>
+      <c r="T50" s="84"/>
+      <c r="U50" s="84"/>
     </row>
     <row r="51" spans="1:23" ht="5.0999999999999996" customHeight="1" x14ac:dyDescent="0.3">
       <c r="I51" s="16"/>
@@ -3469,12 +3473,12 @@
     </row>
     <row r="52" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="I52" s="16"/>
-      <c r="J52" s="75"/>
-      <c r="K52" s="75"/>
-      <c r="L52" s="75"/>
-      <c r="M52" s="75"/>
-      <c r="N52" s="75"/>
-      <c r="O52" s="75"/>
+      <c r="J52" s="96"/>
+      <c r="K52" s="96"/>
+      <c r="L52" s="96"/>
+      <c r="M52" s="96"/>
+      <c r="N52" s="96"/>
+      <c r="O52" s="96"/>
       <c r="Q52" s="16"/>
       <c r="R52" s="15"/>
       <c r="S52" s="21" t="s">
@@ -3489,11 +3493,11 @@
     <row r="54" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="Q54" s="16"/>
       <c r="R54" s="15"/>
-      <c r="S54" s="73" t="s">
+      <c r="S54" s="83" t="s">
         <v>14</v>
       </c>
-      <c r="T54" s="74"/>
-      <c r="U54" s="74"/>
+      <c r="T54" s="84"/>
+      <c r="U54" s="84"/>
     </row>
     <row r="55" spans="1:23" ht="5.0999999999999996" customHeight="1" x14ac:dyDescent="0.3">
       <c r="Q55" s="16"/>
@@ -3501,24 +3505,24 @@
     <row r="56" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="Q56" s="16"/>
       <c r="R56" s="15"/>
-      <c r="S56" s="71" t="s">
+      <c r="S56" s="81" t="s">
         <v>17</v>
       </c>
-      <c r="T56" s="72"/>
-      <c r="U56" s="72"/>
-      <c r="V56" s="72"/>
+      <c r="T56" s="82"/>
+      <c r="U56" s="82"/>
+      <c r="V56" s="82"/>
     </row>
     <row r="57" spans="1:23" ht="5.0999999999999996" customHeight="1" x14ac:dyDescent="0.3">
       <c r="Q57" s="16"/>
     </row>
     <row r="58" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="Q58" s="16"/>
-      <c r="R58" s="75"/>
-      <c r="S58" s="75"/>
-      <c r="T58" s="75"/>
-      <c r="U58" s="75"/>
-      <c r="V58" s="75"/>
-      <c r="W58" s="75"/>
+      <c r="R58" s="96"/>
+      <c r="S58" s="96"/>
+      <c r="T58" s="96"/>
+      <c r="U58" s="96"/>
+      <c r="V58" s="96"/>
+      <c r="W58" s="96"/>
     </row>
     <row r="59" spans="1:23" ht="5.0999999999999996" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="60" spans="1:23" ht="5.0999999999999996" customHeight="1" x14ac:dyDescent="0.3">
@@ -3548,24 +3552,24 @@
     </row>
     <row r="61" spans="1:23" ht="5.0999999999999996" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="62" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A62" s="69" t="s">
+      <c r="A62" s="74" t="s">
         <v>38</v>
       </c>
-      <c r="B62" s="69"/>
-      <c r="C62" s="69"/>
-      <c r="D62" s="69"/>
-      <c r="E62" s="69"/>
+      <c r="B62" s="74"/>
+      <c r="C62" s="74"/>
+      <c r="D62" s="74"/>
+      <c r="E62" s="74"/>
       <c r="F62" s="18"/>
     </row>
     <row r="63" spans="1:23" ht="5.0999999999999996" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="64" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A64" s="69" t="s">
+      <c r="A64" s="74" t="s">
         <v>53</v>
       </c>
-      <c r="B64" s="69"/>
-      <c r="C64" s="69"/>
-      <c r="D64" s="69"/>
-      <c r="E64" s="69"/>
+      <c r="B64" s="74"/>
+      <c r="C64" s="74"/>
+      <c r="D64" s="74"/>
+      <c r="E64" s="74"/>
       <c r="F64" s="18"/>
     </row>
     <row r="65" spans="1:23" ht="5.0999999999999996" customHeight="1" x14ac:dyDescent="0.3">
@@ -3578,45 +3582,45 @@
     </row>
     <row r="66" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B66" s="15"/>
-      <c r="C66" s="70" t="s">
+      <c r="C66" s="87" t="s">
         <v>54</v>
       </c>
-      <c r="D66" s="69"/>
-      <c r="E66" s="69"/>
-      <c r="F66" s="69"/>
-      <c r="G66" s="69"/>
+      <c r="D66" s="74"/>
+      <c r="E66" s="74"/>
+      <c r="F66" s="74"/>
+      <c r="G66" s="74"/>
     </row>
     <row r="67" spans="1:23" ht="5.0999999999999996" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="68" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C68" s="20" t="s">
         <v>31</v>
       </c>
-      <c r="D68" s="85"/>
-      <c r="E68" s="85"/>
-      <c r="F68" s="85"/>
-      <c r="G68" s="85"/>
-      <c r="H68" s="79" t="s">
+      <c r="D68" s="94"/>
+      <c r="E68" s="94"/>
+      <c r="F68" s="94"/>
+      <c r="G68" s="94"/>
+      <c r="H68" s="69" t="s">
         <v>33</v>
       </c>
-      <c r="I68" s="79"/>
-      <c r="J68" s="79"/>
-      <c r="K68" s="84"/>
-      <c r="L68" s="84"/>
+      <c r="I68" s="69"/>
+      <c r="J68" s="69"/>
+      <c r="K68" s="93"/>
+      <c r="L68" s="93"/>
       <c r="M68" s="24" t="s">
         <v>50</v>
       </c>
       <c r="N68" s="27"/>
       <c r="P68" s="15"/>
-      <c r="Q68" s="70" t="s">
+      <c r="Q68" s="87" t="s">
         <v>1</v>
       </c>
-      <c r="R68" s="69"/>
-      <c r="S68" s="69"/>
+      <c r="R68" s="74"/>
+      <c r="S68" s="74"/>
       <c r="U68" s="15"/>
-      <c r="V68" s="70" t="s">
+      <c r="V68" s="87" t="s">
         <v>2</v>
       </c>
-      <c r="W68" s="69"/>
+      <c r="W68" s="74"/>
     </row>
     <row r="69" spans="1:23" ht="5.0999999999999996" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C69" s="12"/>
@@ -3625,8 +3629,8 @@
       <c r="C70" s="20" t="s">
         <v>32</v>
       </c>
-      <c r="D70" s="86"/>
-      <c r="E70" s="86"/>
+      <c r="D70" s="95"/>
+      <c r="E70" s="95"/>
       <c r="F70" s="3" t="s">
         <v>50</v>
       </c>
@@ -3636,193 +3640,193 @@
       <c r="N70" s="4"/>
       <c r="O70" s="4"/>
       <c r="P70" s="15"/>
-      <c r="Q70" s="78" t="s">
+      <c r="Q70" s="88" t="s">
         <v>36</v>
       </c>
-      <c r="R70" s="78"/>
-      <c r="S70" s="78"/>
-      <c r="T70" s="78"/>
-      <c r="U70" s="78"/>
-      <c r="V70" s="78"/>
-      <c r="W70" s="78"/>
+      <c r="R70" s="88"/>
+      <c r="S70" s="88"/>
+      <c r="T70" s="88"/>
+      <c r="U70" s="88"/>
+      <c r="V70" s="88"/>
+      <c r="W70" s="88"/>
     </row>
     <row r="71" spans="1:23" ht="5.0999999999999996" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="Q71" s="78"/>
-      <c r="R71" s="78"/>
-      <c r="S71" s="78"/>
-      <c r="T71" s="78"/>
-      <c r="U71" s="78"/>
-      <c r="V71" s="78"/>
-      <c r="W71" s="78"/>
+      <c r="Q71" s="88"/>
+      <c r="R71" s="88"/>
+      <c r="S71" s="88"/>
+      <c r="T71" s="88"/>
+      <c r="U71" s="88"/>
+      <c r="V71" s="88"/>
+      <c r="W71" s="88"/>
     </row>
     <row r="72" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B72" s="15"/>
-      <c r="C72" s="70" t="s">
+      <c r="C72" s="87" t="s">
         <v>20</v>
       </c>
-      <c r="D72" s="69"/>
-      <c r="E72" s="69"/>
+      <c r="D72" s="74"/>
+      <c r="E72" s="74"/>
       <c r="F72" s="18"/>
-      <c r="Q72" s="78"/>
-      <c r="R72" s="78"/>
-      <c r="S72" s="78"/>
-      <c r="T72" s="78"/>
-      <c r="U72" s="78"/>
-      <c r="V72" s="78"/>
-      <c r="W72" s="78"/>
+      <c r="Q72" s="88"/>
+      <c r="R72" s="88"/>
+      <c r="S72" s="88"/>
+      <c r="T72" s="88"/>
+      <c r="U72" s="88"/>
+      <c r="V72" s="88"/>
+      <c r="W72" s="88"/>
     </row>
     <row r="73" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B73" s="83" t="s">
+      <c r="B73" s="92" t="s">
         <v>44</v>
       </c>
-      <c r="C73" s="83"/>
-      <c r="D73" s="83"/>
-      <c r="E73" s="83"/>
-      <c r="F73" s="83"/>
-      <c r="G73" s="83"/>
-      <c r="H73" s="83"/>
-      <c r="I73" s="83"/>
-      <c r="J73" s="83"/>
-      <c r="K73" s="83"/>
-      <c r="L73" s="83"/>
-      <c r="M73" s="83"/>
-      <c r="N73" s="83"/>
-      <c r="O73" s="83"/>
-      <c r="Q73" s="78"/>
-      <c r="R73" s="78"/>
-      <c r="S73" s="78"/>
-      <c r="T73" s="78"/>
-      <c r="U73" s="78"/>
-      <c r="V73" s="78"/>
-      <c r="W73" s="78"/>
+      <c r="C73" s="92"/>
+      <c r="D73" s="92"/>
+      <c r="E73" s="92"/>
+      <c r="F73" s="92"/>
+      <c r="G73" s="92"/>
+      <c r="H73" s="92"/>
+      <c r="I73" s="92"/>
+      <c r="J73" s="92"/>
+      <c r="K73" s="92"/>
+      <c r="L73" s="92"/>
+      <c r="M73" s="92"/>
+      <c r="N73" s="92"/>
+      <c r="O73" s="92"/>
+      <c r="Q73" s="88"/>
+      <c r="R73" s="88"/>
+      <c r="S73" s="88"/>
+      <c r="T73" s="88"/>
+      <c r="U73" s="88"/>
+      <c r="V73" s="88"/>
+      <c r="W73" s="88"/>
     </row>
     <row r="74" spans="1:23" ht="5.0999999999999996" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="75" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A75" s="78" t="s">
+      <c r="A75" s="88" t="s">
         <v>45</v>
       </c>
-      <c r="B75" s="78"/>
-      <c r="C75" s="78"/>
-      <c r="D75" s="78"/>
-      <c r="E75" s="78"/>
-      <c r="F75" s="78"/>
-      <c r="G75" s="78"/>
-      <c r="H75" s="78"/>
-      <c r="I75" s="78"/>
-      <c r="J75" s="78"/>
-      <c r="K75" s="78"/>
-      <c r="L75" s="78"/>
-      <c r="M75" s="78"/>
-      <c r="N75" s="78"/>
-      <c r="O75" s="78"/>
-      <c r="P75" s="78"/>
-      <c r="Q75" s="78"/>
-      <c r="R75" s="78"/>
-      <c r="S75" s="78"/>
-      <c r="T75" s="78"/>
-      <c r="U75" s="78"/>
-      <c r="V75" s="78"/>
-      <c r="W75" s="78"/>
+      <c r="B75" s="88"/>
+      <c r="C75" s="88"/>
+      <c r="D75" s="88"/>
+      <c r="E75" s="88"/>
+      <c r="F75" s="88"/>
+      <c r="G75" s="88"/>
+      <c r="H75" s="88"/>
+      <c r="I75" s="88"/>
+      <c r="J75" s="88"/>
+      <c r="K75" s="88"/>
+      <c r="L75" s="88"/>
+      <c r="M75" s="88"/>
+      <c r="N75" s="88"/>
+      <c r="O75" s="88"/>
+      <c r="P75" s="88"/>
+      <c r="Q75" s="88"/>
+      <c r="R75" s="88"/>
+      <c r="S75" s="88"/>
+      <c r="T75" s="88"/>
+      <c r="U75" s="88"/>
+      <c r="V75" s="88"/>
+      <c r="W75" s="88"/>
     </row>
     <row r="76" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A76" s="78"/>
-      <c r="B76" s="78"/>
-      <c r="C76" s="78"/>
-      <c r="D76" s="78"/>
-      <c r="E76" s="78"/>
-      <c r="F76" s="78"/>
-      <c r="G76" s="78"/>
-      <c r="H76" s="78"/>
-      <c r="I76" s="78"/>
-      <c r="J76" s="78"/>
-      <c r="K76" s="78"/>
-      <c r="L76" s="78"/>
-      <c r="M76" s="78"/>
-      <c r="N76" s="78"/>
-      <c r="O76" s="78"/>
-      <c r="P76" s="78"/>
-      <c r="Q76" s="78"/>
-      <c r="R76" s="78"/>
-      <c r="S76" s="78"/>
-      <c r="T76" s="78"/>
-      <c r="U76" s="78"/>
-      <c r="V76" s="78"/>
-      <c r="W76" s="78"/>
+      <c r="A76" s="88"/>
+      <c r="B76" s="88"/>
+      <c r="C76" s="88"/>
+      <c r="D76" s="88"/>
+      <c r="E76" s="88"/>
+      <c r="F76" s="88"/>
+      <c r="G76" s="88"/>
+      <c r="H76" s="88"/>
+      <c r="I76" s="88"/>
+      <c r="J76" s="88"/>
+      <c r="K76" s="88"/>
+      <c r="L76" s="88"/>
+      <c r="M76" s="88"/>
+      <c r="N76" s="88"/>
+      <c r="O76" s="88"/>
+      <c r="P76" s="88"/>
+      <c r="Q76" s="88"/>
+      <c r="R76" s="88"/>
+      <c r="S76" s="88"/>
+      <c r="T76" s="88"/>
+      <c r="U76" s="88"/>
+      <c r="V76" s="88"/>
+      <c r="W76" s="88"/>
     </row>
     <row r="77" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A77" s="78"/>
-      <c r="B77" s="78"/>
-      <c r="C77" s="78"/>
-      <c r="D77" s="78"/>
-      <c r="E77" s="78"/>
-      <c r="F77" s="78"/>
-      <c r="G77" s="78"/>
-      <c r="H77" s="78"/>
-      <c r="I77" s="78"/>
-      <c r="J77" s="78"/>
-      <c r="K77" s="78"/>
-      <c r="L77" s="78"/>
-      <c r="M77" s="78"/>
-      <c r="N77" s="78"/>
-      <c r="O77" s="78"/>
-      <c r="P77" s="78"/>
-      <c r="Q77" s="78"/>
-      <c r="R77" s="78"/>
-      <c r="S77" s="78"/>
-      <c r="T77" s="78"/>
-      <c r="U77" s="78"/>
-      <c r="V77" s="78"/>
-      <c r="W77" s="78"/>
+      <c r="A77" s="88"/>
+      <c r="B77" s="88"/>
+      <c r="C77" s="88"/>
+      <c r="D77" s="88"/>
+      <c r="E77" s="88"/>
+      <c r="F77" s="88"/>
+      <c r="G77" s="88"/>
+      <c r="H77" s="88"/>
+      <c r="I77" s="88"/>
+      <c r="J77" s="88"/>
+      <c r="K77" s="88"/>
+      <c r="L77" s="88"/>
+      <c r="M77" s="88"/>
+      <c r="N77" s="88"/>
+      <c r="O77" s="88"/>
+      <c r="P77" s="88"/>
+      <c r="Q77" s="88"/>
+      <c r="R77" s="88"/>
+      <c r="S77" s="88"/>
+      <c r="T77" s="88"/>
+      <c r="U77" s="88"/>
+      <c r="V77" s="88"/>
+      <c r="W77" s="88"/>
     </row>
     <row r="78" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A78" s="78"/>
-      <c r="B78" s="78"/>
-      <c r="C78" s="78"/>
-      <c r="D78" s="78"/>
-      <c r="E78" s="78"/>
-      <c r="F78" s="78"/>
-      <c r="G78" s="78"/>
-      <c r="H78" s="78"/>
-      <c r="I78" s="78"/>
-      <c r="J78" s="78"/>
-      <c r="K78" s="78"/>
-      <c r="L78" s="78"/>
-      <c r="M78" s="78"/>
-      <c r="N78" s="78"/>
-      <c r="O78" s="78"/>
-      <c r="P78" s="78"/>
-      <c r="Q78" s="78"/>
-      <c r="R78" s="78"/>
-      <c r="S78" s="78"/>
-      <c r="T78" s="78"/>
-      <c r="U78" s="78"/>
-      <c r="V78" s="78"/>
-      <c r="W78" s="78"/>
+      <c r="A78" s="88"/>
+      <c r="B78" s="88"/>
+      <c r="C78" s="88"/>
+      <c r="D78" s="88"/>
+      <c r="E78" s="88"/>
+      <c r="F78" s="88"/>
+      <c r="G78" s="88"/>
+      <c r="H78" s="88"/>
+      <c r="I78" s="88"/>
+      <c r="J78" s="88"/>
+      <c r="K78" s="88"/>
+      <c r="L78" s="88"/>
+      <c r="M78" s="88"/>
+      <c r="N78" s="88"/>
+      <c r="O78" s="88"/>
+      <c r="P78" s="88"/>
+      <c r="Q78" s="88"/>
+      <c r="R78" s="88"/>
+      <c r="S78" s="88"/>
+      <c r="T78" s="88"/>
+      <c r="U78" s="88"/>
+      <c r="V78" s="88"/>
+      <c r="W78" s="88"/>
     </row>
     <row r="79" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A79" s="78"/>
-      <c r="B79" s="78"/>
-      <c r="C79" s="78"/>
-      <c r="D79" s="78"/>
-      <c r="E79" s="78"/>
-      <c r="F79" s="78"/>
-      <c r="G79" s="78"/>
-      <c r="H79" s="78"/>
-      <c r="I79" s="78"/>
-      <c r="J79" s="78"/>
-      <c r="K79" s="78"/>
-      <c r="L79" s="78"/>
-      <c r="M79" s="78"/>
-      <c r="N79" s="78"/>
-      <c r="O79" s="78"/>
-      <c r="P79" s="78"/>
-      <c r="Q79" s="78"/>
-      <c r="R79" s="78"/>
-      <c r="S79" s="78"/>
-      <c r="T79" s="78"/>
-      <c r="U79" s="78"/>
-      <c r="V79" s="78"/>
-      <c r="W79" s="78"/>
+      <c r="A79" s="88"/>
+      <c r="B79" s="88"/>
+      <c r="C79" s="88"/>
+      <c r="D79" s="88"/>
+      <c r="E79" s="88"/>
+      <c r="F79" s="88"/>
+      <c r="G79" s="88"/>
+      <c r="H79" s="88"/>
+      <c r="I79" s="88"/>
+      <c r="J79" s="88"/>
+      <c r="K79" s="88"/>
+      <c r="L79" s="88"/>
+      <c r="M79" s="88"/>
+      <c r="N79" s="88"/>
+      <c r="O79" s="88"/>
+      <c r="P79" s="88"/>
+      <c r="Q79" s="88"/>
+      <c r="R79" s="88"/>
+      <c r="S79" s="88"/>
+      <c r="T79" s="88"/>
+      <c r="U79" s="88"/>
+      <c r="V79" s="88"/>
+      <c r="W79" s="88"/>
     </row>
     <row r="80" spans="1:23" ht="5.0999999999999996" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="81" spans="1:92" ht="30" customHeight="1" x14ac:dyDescent="0.3">
@@ -3831,16 +3835,16 @@
       <c r="F81" s="23"/>
       <c r="G81" s="23"/>
       <c r="H81" s="23"/>
-      <c r="I81" s="82">
+      <c r="I81" s="91">
         <f ca="1">TODAY()</f>
         <v>46156</v>
       </c>
-      <c r="J81" s="82"/>
-      <c r="K81" s="82"/>
-      <c r="L81" s="82"/>
-      <c r="M81" s="82"/>
-      <c r="N81" s="82"/>
-      <c r="O81" s="82"/>
+      <c r="J81" s="91"/>
+      <c r="K81" s="91"/>
+      <c r="L81" s="91"/>
+      <c r="M81" s="91"/>
+      <c r="N81" s="91"/>
+      <c r="O81" s="91"/>
     </row>
     <row r="82" spans="1:92" ht="5.0999999999999996" customHeight="1" x14ac:dyDescent="0.3">
       <c r="G82"/>
@@ -3857,52 +3861,52 @@
       <c r="R82" s="17"/>
     </row>
     <row r="83" spans="1:92" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A83" s="77"/>
-      <c r="B83" s="77"/>
-      <c r="C83" s="77"/>
-      <c r="D83" s="77"/>
-      <c r="E83" s="77"/>
-      <c r="F83" s="77"/>
-      <c r="G83" s="77"/>
-      <c r="H83" s="77"/>
-      <c r="I83" s="77"/>
-      <c r="J83" s="77"/>
-      <c r="K83" s="77"/>
-      <c r="L83" s="77"/>
-      <c r="M83" s="77"/>
-      <c r="N83" s="77"/>
-      <c r="O83" s="77"/>
-      <c r="P83" s="77"/>
-      <c r="Q83" s="77"/>
+      <c r="A83" s="86"/>
+      <c r="B83" s="86"/>
+      <c r="C83" s="86"/>
+      <c r="D83" s="86"/>
+      <c r="E83" s="86"/>
+      <c r="F83" s="86"/>
+      <c r="G83" s="86"/>
+      <c r="H83" s="86"/>
+      <c r="I83" s="86"/>
+      <c r="J83" s="86"/>
+      <c r="K83" s="86"/>
+      <c r="L83" s="86"/>
+      <c r="M83" s="86"/>
+      <c r="N83" s="86"/>
+      <c r="O83" s="86"/>
+      <c r="P83" s="86"/>
+      <c r="Q83" s="86"/>
       <c r="R83"/>
-      <c r="S83" s="80" t="s">
+      <c r="S83" s="89" t="s">
         <v>51</v>
       </c>
-      <c r="T83" s="76"/>
-      <c r="U83" s="81"/>
-      <c r="V83" s="81"/>
-      <c r="W83" s="81"/>
+      <c r="T83" s="85"/>
+      <c r="U83" s="90"/>
+      <c r="V83" s="90"/>
+      <c r="W83" s="90"/>
     </row>
     <row r="84" spans="1:92" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A84" s="76" t="s">
+      <c r="A84" s="85" t="s">
         <v>35</v>
       </c>
-      <c r="B84" s="76"/>
-      <c r="C84" s="76"/>
-      <c r="D84" s="76"/>
-      <c r="E84" s="76"/>
-      <c r="F84" s="76"/>
-      <c r="G84" s="76"/>
-      <c r="H84" s="76"/>
-      <c r="I84" s="76"/>
-      <c r="J84" s="76"/>
-      <c r="K84" s="76"/>
-      <c r="L84" s="76"/>
-      <c r="M84" s="76"/>
-      <c r="N84" s="76"/>
-      <c r="O84" s="76"/>
-      <c r="P84" s="76"/>
-      <c r="Q84" s="76"/>
+      <c r="B84" s="85"/>
+      <c r="C84" s="85"/>
+      <c r="D84" s="85"/>
+      <c r="E84" s="85"/>
+      <c r="F84" s="85"/>
+      <c r="G84" s="85"/>
+      <c r="H84" s="85"/>
+      <c r="I84" s="85"/>
+      <c r="J84" s="85"/>
+      <c r="K84" s="85"/>
+      <c r="L84" s="85"/>
+      <c r="M84" s="85"/>
+      <c r="N84" s="85"/>
+      <c r="O84" s="85"/>
+      <c r="P84" s="85"/>
+      <c r="Q84" s="85"/>
       <c r="R84" s="13"/>
       <c r="S84" s="13"/>
       <c r="T84" s="13"/>
@@ -3981,19 +3985,42 @@
     </row>
   </sheetData>
   <mergeCells count="65">
-    <mergeCell ref="A11:C11"/>
-    <mergeCell ref="D11:W11"/>
-    <mergeCell ref="A13:C13"/>
-    <mergeCell ref="D13:W13"/>
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="G1:R3"/>
-    <mergeCell ref="A2:E2"/>
-    <mergeCell ref="B5:W5"/>
-    <mergeCell ref="A7:E7"/>
-    <mergeCell ref="A9:C9"/>
-    <mergeCell ref="D9:E9"/>
-    <mergeCell ref="T9:V9"/>
-    <mergeCell ref="J9:K9"/>
+    <mergeCell ref="A62:E62"/>
+    <mergeCell ref="A64:E64"/>
+    <mergeCell ref="C66:G66"/>
+    <mergeCell ref="K50:O50"/>
+    <mergeCell ref="S50:U50"/>
+    <mergeCell ref="J52:O52"/>
+    <mergeCell ref="S54:U54"/>
+    <mergeCell ref="S56:V56"/>
+    <mergeCell ref="R58:W58"/>
+    <mergeCell ref="A84:Q84"/>
+    <mergeCell ref="A83:Q83"/>
+    <mergeCell ref="Q68:S68"/>
+    <mergeCell ref="V68:W68"/>
+    <mergeCell ref="Q70:W73"/>
+    <mergeCell ref="C72:E72"/>
+    <mergeCell ref="H68:J68"/>
+    <mergeCell ref="S83:T83"/>
+    <mergeCell ref="U83:W83"/>
+    <mergeCell ref="I81:O81"/>
+    <mergeCell ref="A75:W79"/>
+    <mergeCell ref="B73:O73"/>
+    <mergeCell ref="K68:L68"/>
+    <mergeCell ref="D68:G68"/>
+    <mergeCell ref="D70:E70"/>
+    <mergeCell ref="K44:O44"/>
+    <mergeCell ref="S44:V44"/>
+    <mergeCell ref="K46:O46"/>
+    <mergeCell ref="S46:V46"/>
+    <mergeCell ref="K48:O48"/>
+    <mergeCell ref="S48:W48"/>
+    <mergeCell ref="A39:H39"/>
+    <mergeCell ref="I39:P39"/>
+    <mergeCell ref="Q39:W39"/>
+    <mergeCell ref="C42:G42"/>
+    <mergeCell ref="K42:O42"/>
+    <mergeCell ref="S42:V42"/>
     <mergeCell ref="T15:W15"/>
     <mergeCell ref="B17:W17"/>
     <mergeCell ref="A19:E19"/>
@@ -4010,42 +4037,19 @@
     <mergeCell ref="K15:L15"/>
     <mergeCell ref="N15:P15"/>
     <mergeCell ref="Q15:S15"/>
-    <mergeCell ref="A39:H39"/>
-    <mergeCell ref="I39:P39"/>
-    <mergeCell ref="Q39:W39"/>
-    <mergeCell ref="C42:G42"/>
-    <mergeCell ref="K42:O42"/>
-    <mergeCell ref="S42:V42"/>
-    <mergeCell ref="K44:O44"/>
-    <mergeCell ref="S44:V44"/>
-    <mergeCell ref="K46:O46"/>
-    <mergeCell ref="S46:V46"/>
-    <mergeCell ref="K48:O48"/>
-    <mergeCell ref="S48:W48"/>
-    <mergeCell ref="A84:Q84"/>
-    <mergeCell ref="A83:Q83"/>
-    <mergeCell ref="Q68:S68"/>
-    <mergeCell ref="V68:W68"/>
-    <mergeCell ref="Q70:W73"/>
-    <mergeCell ref="C72:E72"/>
-    <mergeCell ref="H68:J68"/>
-    <mergeCell ref="S83:T83"/>
-    <mergeCell ref="U83:W83"/>
-    <mergeCell ref="I81:O81"/>
-    <mergeCell ref="A75:W79"/>
-    <mergeCell ref="B73:O73"/>
-    <mergeCell ref="K68:L68"/>
-    <mergeCell ref="D68:G68"/>
-    <mergeCell ref="D70:E70"/>
-    <mergeCell ref="A62:E62"/>
-    <mergeCell ref="A64:E64"/>
-    <mergeCell ref="C66:G66"/>
-    <mergeCell ref="K50:O50"/>
-    <mergeCell ref="S50:U50"/>
-    <mergeCell ref="J52:O52"/>
-    <mergeCell ref="S54:U54"/>
-    <mergeCell ref="S56:V56"/>
-    <mergeCell ref="R58:W58"/>
+    <mergeCell ref="A11:C11"/>
+    <mergeCell ref="D11:W11"/>
+    <mergeCell ref="A13:C13"/>
+    <mergeCell ref="D13:W13"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="G1:R3"/>
+    <mergeCell ref="A2:E2"/>
+    <mergeCell ref="B5:W5"/>
+    <mergeCell ref="A7:E7"/>
+    <mergeCell ref="A9:C9"/>
+    <mergeCell ref="D9:E9"/>
+    <mergeCell ref="T9:V9"/>
+    <mergeCell ref="J9:K9"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.19685039370078741" right="0.19685039370078741" top="0.39370078740157483" bottom="0.39370078740157483" header="0" footer="0"/>
@@ -4096,26 +4100,26 @@
       <c r="F1" s="29"/>
       <c r="G1" s="29"/>
       <c r="H1" s="29"/>
-      <c r="I1" s="108" t="s">
+      <c r="I1" s="104" t="s">
         <v>69</v>
       </c>
-      <c r="J1" s="108"/>
-      <c r="K1" s="108"/>
-      <c r="L1" s="108"/>
-      <c r="M1" s="108"/>
-      <c r="N1" s="108"/>
-      <c r="O1" s="108"/>
-      <c r="P1" s="108"/>
-      <c r="Q1" s="108"/>
-      <c r="R1" s="108"/>
-      <c r="S1" s="108"/>
-      <c r="T1" s="108"/>
-      <c r="U1" s="108"/>
-      <c r="V1" s="108"/>
-      <c r="W1" s="108"/>
-      <c r="X1" s="108"/>
-      <c r="Y1" s="108"/>
-      <c r="Z1" s="108"/>
+      <c r="J1" s="104"/>
+      <c r="K1" s="104"/>
+      <c r="L1" s="104"/>
+      <c r="M1" s="104"/>
+      <c r="N1" s="104"/>
+      <c r="O1" s="104"/>
+      <c r="P1" s="104"/>
+      <c r="Q1" s="104"/>
+      <c r="R1" s="104"/>
+      <c r="S1" s="104"/>
+      <c r="T1" s="104"/>
+      <c r="U1" s="104"/>
+      <c r="V1" s="104"/>
+      <c r="W1" s="104"/>
+      <c r="X1" s="104"/>
+      <c r="Y1" s="104"/>
+      <c r="Z1" s="104"/>
     </row>
     <row r="2" spans="1:32" ht="14.55" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B2" s="29"/>
@@ -4124,24 +4128,24 @@
       <c r="F2" s="29"/>
       <c r="G2" s="29"/>
       <c r="H2" s="29"/>
-      <c r="I2" s="108"/>
-      <c r="J2" s="108"/>
-      <c r="K2" s="108"/>
-      <c r="L2" s="108"/>
-      <c r="M2" s="108"/>
-      <c r="N2" s="108"/>
-      <c r="O2" s="108"/>
-      <c r="P2" s="108"/>
-      <c r="Q2" s="108"/>
-      <c r="R2" s="108"/>
-      <c r="S2" s="108"/>
-      <c r="T2" s="108"/>
-      <c r="U2" s="108"/>
-      <c r="V2" s="108"/>
-      <c r="W2" s="108"/>
-      <c r="X2" s="108"/>
-      <c r="Y2" s="108"/>
-      <c r="Z2" s="108"/>
+      <c r="I2" s="104"/>
+      <c r="J2" s="104"/>
+      <c r="K2" s="104"/>
+      <c r="L2" s="104"/>
+      <c r="M2" s="104"/>
+      <c r="N2" s="104"/>
+      <c r="O2" s="104"/>
+      <c r="P2" s="104"/>
+      <c r="Q2" s="104"/>
+      <c r="R2" s="104"/>
+      <c r="S2" s="104"/>
+      <c r="T2" s="104"/>
+      <c r="U2" s="104"/>
+      <c r="V2" s="104"/>
+      <c r="W2" s="104"/>
+      <c r="X2" s="104"/>
+      <c r="Y2" s="104"/>
+      <c r="Z2" s="104"/>
     </row>
     <row r="3" spans="1:32" ht="14.55" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B3" s="29"/>
@@ -4150,24 +4154,24 @@
       <c r="F3" s="29"/>
       <c r="G3" s="29"/>
       <c r="H3" s="29"/>
-      <c r="I3" s="108"/>
-      <c r="J3" s="108"/>
-      <c r="K3" s="108"/>
-      <c r="L3" s="108"/>
-      <c r="M3" s="108"/>
-      <c r="N3" s="108"/>
-      <c r="O3" s="108"/>
-      <c r="P3" s="108"/>
-      <c r="Q3" s="108"/>
-      <c r="R3" s="108"/>
-      <c r="S3" s="108"/>
-      <c r="T3" s="108"/>
-      <c r="U3" s="108"/>
-      <c r="V3" s="108"/>
-      <c r="W3" s="108"/>
-      <c r="X3" s="108"/>
-      <c r="Y3" s="108"/>
-      <c r="Z3" s="108"/>
+      <c r="I3" s="104"/>
+      <c r="J3" s="104"/>
+      <c r="K3" s="104"/>
+      <c r="L3" s="104"/>
+      <c r="M3" s="104"/>
+      <c r="N3" s="104"/>
+      <c r="O3" s="104"/>
+      <c r="P3" s="104"/>
+      <c r="Q3" s="104"/>
+      <c r="R3" s="104"/>
+      <c r="S3" s="104"/>
+      <c r="T3" s="104"/>
+      <c r="U3" s="104"/>
+      <c r="V3" s="104"/>
+      <c r="W3" s="104"/>
+      <c r="X3" s="104"/>
+      <c r="Y3" s="104"/>
+      <c r="Z3" s="104"/>
     </row>
     <row r="4" spans="1:32" ht="14.55" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B4" s="29"/>
@@ -4176,45 +4180,45 @@
       <c r="F4" s="29"/>
       <c r="G4" s="29"/>
       <c r="H4" s="29"/>
-      <c r="I4" s="108"/>
-      <c r="J4" s="108"/>
-      <c r="K4" s="108"/>
-      <c r="L4" s="108"/>
-      <c r="M4" s="108"/>
-      <c r="N4" s="108"/>
-      <c r="O4" s="108"/>
-      <c r="P4" s="108"/>
-      <c r="Q4" s="108"/>
-      <c r="R4" s="108"/>
-      <c r="S4" s="108"/>
-      <c r="T4" s="108"/>
-      <c r="U4" s="108"/>
-      <c r="V4" s="108"/>
-      <c r="W4" s="108"/>
-      <c r="X4" s="108"/>
-      <c r="Y4" s="108"/>
-      <c r="Z4" s="108"/>
+      <c r="I4" s="104"/>
+      <c r="J4" s="104"/>
+      <c r="K4" s="104"/>
+      <c r="L4" s="104"/>
+      <c r="M4" s="104"/>
+      <c r="N4" s="104"/>
+      <c r="O4" s="104"/>
+      <c r="P4" s="104"/>
+      <c r="Q4" s="104"/>
+      <c r="R4" s="104"/>
+      <c r="S4" s="104"/>
+      <c r="T4" s="104"/>
+      <c r="U4" s="104"/>
+      <c r="V4" s="104"/>
+      <c r="W4" s="104"/>
+      <c r="X4" s="104"/>
+      <c r="Y4" s="104"/>
+      <c r="Z4" s="104"/>
     </row>
     <row r="5" spans="1:32" ht="14.55" customHeight="1" x14ac:dyDescent="0.35">
       <c r="H5" s="6"/>
-      <c r="I5" s="108"/>
-      <c r="J5" s="108"/>
-      <c r="K5" s="108"/>
-      <c r="L5" s="108"/>
-      <c r="M5" s="108"/>
-      <c r="N5" s="108"/>
-      <c r="O5" s="108"/>
-      <c r="P5" s="108"/>
-      <c r="Q5" s="108"/>
-      <c r="R5" s="108"/>
-      <c r="S5" s="108"/>
-      <c r="T5" s="108"/>
-      <c r="U5" s="108"/>
-      <c r="V5" s="108"/>
-      <c r="W5" s="108"/>
-      <c r="X5" s="108"/>
-      <c r="Y5" s="108"/>
-      <c r="Z5" s="108"/>
+      <c r="I5" s="104"/>
+      <c r="J5" s="104"/>
+      <c r="K5" s="104"/>
+      <c r="L5" s="104"/>
+      <c r="M5" s="104"/>
+      <c r="N5" s="104"/>
+      <c r="O5" s="104"/>
+      <c r="P5" s="104"/>
+      <c r="Q5" s="104"/>
+      <c r="R5" s="104"/>
+      <c r="S5" s="104"/>
+      <c r="T5" s="104"/>
+      <c r="U5" s="104"/>
+      <c r="V5" s="104"/>
+      <c r="W5" s="104"/>
+      <c r="X5" s="104"/>
+      <c r="Y5" s="104"/>
+      <c r="Z5" s="104"/>
     </row>
     <row r="6" spans="1:32" ht="5.0999999999999996" customHeight="1" x14ac:dyDescent="0.35">
       <c r="H6" s="2"/>
@@ -4238,50 +4242,50 @@
       <c r="Z6" s="2"/>
     </row>
     <row r="7" spans="1:32" ht="5.0999999999999996" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="65"/>
-      <c r="B7" s="66"/>
-      <c r="C7" s="66"/>
-      <c r="D7" s="107"/>
-      <c r="E7" s="107"/>
-      <c r="F7" s="107"/>
-      <c r="G7" s="107"/>
-      <c r="H7" s="107"/>
-      <c r="I7" s="107"/>
-      <c r="J7" s="107"/>
-      <c r="K7" s="107"/>
-      <c r="L7" s="107"/>
-      <c r="M7" s="107"/>
-      <c r="N7" s="107"/>
-      <c r="O7" s="107"/>
-      <c r="P7" s="107"/>
-      <c r="Q7" s="107"/>
-      <c r="R7" s="107"/>
-      <c r="S7" s="107"/>
-      <c r="T7" s="107"/>
-      <c r="U7" s="107"/>
-      <c r="V7" s="107"/>
-      <c r="W7" s="107"/>
-      <c r="X7" s="107"/>
-      <c r="Y7" s="107"/>
-      <c r="Z7" s="107"/>
-      <c r="AA7" s="107"/>
-      <c r="AB7" s="107"/>
-      <c r="AC7" s="107"/>
-      <c r="AD7" s="107"/>
-      <c r="AE7" s="107"/>
-      <c r="AF7" s="107"/>
+      <c r="A7" s="64"/>
+      <c r="B7" s="65"/>
+      <c r="C7" s="65"/>
+      <c r="D7" s="103"/>
+      <c r="E7" s="103"/>
+      <c r="F7" s="103"/>
+      <c r="G7" s="103"/>
+      <c r="H7" s="103"/>
+      <c r="I7" s="103"/>
+      <c r="J7" s="103"/>
+      <c r="K7" s="103"/>
+      <c r="L7" s="103"/>
+      <c r="M7" s="103"/>
+      <c r="N7" s="103"/>
+      <c r="O7" s="103"/>
+      <c r="P7" s="103"/>
+      <c r="Q7" s="103"/>
+      <c r="R7" s="103"/>
+      <c r="S7" s="103"/>
+      <c r="T7" s="103"/>
+      <c r="U7" s="103"/>
+      <c r="V7" s="103"/>
+      <c r="W7" s="103"/>
+      <c r="X7" s="103"/>
+      <c r="Y7" s="103"/>
+      <c r="Z7" s="103"/>
+      <c r="AA7" s="103"/>
+      <c r="AB7" s="103"/>
+      <c r="AC7" s="103"/>
+      <c r="AD7" s="103"/>
+      <c r="AE7" s="103"/>
+      <c r="AF7" s="103"/>
     </row>
     <row r="8" spans="1:32" ht="5.0999999999999996" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="9" spans="1:32" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B9" s="100" t="s">
+      <c r="B9" s="105" t="s">
         <v>64</v>
       </c>
-      <c r="C9" s="100"/>
-      <c r="D9" s="100"/>
-      <c r="E9" s="100"/>
-      <c r="F9" s="100"/>
-      <c r="G9" s="100"/>
-      <c r="H9" s="100"/>
+      <c r="C9" s="105"/>
+      <c r="D9" s="105"/>
+      <c r="E9" s="105"/>
+      <c r="F9" s="105"/>
+      <c r="G9" s="105"/>
+      <c r="H9" s="105"/>
       <c r="I9" s="31"/>
       <c r="J9" s="31"/>
       <c r="K9" s="31"/>
@@ -4330,42 +4334,42 @@
       <c r="Z10" s="2"/>
     </row>
     <row r="11" spans="1:32" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B11" s="97" t="s">
+      <c r="B11" s="99" t="s">
         <v>72</v>
       </c>
-      <c r="C11" s="97"/>
-      <c r="D11" s="97"/>
-      <c r="E11" s="97"/>
+      <c r="C11" s="99"/>
+      <c r="D11" s="99"/>
+      <c r="E11" s="99"/>
       <c r="F11" s="98"/>
       <c r="G11" s="98"/>
       <c r="H11" s="98"/>
       <c r="I11" s="31"/>
-      <c r="J11" s="97" t="s">
+      <c r="J11" s="99" t="s">
         <v>23</v>
       </c>
-      <c r="K11" s="97"/>
-      <c r="L11" s="97"/>
+      <c r="K11" s="99"/>
+      <c r="L11" s="99"/>
       <c r="M11" s="36"/>
       <c r="N11" s="36"/>
       <c r="O11" s="33"/>
-      <c r="P11" s="101" t="s">
+      <c r="P11" s="107" t="s">
         <v>73</v>
       </c>
-      <c r="Q11" s="101"/>
-      <c r="R11" s="101"/>
-      <c r="S11" s="101"/>
-      <c r="T11" s="101"/>
-      <c r="U11" s="101"/>
-      <c r="V11" s="101"/>
-      <c r="W11" s="101"/>
-      <c r="X11" s="101"/>
-      <c r="Y11" s="109"/>
-      <c r="Z11" s="109"/>
-      <c r="AA11" s="109"/>
-      <c r="AB11" s="97" t="s">
+      <c r="Q11" s="107"/>
+      <c r="R11" s="107"/>
+      <c r="S11" s="107"/>
+      <c r="T11" s="107"/>
+      <c r="U11" s="107"/>
+      <c r="V11" s="107"/>
+      <c r="W11" s="107"/>
+      <c r="X11" s="107"/>
+      <c r="Y11" s="106"/>
+      <c r="Z11" s="106"/>
+      <c r="AA11" s="106"/>
+      <c r="AB11" s="99" t="s">
         <v>22</v>
       </c>
-      <c r="AC11" s="97"/>
+      <c r="AC11" s="99"/>
       <c r="AD11" s="36"/>
       <c r="AE11" s="29"/>
       <c r="AF11" s="31"/>
@@ -4392,12 +4396,12 @@
       <c r="Z12" s="2"/>
     </row>
     <row r="13" spans="1:32" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B13" s="97" t="s">
+      <c r="B13" s="99" t="s">
         <v>48</v>
       </c>
-      <c r="C13" s="97"/>
-      <c r="D13" s="97"/>
-      <c r="E13" s="97"/>
+      <c r="C13" s="99"/>
+      <c r="D13" s="99"/>
+      <c r="E13" s="99"/>
       <c r="F13" s="114"/>
       <c r="G13" s="114"/>
       <c r="H13" s="114"/>
@@ -4433,12 +4437,12 @@
       <c r="E14" s="35"/>
     </row>
     <row r="15" spans="1:32" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B15" s="97" t="s">
+      <c r="B15" s="99" t="s">
         <v>25</v>
       </c>
-      <c r="C15" s="97"/>
-      <c r="D15" s="97"/>
-      <c r="E15" s="97"/>
+      <c r="C15" s="99"/>
+      <c r="D15" s="99"/>
+      <c r="E15" s="99"/>
       <c r="F15" s="36"/>
       <c r="G15" s="36"/>
       <c r="H15" s="36"/>
@@ -4474,12 +4478,12 @@
       <c r="E16" s="35"/>
     </row>
     <row r="17" spans="2:32" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B17" s="97" t="s">
+      <c r="B17" s="99" t="s">
         <v>49</v>
       </c>
-      <c r="C17" s="97"/>
-      <c r="D17" s="97"/>
-      <c r="E17" s="97"/>
+      <c r="C17" s="99"/>
+      <c r="D17" s="99"/>
+      <c r="E17" s="99"/>
       <c r="F17" s="98"/>
       <c r="G17" s="98"/>
       <c r="H17" s="98"/>
@@ -4501,18 +4505,18 @@
       <c r="T17" s="98"/>
       <c r="U17" s="98"/>
       <c r="V17" s="98"/>
-      <c r="W17" s="97" t="s">
+      <c r="W17" s="99" t="s">
         <v>28</v>
       </c>
-      <c r="X17" s="97"/>
-      <c r="Y17" s="97"/>
-      <c r="Z17" s="97"/>
+      <c r="X17" s="99"/>
+      <c r="Y17" s="99"/>
+      <c r="Z17" s="99"/>
       <c r="AA17" s="36"/>
-      <c r="AB17" s="64"/>
-      <c r="AC17" s="64"/>
-      <c r="AD17" s="64"/>
-      <c r="AE17" s="64"/>
-      <c r="AF17" s="64"/>
+      <c r="AB17" s="63"/>
+      <c r="AC17" s="63"/>
+      <c r="AD17" s="63"/>
+      <c r="AE17" s="63"/>
+      <c r="AF17" s="63"/>
     </row>
     <row r="18" spans="2:32" ht="5.0999999999999996" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B18" s="34"/>
@@ -4548,37 +4552,37 @@
       <c r="AF18" s="38"/>
     </row>
     <row r="19" spans="2:32" ht="4.05" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B19" s="66"/>
-      <c r="C19" s="66"/>
-      <c r="D19" s="66"/>
-      <c r="E19" s="66"/>
-      <c r="F19" s="66"/>
-      <c r="G19" s="66"/>
-      <c r="H19" s="66"/>
-      <c r="I19" s="66"/>
-      <c r="J19" s="66"/>
-      <c r="K19" s="66"/>
-      <c r="L19" s="66"/>
-      <c r="M19" s="66"/>
-      <c r="N19" s="66"/>
-      <c r="O19" s="66"/>
-      <c r="P19" s="66"/>
-      <c r="Q19" s="66"/>
-      <c r="R19" s="66"/>
-      <c r="S19" s="66"/>
-      <c r="T19" s="66"/>
-      <c r="U19" s="66"/>
-      <c r="V19" s="66"/>
-      <c r="W19" s="66"/>
-      <c r="X19" s="66"/>
-      <c r="Y19" s="66"/>
-      <c r="Z19" s="66"/>
-      <c r="AA19" s="66"/>
-      <c r="AB19" s="66"/>
-      <c r="AC19" s="66"/>
-      <c r="AD19" s="66"/>
-      <c r="AE19" s="66"/>
-      <c r="AF19" s="66"/>
+      <c r="B19" s="65"/>
+      <c r="C19" s="65"/>
+      <c r="D19" s="65"/>
+      <c r="E19" s="65"/>
+      <c r="F19" s="65"/>
+      <c r="G19" s="65"/>
+      <c r="H19" s="65"/>
+      <c r="I19" s="65"/>
+      <c r="J19" s="65"/>
+      <c r="K19" s="65"/>
+      <c r="L19" s="65"/>
+      <c r="M19" s="65"/>
+      <c r="N19" s="65"/>
+      <c r="O19" s="65"/>
+      <c r="P19" s="65"/>
+      <c r="Q19" s="65"/>
+      <c r="R19" s="65"/>
+      <c r="S19" s="65"/>
+      <c r="T19" s="65"/>
+      <c r="U19" s="65"/>
+      <c r="V19" s="65"/>
+      <c r="W19" s="65"/>
+      <c r="X19" s="65"/>
+      <c r="Y19" s="65"/>
+      <c r="Z19" s="65"/>
+      <c r="AA19" s="65"/>
+      <c r="AB19" s="65"/>
+      <c r="AC19" s="65"/>
+      <c r="AD19" s="65"/>
+      <c r="AE19" s="65"/>
+      <c r="AF19" s="65"/>
     </row>
     <row r="20" spans="2:32" ht="5.0999999999999996" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B20" s="31"/>
@@ -4614,19 +4618,19 @@
       <c r="AF20" s="31"/>
     </row>
     <row r="21" spans="2:32" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B21" s="111" t="s">
+      <c r="B21" s="101" t="s">
         <v>65</v>
       </c>
-      <c r="C21" s="111"/>
-      <c r="D21" s="111"/>
-      <c r="E21" s="111"/>
-      <c r="F21" s="111"/>
-      <c r="G21" s="111"/>
-      <c r="H21" s="111"/>
-      <c r="I21" s="111"/>
-      <c r="J21" s="111"/>
-      <c r="K21" s="111"/>
-      <c r="L21" s="111"/>
+      <c r="C21" s="101"/>
+      <c r="D21" s="101"/>
+      <c r="E21" s="101"/>
+      <c r="F21" s="101"/>
+      <c r="G21" s="101"/>
+      <c r="H21" s="101"/>
+      <c r="I21" s="101"/>
+      <c r="J21" s="101"/>
+      <c r="K21" s="101"/>
+      <c r="L21" s="101"/>
     </row>
     <row r="22" spans="2:32" ht="5.0999999999999996" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B22" s="39"/>
@@ -4640,23 +4644,23 @@
     <row r="23" spans="2:32" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B23" s="39"/>
       <c r="C23" s="39"/>
-      <c r="D23" s="100" t="s">
+      <c r="D23" s="29" t="s">
         <v>63</v>
       </c>
-      <c r="E23" s="100"/>
-      <c r="F23" s="100"/>
-      <c r="G23" s="100"/>
-      <c r="H23" s="100"/>
-      <c r="I23" s="100"/>
-      <c r="J23" s="100"/>
-      <c r="K23" s="100"/>
-      <c r="L23" s="100"/>
-      <c r="M23" s="100"/>
-      <c r="N23" s="100"/>
-      <c r="O23" s="100"/>
-      <c r="P23" s="100"/>
-      <c r="Q23" s="100"/>
-      <c r="R23" s="100"/>
+      <c r="E23" s="29"/>
+      <c r="F23" s="29"/>
+      <c r="G23" s="29"/>
+      <c r="H23" s="29"/>
+      <c r="I23" s="29"/>
+      <c r="J23" s="29"/>
+      <c r="K23" s="29"/>
+      <c r="L23" s="29"/>
+      <c r="M23" s="29"/>
+      <c r="N23" s="29"/>
+      <c r="O23" s="29"/>
+      <c r="P23" s="29"/>
+      <c r="Q23" s="29"/>
+      <c r="R23" s="29"/>
     </row>
     <row r="24" spans="2:32" ht="5.0999999999999996" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B24" s="39"/>
@@ -4670,11 +4674,11 @@
     <row r="25" spans="2:32" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B25" s="39"/>
       <c r="C25" s="39"/>
-      <c r="D25" s="112"/>
+      <c r="D25" s="68"/>
       <c r="E25" s="32" t="s">
         <v>57</v>
       </c>
-      <c r="F25" s="112"/>
+      <c r="F25" s="68"/>
       <c r="G25" s="32" t="s">
         <v>58</v>
       </c>
@@ -4702,12 +4706,12 @@
       <c r="Z26" s="2"/>
     </row>
     <row r="27" spans="2:32" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B27" s="97" t="s">
+      <c r="B27" s="99" t="s">
         <v>55</v>
       </c>
-      <c r="C27" s="97"/>
-      <c r="D27" s="97"/>
-      <c r="E27" s="97"/>
+      <c r="C27" s="99"/>
+      <c r="D27" s="99"/>
+      <c r="E27" s="99"/>
       <c r="F27" s="114"/>
       <c r="G27" s="114"/>
       <c r="H27" s="114"/>
@@ -4743,12 +4747,12 @@
       <c r="E28" s="35"/>
     </row>
     <row r="29" spans="2:32" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B29" s="97" t="s">
+      <c r="B29" s="99" t="s">
         <v>25</v>
       </c>
-      <c r="C29" s="97"/>
-      <c r="D29" s="97"/>
-      <c r="E29" s="97"/>
+      <c r="C29" s="99"/>
+      <c r="D29" s="99"/>
+      <c r="E29" s="99"/>
       <c r="F29" s="98"/>
       <c r="G29" s="98"/>
       <c r="H29" s="98"/>
@@ -4784,12 +4788,12 @@
       <c r="E30" s="35"/>
     </row>
     <row r="31" spans="2:32" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B31" s="97" t="s">
+      <c r="B31" s="99" t="s">
         <v>26</v>
       </c>
-      <c r="C31" s="97"/>
-      <c r="D31" s="97"/>
-      <c r="E31" s="97"/>
+      <c r="C31" s="99"/>
+      <c r="D31" s="99"/>
+      <c r="E31" s="99"/>
       <c r="F31" s="98"/>
       <c r="G31" s="98"/>
       <c r="H31" s="98"/>
@@ -4806,59 +4810,59 @@
       </c>
       <c r="P31" s="29"/>
       <c r="Q31"/>
-      <c r="R31" s="113"/>
-      <c r="S31" s="113"/>
-      <c r="T31" s="113"/>
-      <c r="U31" s="113"/>
-      <c r="V31" s="113"/>
-      <c r="W31" s="97" t="s">
+      <c r="R31" s="97"/>
+      <c r="S31" s="97"/>
+      <c r="T31" s="97"/>
+      <c r="U31" s="97"/>
+      <c r="V31" s="97"/>
+      <c r="W31" s="99" t="s">
         <v>28</v>
       </c>
-      <c r="X31" s="97"/>
-      <c r="Y31" s="97"/>
-      <c r="Z31" s="97"/>
+      <c r="X31" s="99"/>
+      <c r="Y31" s="99"/>
+      <c r="Z31" s="99"/>
       <c r="AA31" s="36"/>
-      <c r="AB31" s="64"/>
-      <c r="AC31" s="64"/>
-      <c r="AD31" s="64"/>
-      <c r="AE31" s="64"/>
-      <c r="AF31" s="64"/>
+      <c r="AB31" s="63"/>
+      <c r="AC31" s="63"/>
+      <c r="AD31" s="63"/>
+      <c r="AE31" s="63"/>
+      <c r="AF31" s="63"/>
     </row>
     <row r="32" spans="2:32" ht="5.0999999999999996" customHeight="1" x14ac:dyDescent="0.35">
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
     </row>
     <row r="33" spans="2:32" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B33" s="97" t="s">
+      <c r="B33" s="99" t="s">
         <v>59</v>
       </c>
-      <c r="C33" s="97"/>
-      <c r="D33" s="97"/>
-      <c r="E33" s="97"/>
-      <c r="F33" s="99"/>
-      <c r="G33" s="99"/>
-      <c r="H33" s="99"/>
-      <c r="I33" s="99"/>
+      <c r="C33" s="99"/>
+      <c r="D33" s="99"/>
+      <c r="E33" s="99"/>
+      <c r="F33" s="102"/>
+      <c r="G33" s="102"/>
+      <c r="H33" s="102"/>
+      <c r="I33" s="102"/>
       <c r="J33" s="38"/>
-      <c r="K33" s="97" t="s">
+      <c r="K33" s="99" t="s">
         <v>70</v>
       </c>
-      <c r="L33" s="97"/>
-      <c r="M33" s="97"/>
-      <c r="N33" s="97"/>
-      <c r="O33" s="97"/>
-      <c r="P33" s="97"/>
-      <c r="Q33" s="64"/>
-      <c r="R33" s="64"/>
-      <c r="S33" s="64"/>
-      <c r="T33" s="64"/>
-      <c r="U33" s="64"/>
-      <c r="V33" s="64"/>
-      <c r="W33" s="64"/>
-      <c r="X33" s="64"/>
-      <c r="Y33" s="64"/>
-      <c r="Z33" s="64"/>
-      <c r="AA33" s="64"/>
+      <c r="L33" s="99"/>
+      <c r="M33" s="99"/>
+      <c r="N33" s="99"/>
+      <c r="O33" s="99"/>
+      <c r="P33" s="99"/>
+      <c r="Q33" s="63"/>
+      <c r="R33" s="63"/>
+      <c r="S33" s="63"/>
+      <c r="T33" s="63"/>
+      <c r="U33" s="63"/>
+      <c r="V33" s="63"/>
+      <c r="W33" s="63"/>
+      <c r="X33" s="63"/>
+      <c r="Y33" s="63"/>
+      <c r="Z33" s="63"/>
+      <c r="AA33" s="63"/>
       <c r="AB33" s="31"/>
       <c r="AC33" s="31"/>
       <c r="AD33" s="31"/>
@@ -4870,37 +4874,37 @@
       <c r="O34" s="2"/>
     </row>
     <row r="35" spans="2:32" ht="4.05" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B35" s="66"/>
-      <c r="C35" s="66"/>
-      <c r="D35" s="66"/>
-      <c r="E35" s="66"/>
-      <c r="F35" s="66"/>
-      <c r="G35" s="66"/>
-      <c r="H35" s="66"/>
-      <c r="I35" s="66"/>
-      <c r="J35" s="66"/>
-      <c r="K35" s="66"/>
-      <c r="L35" s="66"/>
-      <c r="M35" s="66"/>
-      <c r="N35" s="66"/>
-      <c r="O35" s="66"/>
-      <c r="P35" s="66"/>
-      <c r="Q35" s="66"/>
-      <c r="R35" s="66"/>
-      <c r="S35" s="66"/>
-      <c r="T35" s="66"/>
-      <c r="U35" s="66"/>
-      <c r="V35" s="66"/>
-      <c r="W35" s="66"/>
-      <c r="X35" s="66"/>
-      <c r="Y35" s="66"/>
-      <c r="Z35" s="66"/>
-      <c r="AA35" s="66"/>
-      <c r="AB35" s="66"/>
-      <c r="AC35" s="66"/>
-      <c r="AD35" s="66"/>
-      <c r="AE35" s="66"/>
-      <c r="AF35" s="66"/>
+      <c r="B35" s="65"/>
+      <c r="C35" s="65"/>
+      <c r="D35" s="65"/>
+      <c r="E35" s="65"/>
+      <c r="F35" s="65"/>
+      <c r="G35" s="65"/>
+      <c r="H35" s="65"/>
+      <c r="I35" s="65"/>
+      <c r="J35" s="65"/>
+      <c r="K35" s="65"/>
+      <c r="L35" s="65"/>
+      <c r="M35" s="65"/>
+      <c r="N35" s="65"/>
+      <c r="O35" s="65"/>
+      <c r="P35" s="65"/>
+      <c r="Q35" s="65"/>
+      <c r="R35" s="65"/>
+      <c r="S35" s="65"/>
+      <c r="T35" s="65"/>
+      <c r="U35" s="65"/>
+      <c r="V35" s="65"/>
+      <c r="W35" s="65"/>
+      <c r="X35" s="65"/>
+      <c r="Y35" s="65"/>
+      <c r="Z35" s="65"/>
+      <c r="AA35" s="65"/>
+      <c r="AB35" s="65"/>
+      <c r="AC35" s="65"/>
+      <c r="AD35" s="65"/>
+      <c r="AE35" s="65"/>
+      <c r="AF35" s="65"/>
     </row>
     <row r="36" spans="2:32" ht="5.0999999999999996" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="37" spans="2:32" ht="30" customHeight="1" x14ac:dyDescent="0.35">
@@ -4939,22 +4943,22 @@
       <c r="H39" s="31"/>
       <c r="I39" s="31"/>
       <c r="J39" s="31"/>
-      <c r="K39" s="97" t="s">
+      <c r="K39" s="99" t="s">
         <v>30</v>
       </c>
-      <c r="L39" s="97"/>
-      <c r="M39" s="97"/>
-      <c r="N39" s="98"/>
-      <c r="O39" s="98"/>
-      <c r="P39" s="98"/>
-      <c r="Q39" s="98"/>
-      <c r="R39" s="97" t="s">
+      <c r="L39" s="99"/>
+      <c r="M39" s="99"/>
+      <c r="N39" s="115"/>
+      <c r="O39" s="115"/>
+      <c r="P39" s="115"/>
+      <c r="Q39" s="115"/>
+      <c r="R39" s="99" t="s">
         <v>19</v>
       </c>
-      <c r="S39" s="97"/>
-      <c r="T39" s="97"/>
-      <c r="U39" s="97"/>
-      <c r="V39" s="97"/>
+      <c r="S39" s="99"/>
+      <c r="T39" s="99"/>
+      <c r="U39" s="99"/>
+      <c r="V39" s="99"/>
       <c r="W39" s="36"/>
       <c r="X39" s="36"/>
       <c r="Y39" s="36"/>
@@ -4968,61 +4972,61 @@
     </row>
     <row r="40" spans="2:32" ht="5.0999999999999996" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="41" spans="2:32" ht="4.05" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B41" s="66"/>
-      <c r="C41" s="66"/>
-      <c r="D41" s="66"/>
-      <c r="E41" s="66"/>
-      <c r="F41" s="66"/>
-      <c r="G41" s="66"/>
-      <c r="H41" s="66"/>
-      <c r="I41" s="66"/>
-      <c r="J41" s="66"/>
-      <c r="K41" s="66"/>
-      <c r="L41" s="66"/>
-      <c r="M41" s="66"/>
-      <c r="N41" s="66"/>
-      <c r="O41" s="66"/>
-      <c r="P41" s="66"/>
-      <c r="Q41" s="66"/>
-      <c r="R41" s="66"/>
-      <c r="S41" s="66"/>
-      <c r="T41" s="66"/>
-      <c r="U41" s="66"/>
-      <c r="V41" s="66"/>
-      <c r="W41" s="66"/>
-      <c r="X41" s="66"/>
-      <c r="Y41" s="66"/>
-      <c r="Z41" s="66"/>
-      <c r="AA41" s="66"/>
-      <c r="AB41" s="66"/>
-      <c r="AC41" s="66"/>
-      <c r="AD41" s="66"/>
-      <c r="AE41" s="66"/>
-      <c r="AF41" s="66"/>
+      <c r="B41" s="65"/>
+      <c r="C41" s="65"/>
+      <c r="D41" s="65"/>
+      <c r="E41" s="65"/>
+      <c r="F41" s="65"/>
+      <c r="G41" s="65"/>
+      <c r="H41" s="65"/>
+      <c r="I41" s="65"/>
+      <c r="J41" s="65"/>
+      <c r="K41" s="65"/>
+      <c r="L41" s="65"/>
+      <c r="M41" s="65"/>
+      <c r="N41" s="65"/>
+      <c r="O41" s="65"/>
+      <c r="P41" s="65"/>
+      <c r="Q41" s="65"/>
+      <c r="R41" s="65"/>
+      <c r="S41" s="65"/>
+      <c r="T41" s="65"/>
+      <c r="U41" s="65"/>
+      <c r="V41" s="65"/>
+      <c r="W41" s="65"/>
+      <c r="X41" s="65"/>
+      <c r="Y41" s="65"/>
+      <c r="Z41" s="65"/>
+      <c r="AA41" s="65"/>
+      <c r="AB41" s="65"/>
+      <c r="AC41" s="65"/>
+      <c r="AD41" s="65"/>
+      <c r="AE41" s="65"/>
+      <c r="AF41" s="65"/>
     </row>
     <row r="42" spans="2:32" ht="5.0999999999999996" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="43" spans="2:32" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B43" s="100" t="s">
+      <c r="B43" s="105" t="s">
         <v>67</v>
       </c>
-      <c r="C43" s="100"/>
-      <c r="D43" s="100"/>
-      <c r="E43" s="100"/>
-      <c r="F43" s="100"/>
-      <c r="G43" s="100"/>
-      <c r="H43" s="100"/>
+      <c r="C43" s="105"/>
+      <c r="D43" s="105"/>
+      <c r="E43" s="105"/>
+      <c r="F43" s="105"/>
+      <c r="G43" s="105"/>
+      <c r="H43" s="105"/>
     </row>
     <row r="44" spans="2:32" ht="5.0999999999999996" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="45" spans="2:32" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B45" s="100" t="s">
+      <c r="B45" s="105" t="s">
         <v>53</v>
       </c>
-      <c r="C45" s="100"/>
-      <c r="D45" s="100"/>
-      <c r="E45" s="100"/>
-      <c r="F45" s="100"/>
-      <c r="G45" s="100"/>
-      <c r="H45" s="100"/>
+      <c r="C45" s="105"/>
+      <c r="D45" s="105"/>
+      <c r="E45" s="105"/>
+      <c r="F45" s="105"/>
+      <c r="G45" s="105"/>
+      <c r="H45" s="105"/>
     </row>
     <row r="46" spans="2:32" ht="5.0999999999999996" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B46" s="32"/>
@@ -5067,7 +5071,7 @@
     </row>
     <row r="48" spans="2:32" ht="5.0999999999999996" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B48" s="32"/>
-      <c r="C48" s="63"/>
+      <c r="C48" s="62"/>
       <c r="D48" s="32"/>
       <c r="E48" s="32"/>
       <c r="F48" s="32"/>
@@ -5079,19 +5083,19 @@
     </row>
     <row r="49" spans="2:101" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C49" s="46"/>
-      <c r="D49" s="112"/>
-      <c r="E49" s="103" t="s">
+      <c r="D49" s="68"/>
+      <c r="E49" s="109" t="s">
         <v>56</v>
       </c>
-      <c r="F49" s="100"/>
-      <c r="G49" s="100"/>
-      <c r="H49" s="100"/>
+      <c r="F49" s="105"/>
+      <c r="G49" s="105"/>
+      <c r="H49" s="105"/>
       <c r="I49" s="32"/>
       <c r="J49" s="32"/>
       <c r="K49" s="32"/>
       <c r="U49" s="47"/>
       <c r="W49" s="46"/>
-      <c r="X49" s="112"/>
+      <c r="X49" s="68"/>
       <c r="Y49" s="29" t="s">
         <v>60</v>
       </c>
@@ -5129,15 +5133,15 @@
       <c r="T51" s="36"/>
       <c r="U51" s="47"/>
       <c r="W51" s="46"/>
-      <c r="X51" s="110" t="s">
+      <c r="X51" s="100" t="s">
         <v>21</v>
       </c>
-      <c r="Y51" s="110"/>
-      <c r="Z51" s="110"/>
-      <c r="AA51" s="110"/>
-      <c r="AB51" s="110"/>
-      <c r="AC51" s="110"/>
-      <c r="AD51" s="110"/>
+      <c r="Y51" s="100"/>
+      <c r="Z51" s="100"/>
+      <c r="AA51" s="100"/>
+      <c r="AB51" s="100"/>
+      <c r="AC51" s="100"/>
+      <c r="AD51" s="100"/>
       <c r="AE51" s="49"/>
       <c r="AF51" s="50"/>
     </row>
@@ -5149,13 +5153,13 @@
       <c r="K52" s="31"/>
       <c r="U52" s="47"/>
       <c r="W52" s="46"/>
-      <c r="X52" s="110"/>
-      <c r="Y52" s="110"/>
-      <c r="Z52" s="110"/>
-      <c r="AA52" s="110"/>
-      <c r="AB52" s="110"/>
-      <c r="AC52" s="110"/>
-      <c r="AD52" s="110"/>
+      <c r="X52" s="100"/>
+      <c r="Y52" s="100"/>
+      <c r="Z52" s="100"/>
+      <c r="AA52" s="100"/>
+      <c r="AB52" s="100"/>
+      <c r="AC52" s="100"/>
+      <c r="AD52" s="100"/>
       <c r="AE52" s="49"/>
       <c r="AF52" s="50"/>
     </row>
@@ -5167,13 +5171,13 @@
       <c r="K53" s="31"/>
       <c r="U53" s="47"/>
       <c r="W53" s="46"/>
-      <c r="X53" s="110"/>
-      <c r="Y53" s="110"/>
-      <c r="Z53" s="110"/>
-      <c r="AA53" s="110"/>
-      <c r="AB53" s="110"/>
-      <c r="AC53" s="110"/>
-      <c r="AD53" s="110"/>
+      <c r="X53" s="100"/>
+      <c r="Y53" s="100"/>
+      <c r="Z53" s="100"/>
+      <c r="AA53" s="100"/>
+      <c r="AB53" s="100"/>
+      <c r="AC53" s="100"/>
+      <c r="AD53" s="100"/>
       <c r="AE53" s="49"/>
       <c r="AF53" s="50"/>
     </row>
@@ -5185,13 +5189,13 @@
       <c r="K54" s="31"/>
       <c r="U54" s="47"/>
       <c r="W54" s="46"/>
-      <c r="X54" s="110"/>
-      <c r="Y54" s="110"/>
-      <c r="Z54" s="110"/>
-      <c r="AA54" s="110"/>
-      <c r="AB54" s="110"/>
-      <c r="AC54" s="110"/>
-      <c r="AD54" s="110"/>
+      <c r="X54" s="100"/>
+      <c r="Y54" s="100"/>
+      <c r="Z54" s="100"/>
+      <c r="AA54" s="100"/>
+      <c r="AB54" s="100"/>
+      <c r="AC54" s="100"/>
+      <c r="AD54" s="100"/>
       <c r="AE54" s="49"/>
       <c r="AF54" s="50"/>
     </row>
@@ -5208,27 +5212,27 @@
         <v>50</v>
       </c>
       <c r="K55" s="36"/>
-      <c r="N55" s="112"/>
+      <c r="N55" s="68"/>
       <c r="O55" s="32" t="s">
         <v>61</v>
       </c>
       <c r="P55" s="51"/>
       <c r="Q55" s="32"/>
-      <c r="R55" s="112"/>
-      <c r="S55" s="103" t="s">
+      <c r="R55" s="68"/>
+      <c r="S55" s="109" t="s">
         <v>62</v>
       </c>
-      <c r="T55" s="100"/>
+      <c r="T55" s="105"/>
       <c r="U55" s="52"/>
       <c r="V55" s="32"/>
       <c r="W55" s="46"/>
-      <c r="X55" s="110"/>
-      <c r="Y55" s="110"/>
-      <c r="Z55" s="110"/>
-      <c r="AA55" s="110"/>
-      <c r="AB55" s="110"/>
-      <c r="AC55" s="110"/>
-      <c r="AD55" s="110"/>
+      <c r="X55" s="100"/>
+      <c r="Y55" s="100"/>
+      <c r="Z55" s="100"/>
+      <c r="AA55" s="100"/>
+      <c r="AB55" s="100"/>
+      <c r="AC55" s="100"/>
+      <c r="AD55" s="100"/>
       <c r="AE55" s="49"/>
       <c r="AF55" s="50"/>
     </row>
@@ -5295,39 +5299,39 @@
     </row>
     <row r="58" spans="2:101" ht="5.0999999999999996" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="59" spans="2:101" s="60" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B59" s="106" t="s">
+      <c r="B59" s="113" t="s">
         <v>71</v>
       </c>
-      <c r="C59" s="106"/>
-      <c r="D59" s="106"/>
-      <c r="E59" s="106"/>
-      <c r="F59" s="106"/>
-      <c r="G59" s="106"/>
-      <c r="H59" s="106"/>
-      <c r="I59" s="106"/>
-      <c r="J59" s="106"/>
-      <c r="K59" s="106"/>
-      <c r="L59" s="106"/>
-      <c r="M59" s="106"/>
-      <c r="N59" s="106"/>
-      <c r="O59" s="106"/>
-      <c r="P59" s="106"/>
-      <c r="Q59" s="106"/>
-      <c r="R59" s="106"/>
-      <c r="S59" s="106"/>
-      <c r="T59" s="106"/>
-      <c r="U59" s="106"/>
-      <c r="V59" s="106"/>
-      <c r="W59" s="106"/>
-      <c r="X59" s="106"/>
-      <c r="Y59" s="106"/>
-      <c r="Z59" s="106"/>
-      <c r="AA59" s="106"/>
-      <c r="AB59" s="106"/>
-      <c r="AC59" s="106"/>
-      <c r="AD59" s="106"/>
-      <c r="AE59" s="106"/>
-      <c r="AF59" s="106"/>
+      <c r="C59" s="113"/>
+      <c r="D59" s="113"/>
+      <c r="E59" s="113"/>
+      <c r="F59" s="113"/>
+      <c r="G59" s="113"/>
+      <c r="H59" s="113"/>
+      <c r="I59" s="113"/>
+      <c r="J59" s="113"/>
+      <c r="K59" s="113"/>
+      <c r="L59" s="113"/>
+      <c r="M59" s="113"/>
+      <c r="N59" s="113"/>
+      <c r="O59" s="113"/>
+      <c r="P59" s="113"/>
+      <c r="Q59" s="113"/>
+      <c r="R59" s="113"/>
+      <c r="S59" s="113"/>
+      <c r="T59" s="113"/>
+      <c r="U59" s="113"/>
+      <c r="V59" s="113"/>
+      <c r="W59" s="113"/>
+      <c r="X59" s="113"/>
+      <c r="Y59" s="113"/>
+      <c r="Z59" s="113"/>
+      <c r="AA59" s="113"/>
+      <c r="AB59" s="113"/>
+      <c r="AC59" s="113"/>
+      <c r="AD59" s="113"/>
+      <c r="AE59" s="113"/>
+      <c r="AF59" s="113"/>
       <c r="AG59" s="31"/>
       <c r="AH59" s="31"/>
       <c r="AI59" s="31"/>
@@ -5399,37 +5403,37 @@
       <c r="CW59" s="31"/>
     </row>
     <row r="60" spans="2:101" s="60" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B60" s="106"/>
-      <c r="C60" s="106"/>
-      <c r="D60" s="106"/>
-      <c r="E60" s="106"/>
-      <c r="F60" s="106"/>
-      <c r="G60" s="106"/>
-      <c r="H60" s="106"/>
-      <c r="I60" s="106"/>
-      <c r="J60" s="106"/>
-      <c r="K60" s="106"/>
-      <c r="L60" s="106"/>
-      <c r="M60" s="106"/>
-      <c r="N60" s="106"/>
-      <c r="O60" s="106"/>
-      <c r="P60" s="106"/>
-      <c r="Q60" s="106"/>
-      <c r="R60" s="106"/>
-      <c r="S60" s="106"/>
-      <c r="T60" s="106"/>
-      <c r="U60" s="106"/>
-      <c r="V60" s="106"/>
-      <c r="W60" s="106"/>
-      <c r="X60" s="106"/>
-      <c r="Y60" s="106"/>
-      <c r="Z60" s="106"/>
-      <c r="AA60" s="106"/>
-      <c r="AB60" s="106"/>
-      <c r="AC60" s="106"/>
-      <c r="AD60" s="106"/>
-      <c r="AE60" s="106"/>
-      <c r="AF60" s="106"/>
+      <c r="B60" s="113"/>
+      <c r="C60" s="113"/>
+      <c r="D60" s="113"/>
+      <c r="E60" s="113"/>
+      <c r="F60" s="113"/>
+      <c r="G60" s="113"/>
+      <c r="H60" s="113"/>
+      <c r="I60" s="113"/>
+      <c r="J60" s="113"/>
+      <c r="K60" s="113"/>
+      <c r="L60" s="113"/>
+      <c r="M60" s="113"/>
+      <c r="N60" s="113"/>
+      <c r="O60" s="113"/>
+      <c r="P60" s="113"/>
+      <c r="Q60" s="113"/>
+      <c r="R60" s="113"/>
+      <c r="S60" s="113"/>
+      <c r="T60" s="113"/>
+      <c r="U60" s="113"/>
+      <c r="V60" s="113"/>
+      <c r="W60" s="113"/>
+      <c r="X60" s="113"/>
+      <c r="Y60" s="113"/>
+      <c r="Z60" s="113"/>
+      <c r="AA60" s="113"/>
+      <c r="AB60" s="113"/>
+      <c r="AC60" s="113"/>
+      <c r="AD60" s="113"/>
+      <c r="AE60" s="113"/>
+      <c r="AF60" s="113"/>
       <c r="AG60" s="31"/>
       <c r="AH60" s="31"/>
       <c r="AI60" s="31"/>
@@ -5501,37 +5505,37 @@
       <c r="CW60" s="31"/>
     </row>
     <row r="61" spans="2:101" s="60" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B61" s="106"/>
-      <c r="C61" s="106"/>
-      <c r="D61" s="106"/>
-      <c r="E61" s="106"/>
-      <c r="F61" s="106"/>
-      <c r="G61" s="106"/>
-      <c r="H61" s="106"/>
-      <c r="I61" s="106"/>
-      <c r="J61" s="106"/>
-      <c r="K61" s="106"/>
-      <c r="L61" s="106"/>
-      <c r="M61" s="106"/>
-      <c r="N61" s="106"/>
-      <c r="O61" s="106"/>
-      <c r="P61" s="106"/>
-      <c r="Q61" s="106"/>
-      <c r="R61" s="106"/>
-      <c r="S61" s="106"/>
-      <c r="T61" s="106"/>
-      <c r="U61" s="106"/>
-      <c r="V61" s="106"/>
-      <c r="W61" s="106"/>
-      <c r="X61" s="106"/>
-      <c r="Y61" s="106"/>
-      <c r="Z61" s="106"/>
-      <c r="AA61" s="106"/>
-      <c r="AB61" s="106"/>
-      <c r="AC61" s="106"/>
-      <c r="AD61" s="106"/>
-      <c r="AE61" s="106"/>
-      <c r="AF61" s="106"/>
+      <c r="B61" s="113"/>
+      <c r="C61" s="113"/>
+      <c r="D61" s="113"/>
+      <c r="E61" s="113"/>
+      <c r="F61" s="113"/>
+      <c r="G61" s="113"/>
+      <c r="H61" s="113"/>
+      <c r="I61" s="113"/>
+      <c r="J61" s="113"/>
+      <c r="K61" s="113"/>
+      <c r="L61" s="113"/>
+      <c r="M61" s="113"/>
+      <c r="N61" s="113"/>
+      <c r="O61" s="113"/>
+      <c r="P61" s="113"/>
+      <c r="Q61" s="113"/>
+      <c r="R61" s="113"/>
+      <c r="S61" s="113"/>
+      <c r="T61" s="113"/>
+      <c r="U61" s="113"/>
+      <c r="V61" s="113"/>
+      <c r="W61" s="113"/>
+      <c r="X61" s="113"/>
+      <c r="Y61" s="113"/>
+      <c r="Z61" s="113"/>
+      <c r="AA61" s="113"/>
+      <c r="AB61" s="113"/>
+      <c r="AC61" s="113"/>
+      <c r="AD61" s="113"/>
+      <c r="AE61" s="113"/>
+      <c r="AF61" s="113"/>
       <c r="AG61" s="31"/>
       <c r="AH61" s="31"/>
       <c r="AI61" s="31"/>
@@ -5603,37 +5607,37 @@
       <c r="CW61" s="31"/>
     </row>
     <row r="62" spans="2:101" s="60" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B62" s="106"/>
-      <c r="C62" s="106"/>
-      <c r="D62" s="106"/>
-      <c r="E62" s="106"/>
-      <c r="F62" s="106"/>
-      <c r="G62" s="106"/>
-      <c r="H62" s="106"/>
-      <c r="I62" s="106"/>
-      <c r="J62" s="106"/>
-      <c r="K62" s="106"/>
-      <c r="L62" s="106"/>
-      <c r="M62" s="106"/>
-      <c r="N62" s="106"/>
-      <c r="O62" s="106"/>
-      <c r="P62" s="106"/>
-      <c r="Q62" s="106"/>
-      <c r="R62" s="106"/>
-      <c r="S62" s="106"/>
-      <c r="T62" s="106"/>
-      <c r="U62" s="106"/>
-      <c r="V62" s="106"/>
-      <c r="W62" s="106"/>
-      <c r="X62" s="106"/>
-      <c r="Y62" s="106"/>
-      <c r="Z62" s="106"/>
-      <c r="AA62" s="106"/>
-      <c r="AB62" s="106"/>
-      <c r="AC62" s="106"/>
-      <c r="AD62" s="106"/>
-      <c r="AE62" s="106"/>
-      <c r="AF62" s="106"/>
+      <c r="B62" s="113"/>
+      <c r="C62" s="113"/>
+      <c r="D62" s="113"/>
+      <c r="E62" s="113"/>
+      <c r="F62" s="113"/>
+      <c r="G62" s="113"/>
+      <c r="H62" s="113"/>
+      <c r="I62" s="113"/>
+      <c r="J62" s="113"/>
+      <c r="K62" s="113"/>
+      <c r="L62" s="113"/>
+      <c r="M62" s="113"/>
+      <c r="N62" s="113"/>
+      <c r="O62" s="113"/>
+      <c r="P62" s="113"/>
+      <c r="Q62" s="113"/>
+      <c r="R62" s="113"/>
+      <c r="S62" s="113"/>
+      <c r="T62" s="113"/>
+      <c r="U62" s="113"/>
+      <c r="V62" s="113"/>
+      <c r="W62" s="113"/>
+      <c r="X62" s="113"/>
+      <c r="Y62" s="113"/>
+      <c r="Z62" s="113"/>
+      <c r="AA62" s="113"/>
+      <c r="AB62" s="113"/>
+      <c r="AC62" s="113"/>
+      <c r="AD62" s="113"/>
+      <c r="AE62" s="113"/>
+      <c r="AF62" s="113"/>
       <c r="AG62" s="31"/>
       <c r="AH62" s="31"/>
       <c r="AI62" s="31"/>
@@ -5705,37 +5709,37 @@
       <c r="CW62" s="31"/>
     </row>
     <row r="63" spans="2:101" s="60" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B63" s="106"/>
-      <c r="C63" s="106"/>
-      <c r="D63" s="106"/>
-      <c r="E63" s="106"/>
-      <c r="F63" s="106"/>
-      <c r="G63" s="106"/>
-      <c r="H63" s="106"/>
-      <c r="I63" s="106"/>
-      <c r="J63" s="106"/>
-      <c r="K63" s="106"/>
-      <c r="L63" s="106"/>
-      <c r="M63" s="106"/>
-      <c r="N63" s="106"/>
-      <c r="O63" s="106"/>
-      <c r="P63" s="106"/>
-      <c r="Q63" s="106"/>
-      <c r="R63" s="106"/>
-      <c r="S63" s="106"/>
-      <c r="T63" s="106"/>
-      <c r="U63" s="106"/>
-      <c r="V63" s="106"/>
-      <c r="W63" s="106"/>
-      <c r="X63" s="106"/>
-      <c r="Y63" s="106"/>
-      <c r="Z63" s="106"/>
-      <c r="AA63" s="106"/>
-      <c r="AB63" s="106"/>
-      <c r="AC63" s="106"/>
-      <c r="AD63" s="106"/>
-      <c r="AE63" s="106"/>
-      <c r="AF63" s="106"/>
+      <c r="B63" s="113"/>
+      <c r="C63" s="113"/>
+      <c r="D63" s="113"/>
+      <c r="E63" s="113"/>
+      <c r="F63" s="113"/>
+      <c r="G63" s="113"/>
+      <c r="H63" s="113"/>
+      <c r="I63" s="113"/>
+      <c r="J63" s="113"/>
+      <c r="K63" s="113"/>
+      <c r="L63" s="113"/>
+      <c r="M63" s="113"/>
+      <c r="N63" s="113"/>
+      <c r="O63" s="113"/>
+      <c r="P63" s="113"/>
+      <c r="Q63" s="113"/>
+      <c r="R63" s="113"/>
+      <c r="S63" s="113"/>
+      <c r="T63" s="113"/>
+      <c r="U63" s="113"/>
+      <c r="V63" s="113"/>
+      <c r="W63" s="113"/>
+      <c r="X63" s="113"/>
+      <c r="Y63" s="113"/>
+      <c r="Z63" s="113"/>
+      <c r="AA63" s="113"/>
+      <c r="AB63" s="113"/>
+      <c r="AC63" s="113"/>
+      <c r="AD63" s="113"/>
+      <c r="AE63" s="113"/>
+      <c r="AF63" s="113"/>
       <c r="AG63" s="31"/>
       <c r="AH63" s="31"/>
       <c r="AI63" s="31"/>
@@ -5807,37 +5811,37 @@
       <c r="CW63" s="31"/>
     </row>
     <row r="64" spans="2:101" s="60" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B64" s="106"/>
-      <c r="C64" s="106"/>
-      <c r="D64" s="106"/>
-      <c r="E64" s="106"/>
-      <c r="F64" s="106"/>
-      <c r="G64" s="106"/>
-      <c r="H64" s="106"/>
-      <c r="I64" s="106"/>
-      <c r="J64" s="106"/>
-      <c r="K64" s="106"/>
-      <c r="L64" s="106"/>
-      <c r="M64" s="106"/>
-      <c r="N64" s="106"/>
-      <c r="O64" s="106"/>
-      <c r="P64" s="106"/>
-      <c r="Q64" s="106"/>
-      <c r="R64" s="106"/>
-      <c r="S64" s="106"/>
-      <c r="T64" s="106"/>
-      <c r="U64" s="106"/>
-      <c r="V64" s="106"/>
-      <c r="W64" s="106"/>
-      <c r="X64" s="106"/>
-      <c r="Y64" s="106"/>
-      <c r="Z64" s="106"/>
-      <c r="AA64" s="106"/>
-      <c r="AB64" s="106"/>
-      <c r="AC64" s="106"/>
-      <c r="AD64" s="106"/>
-      <c r="AE64" s="106"/>
-      <c r="AF64" s="106"/>
+      <c r="B64" s="113"/>
+      <c r="C64" s="113"/>
+      <c r="D64" s="113"/>
+      <c r="E64" s="113"/>
+      <c r="F64" s="113"/>
+      <c r="G64" s="113"/>
+      <c r="H64" s="113"/>
+      <c r="I64" s="113"/>
+      <c r="J64" s="113"/>
+      <c r="K64" s="113"/>
+      <c r="L64" s="113"/>
+      <c r="M64" s="113"/>
+      <c r="N64" s="113"/>
+      <c r="O64" s="113"/>
+      <c r="P64" s="113"/>
+      <c r="Q64" s="113"/>
+      <c r="R64" s="113"/>
+      <c r="S64" s="113"/>
+      <c r="T64" s="113"/>
+      <c r="U64" s="113"/>
+      <c r="V64" s="113"/>
+      <c r="W64" s="113"/>
+      <c r="X64" s="113"/>
+      <c r="Y64" s="113"/>
+      <c r="Z64" s="113"/>
+      <c r="AA64" s="113"/>
+      <c r="AB64" s="113"/>
+      <c r="AC64" s="113"/>
+      <c r="AD64" s="113"/>
+      <c r="AE64" s="113"/>
+      <c r="AF64" s="113"/>
       <c r="AG64" s="31"/>
       <c r="AH64" s="31"/>
       <c r="AI64" s="31"/>
@@ -5909,37 +5913,37 @@
       <c r="CW64" s="31"/>
     </row>
     <row r="65" spans="2:101" s="60" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B65" s="106"/>
-      <c r="C65" s="106"/>
-      <c r="D65" s="106"/>
-      <c r="E65" s="106"/>
-      <c r="F65" s="106"/>
-      <c r="G65" s="106"/>
-      <c r="H65" s="106"/>
-      <c r="I65" s="106"/>
-      <c r="J65" s="106"/>
-      <c r="K65" s="106"/>
-      <c r="L65" s="106"/>
-      <c r="M65" s="106"/>
-      <c r="N65" s="106"/>
-      <c r="O65" s="106"/>
-      <c r="P65" s="106"/>
-      <c r="Q65" s="106"/>
-      <c r="R65" s="106"/>
-      <c r="S65" s="106"/>
-      <c r="T65" s="106"/>
-      <c r="U65" s="106"/>
-      <c r="V65" s="106"/>
-      <c r="W65" s="106"/>
-      <c r="X65" s="106"/>
-      <c r="Y65" s="106"/>
-      <c r="Z65" s="106"/>
-      <c r="AA65" s="106"/>
-      <c r="AB65" s="106"/>
-      <c r="AC65" s="106"/>
-      <c r="AD65" s="106"/>
-      <c r="AE65" s="106"/>
-      <c r="AF65" s="106"/>
+      <c r="B65" s="113"/>
+      <c r="C65" s="113"/>
+      <c r="D65" s="113"/>
+      <c r="E65" s="113"/>
+      <c r="F65" s="113"/>
+      <c r="G65" s="113"/>
+      <c r="H65" s="113"/>
+      <c r="I65" s="113"/>
+      <c r="J65" s="113"/>
+      <c r="K65" s="113"/>
+      <c r="L65" s="113"/>
+      <c r="M65" s="113"/>
+      <c r="N65" s="113"/>
+      <c r="O65" s="113"/>
+      <c r="P65" s="113"/>
+      <c r="Q65" s="113"/>
+      <c r="R65" s="113"/>
+      <c r="S65" s="113"/>
+      <c r="T65" s="113"/>
+      <c r="U65" s="113"/>
+      <c r="V65" s="113"/>
+      <c r="W65" s="113"/>
+      <c r="X65" s="113"/>
+      <c r="Y65" s="113"/>
+      <c r="Z65" s="113"/>
+      <c r="AA65" s="113"/>
+      <c r="AB65" s="113"/>
+      <c r="AC65" s="113"/>
+      <c r="AD65" s="113"/>
+      <c r="AE65" s="113"/>
+      <c r="AF65" s="113"/>
       <c r="AG65" s="31"/>
       <c r="AH65" s="31"/>
       <c r="AI65" s="31"/>
@@ -6011,136 +6015,136 @@
       <c r="CW65" s="31"/>
     </row>
     <row r="66" spans="2:101" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B66" s="106"/>
-      <c r="C66" s="106"/>
-      <c r="D66" s="106"/>
-      <c r="E66" s="106"/>
-      <c r="F66" s="106"/>
-      <c r="G66" s="106"/>
-      <c r="H66" s="106"/>
-      <c r="I66" s="106"/>
-      <c r="J66" s="106"/>
-      <c r="K66" s="106"/>
-      <c r="L66" s="106"/>
-      <c r="M66" s="106"/>
-      <c r="N66" s="106"/>
-      <c r="O66" s="106"/>
-      <c r="P66" s="106"/>
-      <c r="Q66" s="106"/>
-      <c r="R66" s="106"/>
-      <c r="S66" s="106"/>
-      <c r="T66" s="106"/>
-      <c r="U66" s="106"/>
-      <c r="V66" s="106"/>
-      <c r="W66" s="106"/>
-      <c r="X66" s="106"/>
-      <c r="Y66" s="106"/>
-      <c r="Z66" s="106"/>
-      <c r="AA66" s="106"/>
-      <c r="AB66" s="106"/>
-      <c r="AC66" s="106"/>
-      <c r="AD66" s="106"/>
-      <c r="AE66" s="106"/>
-      <c r="AF66" s="106"/>
+      <c r="B66" s="113"/>
+      <c r="C66" s="113"/>
+      <c r="D66" s="113"/>
+      <c r="E66" s="113"/>
+      <c r="F66" s="113"/>
+      <c r="G66" s="113"/>
+      <c r="H66" s="113"/>
+      <c r="I66" s="113"/>
+      <c r="J66" s="113"/>
+      <c r="K66" s="113"/>
+      <c r="L66" s="113"/>
+      <c r="M66" s="113"/>
+      <c r="N66" s="113"/>
+      <c r="O66" s="113"/>
+      <c r="P66" s="113"/>
+      <c r="Q66" s="113"/>
+      <c r="R66" s="113"/>
+      <c r="S66" s="113"/>
+      <c r="T66" s="113"/>
+      <c r="U66" s="113"/>
+      <c r="V66" s="113"/>
+      <c r="W66" s="113"/>
+      <c r="X66" s="113"/>
+      <c r="Y66" s="113"/>
+      <c r="Z66" s="113"/>
+      <c r="AA66" s="113"/>
+      <c r="AB66" s="113"/>
+      <c r="AC66" s="113"/>
+      <c r="AD66" s="113"/>
+      <c r="AE66" s="113"/>
+      <c r="AF66" s="113"/>
     </row>
     <row r="67" spans="2:101" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B67" s="106"/>
-      <c r="C67" s="106"/>
-      <c r="D67" s="106"/>
-      <c r="E67" s="106"/>
-      <c r="F67" s="106"/>
-      <c r="G67" s="106"/>
-      <c r="H67" s="106"/>
-      <c r="I67" s="106"/>
-      <c r="J67" s="106"/>
-      <c r="K67" s="106"/>
-      <c r="L67" s="106"/>
-      <c r="M67" s="106"/>
-      <c r="N67" s="106"/>
-      <c r="O67" s="106"/>
-      <c r="P67" s="106"/>
-      <c r="Q67" s="106"/>
-      <c r="R67" s="106"/>
-      <c r="S67" s="106"/>
-      <c r="T67" s="106"/>
-      <c r="U67" s="106"/>
-      <c r="V67" s="106"/>
-      <c r="W67" s="106"/>
-      <c r="X67" s="106"/>
-      <c r="Y67" s="106"/>
-      <c r="Z67" s="106"/>
-      <c r="AA67" s="106"/>
-      <c r="AB67" s="106"/>
-      <c r="AC67" s="106"/>
-      <c r="AD67" s="106"/>
-      <c r="AE67" s="106"/>
-      <c r="AF67" s="106"/>
+      <c r="B67" s="113"/>
+      <c r="C67" s="113"/>
+      <c r="D67" s="113"/>
+      <c r="E67" s="113"/>
+      <c r="F67" s="113"/>
+      <c r="G67" s="113"/>
+      <c r="H67" s="113"/>
+      <c r="I67" s="113"/>
+      <c r="J67" s="113"/>
+      <c r="K67" s="113"/>
+      <c r="L67" s="113"/>
+      <c r="M67" s="113"/>
+      <c r="N67" s="113"/>
+      <c r="O67" s="113"/>
+      <c r="P67" s="113"/>
+      <c r="Q67" s="113"/>
+      <c r="R67" s="113"/>
+      <c r="S67" s="113"/>
+      <c r="T67" s="113"/>
+      <c r="U67" s="113"/>
+      <c r="V67" s="113"/>
+      <c r="W67" s="113"/>
+      <c r="X67" s="113"/>
+      <c r="Y67" s="113"/>
+      <c r="Z67" s="113"/>
+      <c r="AA67" s="113"/>
+      <c r="AB67" s="113"/>
+      <c r="AC67" s="113"/>
+      <c r="AD67" s="113"/>
+      <c r="AE67" s="113"/>
+      <c r="AF67" s="113"/>
     </row>
     <row r="68" spans="2:101" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B68" s="106"/>
-      <c r="C68" s="106"/>
-      <c r="D68" s="106"/>
-      <c r="E68" s="106"/>
-      <c r="F68" s="106"/>
-      <c r="G68" s="106"/>
-      <c r="H68" s="106"/>
-      <c r="I68" s="106"/>
-      <c r="J68" s="106"/>
-      <c r="K68" s="106"/>
-      <c r="L68" s="106"/>
-      <c r="M68" s="106"/>
-      <c r="N68" s="106"/>
-      <c r="O68" s="106"/>
-      <c r="P68" s="106"/>
-      <c r="Q68" s="106"/>
-      <c r="R68" s="106"/>
-      <c r="S68" s="106"/>
-      <c r="T68" s="106"/>
-      <c r="U68" s="106"/>
-      <c r="V68" s="106"/>
-      <c r="W68" s="106"/>
-      <c r="X68" s="106"/>
-      <c r="Y68" s="106"/>
-      <c r="Z68" s="106"/>
-      <c r="AA68" s="106"/>
-      <c r="AB68" s="106"/>
-      <c r="AC68" s="106"/>
-      <c r="AD68" s="106"/>
-      <c r="AE68" s="106"/>
-      <c r="AF68" s="106"/>
+      <c r="B68" s="113"/>
+      <c r="C68" s="113"/>
+      <c r="D68" s="113"/>
+      <c r="E68" s="113"/>
+      <c r="F68" s="113"/>
+      <c r="G68" s="113"/>
+      <c r="H68" s="113"/>
+      <c r="I68" s="113"/>
+      <c r="J68" s="113"/>
+      <c r="K68" s="113"/>
+      <c r="L68" s="113"/>
+      <c r="M68" s="113"/>
+      <c r="N68" s="113"/>
+      <c r="O68" s="113"/>
+      <c r="P68" s="113"/>
+      <c r="Q68" s="113"/>
+      <c r="R68" s="113"/>
+      <c r="S68" s="113"/>
+      <c r="T68" s="113"/>
+      <c r="U68" s="113"/>
+      <c r="V68" s="113"/>
+      <c r="W68" s="113"/>
+      <c r="X68" s="113"/>
+      <c r="Y68" s="113"/>
+      <c r="Z68" s="113"/>
+      <c r="AA68" s="113"/>
+      <c r="AB68" s="113"/>
+      <c r="AC68" s="113"/>
+      <c r="AD68" s="113"/>
+      <c r="AE68" s="113"/>
+      <c r="AF68" s="113"/>
     </row>
     <row r="69" spans="2:101" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B69" s="106"/>
-      <c r="C69" s="106"/>
-      <c r="D69" s="106"/>
-      <c r="E69" s="106"/>
-      <c r="F69" s="106"/>
-      <c r="G69" s="106"/>
-      <c r="H69" s="106"/>
-      <c r="I69" s="106"/>
-      <c r="J69" s="106"/>
-      <c r="K69" s="106"/>
-      <c r="L69" s="106"/>
-      <c r="M69" s="106"/>
-      <c r="N69" s="106"/>
-      <c r="O69" s="106"/>
-      <c r="P69" s="106"/>
-      <c r="Q69" s="106"/>
-      <c r="R69" s="106"/>
-      <c r="S69" s="106"/>
-      <c r="T69" s="106"/>
-      <c r="U69" s="106"/>
-      <c r="V69" s="106"/>
-      <c r="W69" s="106"/>
-      <c r="X69" s="106"/>
-      <c r="Y69" s="106"/>
-      <c r="Z69" s="106"/>
-      <c r="AA69" s="106"/>
-      <c r="AB69" s="106"/>
-      <c r="AC69" s="106"/>
-      <c r="AD69" s="106"/>
-      <c r="AE69" s="106"/>
-      <c r="AF69" s="106"/>
+      <c r="B69" s="113"/>
+      <c r="C69" s="113"/>
+      <c r="D69" s="113"/>
+      <c r="E69" s="113"/>
+      <c r="F69" s="113"/>
+      <c r="G69" s="113"/>
+      <c r="H69" s="113"/>
+      <c r="I69" s="113"/>
+      <c r="J69" s="113"/>
+      <c r="K69" s="113"/>
+      <c r="L69" s="113"/>
+      <c r="M69" s="113"/>
+      <c r="N69" s="113"/>
+      <c r="O69" s="113"/>
+      <c r="P69" s="113"/>
+      <c r="Q69" s="113"/>
+      <c r="R69" s="113"/>
+      <c r="S69" s="113"/>
+      <c r="T69" s="113"/>
+      <c r="U69" s="113"/>
+      <c r="V69" s="113"/>
+      <c r="W69" s="113"/>
+      <c r="X69" s="113"/>
+      <c r="Y69" s="113"/>
+      <c r="Z69" s="113"/>
+      <c r="AA69" s="113"/>
+      <c r="AB69" s="113"/>
+      <c r="AC69" s="113"/>
+      <c r="AD69" s="113"/>
+      <c r="AE69" s="113"/>
+      <c r="AF69" s="113"/>
     </row>
     <row r="70" spans="2:101" ht="5.0999999999999996" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B70" s="50"/>
@@ -6178,25 +6182,25 @@
     <row r="71" spans="2:101" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="F71"/>
       <c r="G71"/>
-      <c r="H71" s="61"/>
-      <c r="I71" s="61"/>
-      <c r="J71" s="61"/>
-      <c r="K71" s="61"/>
-      <c r="L71" s="61"/>
-      <c r="M71" s="104">
+      <c r="H71" s="116"/>
+      <c r="I71" s="116"/>
+      <c r="J71" s="116"/>
+      <c r="K71" s="116"/>
+      <c r="L71" s="116"/>
+      <c r="M71" s="110">
         <f ca="1">TODAY()</f>
         <v>46156</v>
       </c>
-      <c r="N71" s="104"/>
-      <c r="O71" s="104"/>
-      <c r="P71" s="104"/>
-      <c r="Q71" s="104"/>
-      <c r="R71" s="104"/>
-      <c r="S71" s="104"/>
-      <c r="T71" s="104"/>
-      <c r="U71" s="104"/>
-      <c r="V71" s="104"/>
-      <c r="W71" s="104"/>
+      <c r="N71" s="110"/>
+      <c r="O71" s="110"/>
+      <c r="P71" s="110"/>
+      <c r="Q71" s="110"/>
+      <c r="R71" s="110"/>
+      <c r="S71" s="110"/>
+      <c r="T71" s="110"/>
+      <c r="U71" s="110"/>
+      <c r="V71" s="110"/>
+      <c r="W71" s="110"/>
     </row>
     <row r="72" spans="2:101" ht="5.0999999999999996" customHeight="1" x14ac:dyDescent="0.35">
       <c r="I72" s="31"/>
@@ -6210,76 +6214,76 @@
       <c r="Q72" s="31"/>
       <c r="R72" s="31"/>
       <c r="S72" s="31"/>
-      <c r="T72" s="62"/>
-      <c r="U72" s="62"/>
-      <c r="V72" s="62"/>
-      <c r="W72" s="62"/>
-      <c r="X72" s="62"/>
-      <c r="Y72" s="62"/>
-      <c r="Z72" s="62"/>
+      <c r="T72" s="61"/>
+      <c r="U72" s="61"/>
+      <c r="V72" s="61"/>
+      <c r="W72" s="61"/>
+      <c r="X72" s="61"/>
+      <c r="Y72" s="61"/>
+      <c r="Z72" s="61"/>
     </row>
     <row r="73" spans="2:101" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B73" s="105"/>
-      <c r="C73" s="105"/>
-      <c r="D73" s="105"/>
-      <c r="E73" s="105"/>
-      <c r="F73" s="105"/>
-      <c r="G73" s="105"/>
-      <c r="H73" s="105"/>
-      <c r="I73" s="105"/>
-      <c r="J73" s="105"/>
-      <c r="K73" s="105"/>
-      <c r="L73" s="105"/>
-      <c r="M73" s="105"/>
-      <c r="N73" s="105"/>
-      <c r="O73" s="105"/>
-      <c r="P73" s="105"/>
-      <c r="Q73" s="105"/>
-      <c r="R73" s="105"/>
-      <c r="S73" s="105"/>
-      <c r="T73" s="105"/>
-      <c r="U73" s="105"/>
-      <c r="V73" s="105"/>
-      <c r="W73" s="105"/>
-      <c r="X73" s="105"/>
-      <c r="Y73" s="105"/>
+      <c r="B73" s="111"/>
+      <c r="C73" s="111"/>
+      <c r="D73" s="111"/>
+      <c r="E73" s="111"/>
+      <c r="F73" s="111"/>
+      <c r="G73" s="111"/>
+      <c r="H73" s="111"/>
+      <c r="I73" s="111"/>
+      <c r="J73" s="111"/>
+      <c r="K73" s="111"/>
+      <c r="L73" s="111"/>
+      <c r="M73" s="111"/>
+      <c r="N73" s="111"/>
+      <c r="O73" s="111"/>
+      <c r="P73" s="111"/>
+      <c r="Q73" s="111"/>
+      <c r="R73" s="111"/>
+      <c r="S73" s="111"/>
+      <c r="T73" s="111"/>
+      <c r="U73" s="111"/>
+      <c r="V73" s="111"/>
+      <c r="W73" s="111"/>
+      <c r="X73" s="111"/>
+      <c r="Y73" s="111"/>
       <c r="Z73" s="31"/>
-      <c r="AA73" s="102" t="s">
+      <c r="AA73" s="108" t="s">
         <v>51</v>
       </c>
-      <c r="AB73" s="101"/>
-      <c r="AC73" s="115"/>
-      <c r="AD73" s="115"/>
-      <c r="AE73" s="115"/>
-      <c r="AF73" s="115"/>
+      <c r="AB73" s="107"/>
+      <c r="AC73" s="112"/>
+      <c r="AD73" s="112"/>
+      <c r="AE73" s="112"/>
+      <c r="AF73" s="112"/>
     </row>
     <row r="74" spans="2:101" s="60" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B74" s="101" t="s">
+      <c r="B74" s="107" t="s">
         <v>68</v>
       </c>
-      <c r="C74" s="101"/>
-      <c r="D74" s="101"/>
-      <c r="E74" s="101"/>
-      <c r="F74" s="101"/>
-      <c r="G74" s="101"/>
-      <c r="H74" s="101"/>
-      <c r="I74" s="101"/>
-      <c r="J74" s="101"/>
-      <c r="K74" s="101"/>
-      <c r="L74" s="101"/>
-      <c r="M74" s="101"/>
-      <c r="N74" s="101"/>
-      <c r="O74" s="101"/>
-      <c r="P74" s="101"/>
-      <c r="Q74" s="101"/>
-      <c r="R74" s="101"/>
-      <c r="S74" s="101"/>
-      <c r="T74" s="101"/>
-      <c r="U74" s="101"/>
-      <c r="V74" s="101"/>
-      <c r="W74" s="101"/>
-      <c r="X74" s="101"/>
-      <c r="Y74" s="101"/>
+      <c r="C74" s="107"/>
+      <c r="D74" s="107"/>
+      <c r="E74" s="107"/>
+      <c r="F74" s="107"/>
+      <c r="G74" s="107"/>
+      <c r="H74" s="107"/>
+      <c r="I74" s="107"/>
+      <c r="J74" s="107"/>
+      <c r="K74" s="107"/>
+      <c r="L74" s="107"/>
+      <c r="M74" s="107"/>
+      <c r="N74" s="107"/>
+      <c r="O74" s="107"/>
+      <c r="P74" s="107"/>
+      <c r="Q74" s="107"/>
+      <c r="R74" s="107"/>
+      <c r="S74" s="107"/>
+      <c r="T74" s="107"/>
+      <c r="U74" s="107"/>
+      <c r="V74" s="107"/>
+      <c r="W74" s="107"/>
+      <c r="X74" s="107"/>
+      <c r="Y74" s="107"/>
       <c r="Z74" s="29"/>
       <c r="AA74" s="29"/>
       <c r="AB74" s="29"/>
@@ -6358,11 +6362,11 @@
       <c r="CW74" s="31"/>
     </row>
     <row r="75" spans="2:101" x14ac:dyDescent="0.35">
-      <c r="B75" s="67" t="s">
+      <c r="B75" s="66" t="s">
         <v>74</v>
       </c>
-      <c r="C75" s="68"/>
-      <c r="D75" s="68"/>
+      <c r="C75" s="67"/>
+      <c r="D75" s="67"/>
     </row>
     <row r="79" spans="2:101" x14ac:dyDescent="0.35">
       <c r="E79" s="31"/>
@@ -6619,30 +6623,14 @@
     </row>
   </sheetData>
   <mergeCells count="48">
-    <mergeCell ref="R31:V31"/>
-    <mergeCell ref="R17:V17"/>
-    <mergeCell ref="W17:Z17"/>
-    <mergeCell ref="X51:AD55"/>
-    <mergeCell ref="F51:I51"/>
-    <mergeCell ref="F55:I55"/>
-    <mergeCell ref="N51:R51"/>
-    <mergeCell ref="B21:L21"/>
-    <mergeCell ref="B27:E27"/>
-    <mergeCell ref="B33:E33"/>
-    <mergeCell ref="F33:I33"/>
-    <mergeCell ref="K39:M39"/>
-    <mergeCell ref="N39:Q39"/>
-    <mergeCell ref="R39:V39"/>
-    <mergeCell ref="K33:P33"/>
-    <mergeCell ref="D7:AF7"/>
-    <mergeCell ref="I1:Z5"/>
-    <mergeCell ref="B9:H9"/>
-    <mergeCell ref="F11:H11"/>
-    <mergeCell ref="J11:L11"/>
-    <mergeCell ref="AB11:AC11"/>
-    <mergeCell ref="B11:E11"/>
-    <mergeCell ref="Y11:AA11"/>
-    <mergeCell ref="P11:X11"/>
+    <mergeCell ref="H71:L71"/>
+    <mergeCell ref="B13:E13"/>
+    <mergeCell ref="F13:AF13"/>
+    <mergeCell ref="F27:AF27"/>
+    <mergeCell ref="F17:I17"/>
+    <mergeCell ref="B17:E17"/>
+    <mergeCell ref="B15:E15"/>
+    <mergeCell ref="L17:M17"/>
     <mergeCell ref="B74:Y74"/>
     <mergeCell ref="B29:E29"/>
     <mergeCell ref="F29:AF29"/>
@@ -6659,14 +6647,30 @@
     <mergeCell ref="L31:M31"/>
     <mergeCell ref="B59:AF69"/>
     <mergeCell ref="W31:Z31"/>
-    <mergeCell ref="B13:E13"/>
-    <mergeCell ref="F13:AF13"/>
-    <mergeCell ref="F27:AF27"/>
-    <mergeCell ref="F17:I17"/>
-    <mergeCell ref="B17:E17"/>
-    <mergeCell ref="B15:E15"/>
-    <mergeCell ref="L17:M17"/>
-    <mergeCell ref="D23:R23"/>
+    <mergeCell ref="D7:AF7"/>
+    <mergeCell ref="I1:Z5"/>
+    <mergeCell ref="B9:H9"/>
+    <mergeCell ref="F11:H11"/>
+    <mergeCell ref="J11:L11"/>
+    <mergeCell ref="AB11:AC11"/>
+    <mergeCell ref="B11:E11"/>
+    <mergeCell ref="Y11:AA11"/>
+    <mergeCell ref="P11:X11"/>
+    <mergeCell ref="R31:V31"/>
+    <mergeCell ref="R17:V17"/>
+    <mergeCell ref="W17:Z17"/>
+    <mergeCell ref="X51:AD55"/>
+    <mergeCell ref="F51:I51"/>
+    <mergeCell ref="F55:I55"/>
+    <mergeCell ref="N51:R51"/>
+    <mergeCell ref="B21:L21"/>
+    <mergeCell ref="B27:E27"/>
+    <mergeCell ref="B33:E33"/>
+    <mergeCell ref="F33:I33"/>
+    <mergeCell ref="K39:M39"/>
+    <mergeCell ref="N39:Q39"/>
+    <mergeCell ref="R39:V39"/>
+    <mergeCell ref="K33:P33"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.39370078740157483" right="0.39370078740157483" top="0.78740157480314965" bottom="0.39370078740157483" header="0" footer="0"/>
@@ -6680,6 +6684,21 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x01010095EF753253AC424BB919D030F322784C" ma:contentTypeVersion="11" ma:contentTypeDescription="Crie um novo documento." ma:contentTypeScope="" ma:versionID="5dee361c03f39daaba29bb6301110b52">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="61b10da2-a8bd-4c80-ada7-20e862ed4a55" xmlns:ns4="226b3370-e759-4194-8b3e-3f54776e6815" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="ba1a39153a8fc78cfabfc4e3ad702b04" ns3:_="" ns4:_="">
     <xsd:import namespace="61b10da2-a8bd-4c80-ada7-20e862ed4a55"/>
@@ -6888,36 +6907,10 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6D498770-2854-44B7-AA88-0BB2DC723969}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{42BA872A-576E-43AD-8084-92A56E3B6179}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="61b10da2-a8bd-4c80-ada7-20e862ed4a55"/>
-    <ds:schemaRef ds:uri="226b3370-e759-4194-8b3e-3f54776e6815"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -6940,9 +6933,20 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{42BA872A-576E-43AD-8084-92A56E3B6179}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6D498770-2854-44B7-AA88-0BB2DC723969}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="61b10da2-a8bd-4c80-ada7-20e862ed4a55"/>
+    <ds:schemaRef ds:uri="226b3370-e759-4194-8b3e-3f54776e6815"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>